--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,1047 +394,1047 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>265</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>258</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>257</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
-        <v>248</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
-        <v>249</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
-        <v>247</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
-        <v>257</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>247</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>261</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>264</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>272</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>277</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>216</v>
+        <v>666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>214</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>221</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>216</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>209</v>
+        <v>723</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>207</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>208</v>
+        <v>714</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>201</v>
+        <v>738</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>245</v>
+        <v>787</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>273</v>
+        <v>786</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>309</v>
+        <v>784</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>333</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>729</v>
+        <v>777</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>725</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>697</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>431</v>
+        <v>765</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>424</v>
+        <v>753</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>416</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>370</v>
+        <v>746</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>287</v>
+        <v>539</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>270</v>
+        <v>534</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>292</v>
+        <v>544</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>299</v>
+        <v>692</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>227</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>205</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>197</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>196</v>
+        <v>393</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>156</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>153</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>163</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>161</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>151</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>152</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>179</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>181</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>216</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>223</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>252</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>428</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>448</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>464</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>510</v>
+        <v>424</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>861</v>
+        <v>799</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>871</v>
+        <v>816</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>869</v>
+        <v>831</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>874</v>
+        <v>855</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>928</v>
+        <v>907</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>933</v>
+        <v>921</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>937</v>
+        <v>917</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>934</v>
+        <v>946</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>903</v>
+        <v>939</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>904</v>
+        <v>937</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>908</v>
+        <v>983</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>910</v>
+        <v>987</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>872</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>871</v>
+        <v>975</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>865</v>
+        <v>967</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>842</v>
+        <v>937</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>841</v>
+        <v>938</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>833</v>
+        <v>936</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>631</v>
+        <v>865</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>617</v>
+        <v>855</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>618</v>
+        <v>854</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>620</v>
+        <v>851</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>458</v>
+        <v>718</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>440</v>
+        <v>722</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>439</v>
+        <v>683</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>435</v>
+        <v>667</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>298</v>
+        <v>635</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
-        <v>297</v>
+        <v>637</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
-        <v>298</v>
+        <v>635</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
-        <v>305</v>
+        <v>634</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
-        <v>572</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>616</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>614</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
-        <v>360</v>
+        <v>603</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
-        <v>353</v>
+        <v>595</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
-        <v>354</v>
+        <v>596</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
-        <v>352</v>
+        <v>603</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
-        <v>300</v>
+        <v>574</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
-        <v>295</v>
+        <v>566</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
-        <v>296</v>
+        <v>549</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
-        <v>295</v>
+        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
-        <v>296</v>
+        <v>535</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
-        <v>294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
-        <v>296</v>
+        <v>533</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
-        <v>303</v>
+        <v>535</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>361</v>
+        <v>532</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
-        <v>368</v>
+        <v>535</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
-        <v>381</v>
+        <v>536</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
-        <v>394</v>
+        <v>563</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>505</v>
+        <v>654</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>506</v>
+        <v>672</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>508</v>
+        <v>671</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>677</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>609</v>
+        <v>829</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>616</v>
+        <v>818</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>609</v>
+        <v>809</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>605</v>
+        <v>807</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>301</v>
+        <v>785</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1442,39 +1442,39 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,775 +394,775 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>670</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
-        <v>658</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
-        <v>661</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
-        <v>669</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
-        <v>680</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
-        <v>676</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
-        <v>677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>678</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>666</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>663</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>666</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>667</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>669</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>702</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>689</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>714</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>738</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>787</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>786</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>780</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>567</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>777</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>782</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>784</v>
+        <v>581</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>765</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>753</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>751</v>
+        <v>465</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>746</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>539</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>534</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>544</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>692</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>420</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>421</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>414</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>393</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>263</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>256</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>165</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>164</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>126</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>121</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>124</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>125</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>120</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>119</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>120</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>123</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>188</v>
+        <v>277</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>71</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>73</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>149</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>168</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>224</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>267</v>
+        <v>477</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>345</v>
+        <v>481</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>424</v>
+        <v>515</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>799</v>
+        <v>656</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>816</v>
+        <v>663</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>831</v>
+        <v>665</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>855</v>
+        <v>672</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>907</v>
+        <v>694</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>921</v>
+        <v>698</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>917</v>
+        <v>694</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>946</v>
+        <v>706</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>939</v>
+        <v>659</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>937</v>
+        <v>669</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>983</v>
+        <v>674</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>1132</v>
+        <v>645</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>975</v>
+        <v>644</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>967</v>
+        <v>645</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>643</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>937</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>588</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>938</v>
+        <v>587</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>936</v>
+        <v>590</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>865</v>
+        <v>546</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,103 +1170,103 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,127 +1274,127 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1085,7 +1085,7 @@
         <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>547</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1093,7 +1093,7 @@
         <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1101,7 +1101,7 @@
         <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>428</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1109,7 +1109,7 @@
         <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1117,7 +1117,7 @@
         <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1125,7 +1125,7 @@
         <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1133,7 +1133,7 @@
         <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1141,7 +1141,7 @@
         <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1149,7 +1149,7 @@
         <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1157,7 +1157,7 @@
         <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>343</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1165,7 +1165,7 @@
         <v>46107</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1173,7 +1173,7 @@
         <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1189,7 +1189,7 @@
         <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1197,7 +1197,7 @@
         <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1205,7 +1205,7 @@
         <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1213,7 +1213,7 @@
         <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1221,7 +1221,7 @@
         <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1229,7 +1229,7 @@
         <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1245,7 +1245,7 @@
         <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1253,7 +1253,7 @@
         <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1261,7 +1261,7 @@
         <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1269,7 +1269,7 @@
         <v>46107.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1285,7 +1285,7 @@
         <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1293,7 +1293,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1301,7 +1301,7 @@
         <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1317,7 +1317,7 @@
         <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1325,7 +1325,7 @@
         <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>464</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1333,7 +1333,7 @@
         <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>476</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1341,7 +1341,7 @@
         <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>479</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1349,7 +1349,7 @@
         <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1357,7 +1357,7 @@
         <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1373,7 +1373,7 @@
         <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>517</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1381,7 +1381,7 @@
         <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>522</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1389,7 +1389,7 @@
         <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>536</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1397,7 +1397,7 @@
         <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>615</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -1405,7 +1405,7 @@
         <v>46107.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>597</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1413,7 +1413,7 @@
         <v>46107.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>606</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -1421,7 +1421,7 @@
         <v>46107.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>454</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1429,7 +1429,7 @@
         <v>46107.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1437,7 +1437,7 @@
         <v>46107.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>493</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -1445,7 +1445,7 @@
         <v>46107.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>489</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1453,7 +1453,7 @@
         <v>46107.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>563</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1461,7 +1461,7 @@
         <v>46107.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>436</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1469,7 +1469,7 @@
         <v>46107.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -1477,7 +1477,7 @@
         <v>46107.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1485,7 +1485,7 @@
         <v>46107.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1493,7 +1493,7 @@
         <v>46107.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -1501,7 +1501,7 @@
         <v>46107.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1509,7 +1509,7 @@
         <v>46107.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -1517,7 +1517,7 @@
         <v>46107.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -1525,7 +1525,7 @@
         <v>46107.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -1533,7 +1533,7 @@
         <v>46107.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1541,7 +1541,7 @@
         <v>46107.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>211</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -1549,7 +1549,7 @@
         <v>46107.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>46107.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -1565,7 +1565,7 @@
         <v>46107.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -1573,7 +1573,7 @@
         <v>46107.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -1581,7 +1581,7 @@
         <v>46107.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -1589,7 +1589,7 @@
         <v>46107.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -1597,7 +1597,7 @@
         <v>46107.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -1605,7 +1605,7 @@
         <v>46107.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>327</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -1613,7 +1613,7 @@
         <v>46107.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>366</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -1621,7 +1621,7 @@
         <v>46107.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -1629,7 +1629,7 @@
         <v>46107.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -1637,7 +1637,7 @@
         <v>46107.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -1645,7 +1645,7 @@
         <v>46107.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -1653,7 +1653,7 @@
         <v>46107.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>412</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -1661,7 +1661,7 @@
         <v>46107.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -1669,7 +1669,7 @@
         <v>46107.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -1677,7 +1677,7 @@
         <v>46107.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>462</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -1685,7 +1685,7 @@
         <v>46107.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>464</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -1693,7 +1693,7 @@
         <v>46107.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>461</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -1701,7 +1701,7 @@
         <v>46107.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -1709,7 +1709,7 @@
         <v>46107.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>609</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -1717,7 +1717,7 @@
         <v>46107.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>653</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -1725,7 +1725,7 @@
         <v>46107.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>669</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -1733,7 +1733,7 @@
         <v>46107.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>675</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -1741,7 +1741,7 @@
         <v>46107.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>755</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -1749,7 +1749,7 @@
         <v>46107.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>770</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -1757,7 +1757,7 @@
         <v>46107.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>787</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -1765,7 +1765,7 @@
         <v>46107.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>780</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -1773,7 +1773,7 @@
         <v>46107.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -1789,7 +1789,7 @@
         <v>46107.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>747</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -1797,7 +1797,7 @@
         <v>46107.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>742</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -1805,7 +1805,7 @@
         <v>46107.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>703</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -1813,7 +1813,7 @@
         <v>46107.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>702</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -1821,7 +1821,7 @@
         <v>46107.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -1829,7 +1829,7 @@
         <v>46107.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>696</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -1837,7 +1837,7 @@
         <v>46107.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>648</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -1845,7 +1845,7 @@
         <v>46107.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -1861,7 +1861,7 @@
         <v>46107.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>587</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -1869,7 +1869,7 @@
         <v>46107.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>408</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -1877,7 +1877,7 @@
         <v>46107.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -1885,7 +1885,7 @@
         <v>46107.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -1893,7 +1893,7 @@
         <v>46107.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>417</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -1901,7 +1901,7 @@
         <v>46107.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -1909,7 +1909,7 @@
         <v>46107.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>363</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -1917,7 +1917,7 @@
         <v>46107.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>365</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -1925,6 +1925,3046 @@
         <v>46107.98958333334</v>
       </c>
       <c r="B193">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B194">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46108.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46108.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46108.03125</v>
+      </c>
+      <c r="B197">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46108.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46108.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46108.0625</v>
+      </c>
+      <c r="B200">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46108.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46108.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46108.09375</v>
+      </c>
+      <c r="B203">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46108.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46108.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46108.125</v>
+      </c>
+      <c r="B206">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46108.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46108.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46108.15625</v>
+      </c>
+      <c r="B209">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46108.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46108.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46108.1875</v>
+      </c>
+      <c r="B212">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46108.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46108.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46108.21875</v>
+      </c>
+      <c r="B215">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46108.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46108.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46108.25</v>
+      </c>
+      <c r="B218">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46108.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46108.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46108.28125</v>
+      </c>
+      <c r="B221">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46108.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46108.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46108.3125</v>
+      </c>
+      <c r="B224">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46108.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46108.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46108.34375</v>
+      </c>
+      <c r="B227">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46108.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46108.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46108.375</v>
+      </c>
+      <c r="B230">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46108.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46108.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46108.40625</v>
+      </c>
+      <c r="B233">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46108.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46108.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46108.4375</v>
+      </c>
+      <c r="B236">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46108.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46108.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46108.46875</v>
+      </c>
+      <c r="B239">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46108.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46108.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46108.5</v>
+      </c>
+      <c r="B242">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46108.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46108.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46108.53125</v>
+      </c>
+      <c r="B245">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46108.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46108.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46108.5625</v>
+      </c>
+      <c r="B248">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46108.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46108.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46108.59375</v>
+      </c>
+      <c r="B251">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46108.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46108.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46108.625</v>
+      </c>
+      <c r="B254">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46108.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46108.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46108.65625</v>
+      </c>
+      <c r="B257">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46108.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46108.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46108.6875</v>
+      </c>
+      <c r="B260">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46108.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46108.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46108.71875</v>
+      </c>
+      <c r="B263">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46108.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46108.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46108.75</v>
+      </c>
+      <c r="B266">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46108.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46108.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46108.78125</v>
+      </c>
+      <c r="B269">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46108.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46108.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46108.8125</v>
+      </c>
+      <c r="B272">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46108.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46108.84375</v>
+      </c>
+      <c r="B275">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46108.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46108.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46108.875</v>
+      </c>
+      <c r="B278">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46108.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46108.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46108.90625</v>
+      </c>
+      <c r="B281">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46108.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46108.9375</v>
+      </c>
+      <c r="B284">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46108.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46108.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46108.96875</v>
+      </c>
+      <c r="B287">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46108.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46108.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B290">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46109.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46109.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46109.03125</v>
+      </c>
+      <c r="B293">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46109.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46109.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46109.0625</v>
+      </c>
+      <c r="B296">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46109.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46109.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46109.09375</v>
+      </c>
+      <c r="B299">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46109.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46109.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46109.125</v>
+      </c>
+      <c r="B302">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46109.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46109.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46109.15625</v>
+      </c>
+      <c r="B305">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46109.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46109.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46109.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46109.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46109.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46109.21875</v>
+      </c>
+      <c r="B311">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46109.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46109.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46109.25</v>
+      </c>
+      <c r="B314">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46109.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46109.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46109.28125</v>
+      </c>
+      <c r="B317">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46109.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46109.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46109.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46109.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46109.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46109.34375</v>
+      </c>
+      <c r="B323">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46109.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46109.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46109.375</v>
+      </c>
+      <c r="B326">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46109.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46109.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46109.40625</v>
+      </c>
+      <c r="B329">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46109.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46109.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46109.4375</v>
+      </c>
+      <c r="B332">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46109.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46109.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46109.46875</v>
+      </c>
+      <c r="B335">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46109.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46109.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46109.5</v>
+      </c>
+      <c r="B338">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46109.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46109.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46109.53125</v>
+      </c>
+      <c r="B341">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46109.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46109.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46109.5625</v>
+      </c>
+      <c r="B344">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46109.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46109.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46109.59375</v>
+      </c>
+      <c r="B347">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46109.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46109.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46109.625</v>
+      </c>
+      <c r="B350">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46109.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46109.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46109.65625</v>
+      </c>
+      <c r="B353">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46109.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46109.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46109.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46109.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46109.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46109.71875</v>
+      </c>
+      <c r="B359">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46109.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46109.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46109.75</v>
+      </c>
+      <c r="B362">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46109.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46109.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46109.78125</v>
+      </c>
+      <c r="B365">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46109.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46109.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46109.8125</v>
+      </c>
+      <c r="B368">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46109.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46109.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46109.84375</v>
+      </c>
+      <c r="B371">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46109.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46109.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46109.875</v>
+      </c>
+      <c r="B374">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46109.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46109.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46109.90625</v>
+      </c>
+      <c r="B377">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46109.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46109.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46109.9375</v>
+      </c>
+      <c r="B380">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46109.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46109.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46109.96875</v>
+      </c>
+      <c r="B383">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46109.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46109.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46110</v>
+      </c>
+      <c r="B386">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46110.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46110.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46110.03125</v>
+      </c>
+      <c r="B389">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46110.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46110.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46110.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46110.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46110.125</v>
+      </c>
+      <c r="B394">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46110.13541666666</v>
+      </c>
+      <c r="B395">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46110.14583333334</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46110.15625</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46110.16666666666</v>
+      </c>
+      <c r="B398">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46110.17708333334</v>
+      </c>
+      <c r="B399">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46110.1875</v>
+      </c>
+      <c r="B400">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46110.19791666666</v>
+      </c>
+      <c r="B401">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46110.20833333334</v>
+      </c>
+      <c r="B402">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46110.21875</v>
+      </c>
+      <c r="B403">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46110.22916666666</v>
+      </c>
+      <c r="B404">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46110.23958333334</v>
+      </c>
+      <c r="B405">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46110.25</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46110.26041666666</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46110.27083333334</v>
+      </c>
+      <c r="B408">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46110.28125</v>
+      </c>
+      <c r="B409">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46110.29166666666</v>
+      </c>
+      <c r="B410">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46110.30208333334</v>
+      </c>
+      <c r="B411">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46110.3125</v>
+      </c>
+      <c r="B412">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46110.32291666666</v>
+      </c>
+      <c r="B413">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46110.33333333334</v>
+      </c>
+      <c r="B414">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46110.34375</v>
+      </c>
+      <c r="B415">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46110.35416666666</v>
+      </c>
+      <c r="B416">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46110.36458333334</v>
+      </c>
+      <c r="B417">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46110.375</v>
+      </c>
+      <c r="B418">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46110.38541666666</v>
+      </c>
+      <c r="B419">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46110.39583333334</v>
+      </c>
+      <c r="B420">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46110.40625</v>
+      </c>
+      <c r="B421">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46110.41666666666</v>
+      </c>
+      <c r="B422">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46110.42708333334</v>
+      </c>
+      <c r="B423">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46110.4375</v>
+      </c>
+      <c r="B424">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46110.44791666666</v>
+      </c>
+      <c r="B425">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46110.45833333334</v>
+      </c>
+      <c r="B426">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46110.46875</v>
+      </c>
+      <c r="B427">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46110.47916666666</v>
+      </c>
+      <c r="B428">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46110.48958333334</v>
+      </c>
+      <c r="B429">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46110.5</v>
+      </c>
+      <c r="B430">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46110.51041666666</v>
+      </c>
+      <c r="B431">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46110.52083333334</v>
+      </c>
+      <c r="B432">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46110.53125</v>
+      </c>
+      <c r="B433">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46110.54166666666</v>
+      </c>
+      <c r="B434">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46110.55208333334</v>
+      </c>
+      <c r="B435">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46110.5625</v>
+      </c>
+      <c r="B436">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46110.57291666666</v>
+      </c>
+      <c r="B437">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46110.58333333334</v>
+      </c>
+      <c r="B438">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46110.59375</v>
+      </c>
+      <c r="B439">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46110.60416666666</v>
+      </c>
+      <c r="B440">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46110.61458333334</v>
+      </c>
+      <c r="B441">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46110.625</v>
+      </c>
+      <c r="B442">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46110.63541666666</v>
+      </c>
+      <c r="B443">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46110.64583333334</v>
+      </c>
+      <c r="B444">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46110.65625</v>
+      </c>
+      <c r="B445">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46110.66666666666</v>
+      </c>
+      <c r="B446">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46110.67708333334</v>
+      </c>
+      <c r="B447">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46110.6875</v>
+      </c>
+      <c r="B448">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46110.69791666666</v>
+      </c>
+      <c r="B449">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46110.70833333334</v>
+      </c>
+      <c r="B450">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46110.71875</v>
+      </c>
+      <c r="B451">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46110.72916666666</v>
+      </c>
+      <c r="B452">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46110.73958333334</v>
+      </c>
+      <c r="B453">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46110.75</v>
+      </c>
+      <c r="B454">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46110.76041666666</v>
+      </c>
+      <c r="B455">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46110.77083333334</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46110.78125</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46110.79166666666</v>
+      </c>
+      <c r="B458">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46110.80208333334</v>
+      </c>
+      <c r="B459">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46110.8125</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46110.82291666666</v>
+      </c>
+      <c r="B461">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46110.83333333334</v>
+      </c>
+      <c r="B462">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46110.84375</v>
+      </c>
+      <c r="B463">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46110.85416666666</v>
+      </c>
+      <c r="B464">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46110.86458333334</v>
+      </c>
+      <c r="B465">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46110.875</v>
+      </c>
+      <c r="B466">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46110.88541666666</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46110.89583333334</v>
+      </c>
+      <c r="B468">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46110.90625</v>
+      </c>
+      <c r="B469">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46110.91666666666</v>
+      </c>
+      <c r="B470">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46110.92708333334</v>
+      </c>
+      <c r="B471">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46110.9375</v>
+      </c>
+      <c r="B472">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46110.94791666666</v>
+      </c>
+      <c r="B473">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46110.95833333334</v>
+      </c>
+      <c r="B474">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46110.96875</v>
+      </c>
+      <c r="B475">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46110.97916666666</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46110.98958333334</v>
+      </c>
+      <c r="B477">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46111.01041666666</v>
+      </c>
+      <c r="B479">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46111.02083333334</v>
+      </c>
+      <c r="B480">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46111.03125</v>
+      </c>
+      <c r="B481">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46111.04166666666</v>
+      </c>
+      <c r="B482">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46111.05208333334</v>
+      </c>
+      <c r="B483">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46111.0625</v>
+      </c>
+      <c r="B484">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46111.07291666666</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46111.08333333334</v>
+      </c>
+      <c r="B486">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
+        <v>46111.09375</v>
+      </c>
+      <c r="B487">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
+        <v>46111.10416666666</v>
+      </c>
+      <c r="B488">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
+        <v>46111.11458333334</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
+        <v>46111.125</v>
+      </c>
+      <c r="B490">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
+        <v>46111.13541666666</v>
+      </c>
+      <c r="B491">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
+        <v>46111.14583333334</v>
+      </c>
+      <c r="B492">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
+        <v>46111.15625</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
+        <v>46111.16666666666</v>
+      </c>
+      <c r="B494">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
+        <v>46111.17708333334</v>
+      </c>
+      <c r="B495">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
+        <v>46111.1875</v>
+      </c>
+      <c r="B496">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
+        <v>46111.19791666666</v>
+      </c>
+      <c r="B497">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
+        <v>46111.20833333334</v>
+      </c>
+      <c r="B498">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
+        <v>46111.21875</v>
+      </c>
+      <c r="B499">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
+        <v>46111.22916666666</v>
+      </c>
+      <c r="B500">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
+        <v>46111.23958333334</v>
+      </c>
+      <c r="B501">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="2">
+        <v>46111.25</v>
+      </c>
+      <c r="B502">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2">
+        <v>46111.26041666666</v>
+      </c>
+      <c r="B503">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2">
+        <v>46111.27083333334</v>
+      </c>
+      <c r="B504">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2">
+        <v>46111.28125</v>
+      </c>
+      <c r="B505">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2">
+        <v>46111.29166666666</v>
+      </c>
+      <c r="B506">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2">
+        <v>46111.30208333334</v>
+      </c>
+      <c r="B507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="2">
+        <v>46111.3125</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="2">
+        <v>46111.32291666666</v>
+      </c>
+      <c r="B509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2">
+        <v>46111.34375</v>
+      </c>
+      <c r="B511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2">
+        <v>46111.35416666666</v>
+      </c>
+      <c r="B512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2">
+        <v>46111.36458333334</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2">
+        <v>46111.375</v>
+      </c>
+      <c r="B514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2">
+        <v>46111.38541666666</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2">
+        <v>46111.39583333334</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2">
+        <v>46111.40625</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2">
+        <v>46111.41666666666</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2">
+        <v>46111.42708333334</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2">
+        <v>46111.4375</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2">
+        <v>46111.44791666666</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2">
+        <v>46111.45833333334</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2">
+        <v>46111.46875</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2">
+        <v>46111.47916666666</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2">
+        <v>46111.48958333334</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="2">
+        <v>46111.5</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2">
+        <v>46111.51041666666</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2">
+        <v>46111.52083333334</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2">
+        <v>46111.53125</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2">
+        <v>46111.54166666666</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2">
+        <v>46111.55208333334</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2">
+        <v>46111.5625</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2">
+        <v>46111.57291666666</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2">
+        <v>46111.58333333334</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2">
+        <v>46111.59375</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2">
+        <v>46111.60416666666</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2">
+        <v>46111.61458333334</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2">
+        <v>46111.625</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2">
+        <v>46111.63541666666</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2">
+        <v>46111.64583333334</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2">
+        <v>46111.65625</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2">
+        <v>46111.66666666666</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2">
+        <v>46111.67708333334</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2">
+        <v>46111.6875</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2">
+        <v>46111.69791666666</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2">
+        <v>46111.70833333334</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2">
+        <v>46111.71875</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2">
+        <v>46111.72916666666</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2">
+        <v>46111.73958333334</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2">
+        <v>46111.75</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2">
+        <v>46111.76041666666</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2">
+        <v>46111.77083333334</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2">
+        <v>46111.78125</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2">
+        <v>46111.79166666666</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2">
+        <v>46111.80208333334</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2">
+        <v>46111.8125</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2">
+        <v>46111.82291666666</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2">
+        <v>46111.84375</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2">
+        <v>46111.85416666666</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2">
+        <v>46111.86458333334</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2">
+        <v>46111.875</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2">
+        <v>46111.88541666666</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2">
+        <v>46111.89583333334</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2">
+        <v>46111.90625</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2">
+        <v>46111.91666666666</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2">
+        <v>46111.92708333334</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2">
+        <v>46111.9375</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2">
+        <v>46111.94791666666</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2">
+        <v>46111.95833333334</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2">
+        <v>46111.96875</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="2">
+        <v>46111.97916666666</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="2">
+        <v>46111.98958333334</v>
+      </c>
+      <c r="B573">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,1143 +394,1143 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
-        <v>683</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
-        <v>650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
-        <v>651</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
-        <v>645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
-        <v>617</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
-        <v>623</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>625</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>622</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>623</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>622</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>623</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>655</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
-        <v>654</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
-        <v>636</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
-        <v>679</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>701</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>690</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>692</v>
+        <v>522</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>676</v>
+        <v>523</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>668</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>601</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>614</v>
+        <v>556</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>615</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>589</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>564</v>
+        <v>547</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>410</v>
+        <v>634</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>400</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>396</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>378</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>285</v>
+        <v>650</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>238</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>233</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>236</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>235</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>234</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>233</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>234</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>236</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>217</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>253</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>264</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>230</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>225</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>227</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>223</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>214</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>226</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>220</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>191</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>198</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>276</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>272</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>332</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>350</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>437</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>431</v>
+        <v>573</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>750</v>
+        <v>782</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>826</v>
+        <v>783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>822</v>
+        <v>791</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>799</v>
+        <v>807</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>765</v>
+        <v>814</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>788</v>
+        <v>821</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>703</v>
+        <v>833</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>620</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>580</v>
+        <v>805</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>608</v>
+        <v>801</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>656</v>
+        <v>798</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>739</v>
+        <v>801</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>718</v>
+        <v>771</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>714</v>
+        <v>769</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>712</v>
+        <v>767</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>710</v>
+        <v>769</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>642</v>
+        <v>753</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>645</v>
+        <v>740</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>643</v>
+        <v>737</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>636</v>
+        <v>711</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>589</v>
+        <v>566</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>612</v>
+        <v>490</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>606</v>
+        <v>486</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>604</v>
+        <v>487</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>602</v>
+        <v>483</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>655</v>
+        <v>452</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
-        <v>665</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
-        <v>667</v>
+        <v>453</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
-        <v>665</v>
+        <v>464</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
-        <v>670</v>
+        <v>596</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
-        <v>668</v>
+        <v>599</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>598</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
-        <v>663</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
-        <v>664</v>
+        <v>599</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
-        <v>667</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
-        <v>666</v>
+        <v>565</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
-        <v>669</v>
+        <v>579</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
-        <v>724</v>
+        <v>604</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
-        <v>722</v>
+        <v>603</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
-        <v>721</v>
+        <v>602</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
-        <v>707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>709</v>
+        <v>625</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
-        <v>707</v>
+        <v>618</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
-        <v>709</v>
+        <v>633</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>713</v>
+        <v>631</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>788</v>
+        <v>662</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>799</v>
+        <v>688</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>790</v>
+        <v>696</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>792</v>
+        <v>711</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>776</v>
+        <v>708</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>787</v>
+        <v>699</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>792</v>
+        <v>705</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>679</v>
+        <v>704</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>669</v>
+        <v>706</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>670</v>
+        <v>688</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>664</v>
+        <v>694</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>410</v>
+        <v>645</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>339</v>
+        <v>640</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>320</v>
+        <v>593</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>297</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>138</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>134</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>133</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>130</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>155</v>
+        <v>282</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>274</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,15 +1538,15 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1183 +394,1183 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>380</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>381</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>376</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>396</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>433</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>448</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>390</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>418</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>423</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>458</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>443</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>480</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>485</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>450</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>476</v>
+        <v>631</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>492</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>522</v>
+        <v>688</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>523</v>
+        <v>696</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>548</v>
+        <v>711</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>556</v>
+        <v>708</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>507</v>
+        <v>699</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>493</v>
+        <v>705</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>565</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>571</v>
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>550</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>547</v>
+        <v>694</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>634</v>
+        <v>645</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>604</v>
+        <v>640</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>611</v>
+        <v>593</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>596</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>650</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>613</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>554</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>355</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>345</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>342</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>329</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>186</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>154</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>209</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>168</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>175</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>307</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>297</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>290</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>298</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>380</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>381</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>380</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>366</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>406</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>420</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>415</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>428</v>
+        <v>247</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>502</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>550</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>573</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>782</v>
+        <v>692</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>783</v>
+        <v>715</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>791</v>
+        <v>724</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>807</v>
+        <v>717</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>814</v>
+        <v>874</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>821</v>
+        <v>883</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>833</v>
+        <v>903</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>913</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>805</v>
+        <v>848</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>801</v>
+        <v>873</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>798</v>
+        <v>890</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>801</v>
+        <v>896</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>771</v>
+        <v>847</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>769</v>
+        <v>867</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>767</v>
+        <v>862</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>769</v>
+        <v>857</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>740</v>
+        <v>747</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>737</v>
+        <v>744</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>711</v>
+        <v>743</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>566</v>
+        <v>671</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>578</v>
+        <v>669</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>585</v>
+        <v>668</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>582</v>
+        <v>663</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>490</v>
+        <v>541</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>486</v>
+        <v>539</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>487</v>
+        <v>541</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>483</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>452</v>
+        <v>535</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
-        <v>456</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
-        <v>453</v>
+        <v>527</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
-        <v>464</v>
+        <v>524</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
-        <v>596</v>
+        <v>583</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
-        <v>599</v>
+        <v>586</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
-        <v>598</v>
+        <v>587</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
-        <v>565</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
-        <v>599</v>
+        <v>587</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
-        <v>545</v>
+        <v>584</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
-        <v>565</v>
+        <v>585</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
-        <v>604</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
-        <v>603</v>
+        <v>574</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
-        <v>602</v>
+        <v>579</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>625</v>
+        <v>598</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
-        <v>618</v>
+        <v>605</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>662</v>
+        <v>696</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>688</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>696</v>
+        <v>912</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>905</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>711</v>
+        <v>893</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>708</v>
+        <v>869</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>699</v>
+        <v>770</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>705</v>
+        <v>673</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>704</v>
+        <v>425</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>706</v>
+        <v>511</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>688</v>
+        <v>722</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>694</v>
+        <v>678</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>645</v>
+        <v>538</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>640</v>
+        <v>476</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>593</v>
+        <v>471</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>558</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>416</v>
+        <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>405</v>
+        <v>129</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>398</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>410</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>282</v>
+        <v>113</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>274</v>
+        <v>112</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>237</v>
+        <v>113</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>265</v>
+        <v>110</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>250</v>
+        <v>88</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,111 +1578,111 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>185</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>166</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,143 +1690,143 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>357</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>393</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>740</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>757</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>756</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>764</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>797</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>806</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>802</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>805</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>758</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>770</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>776</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,97 +1834,1633 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>705</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>686</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>675</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>597</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>584</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>581</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,63 +394,63 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>532</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>467</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>481</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>478</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>398</v>
@@ -458,1039 +458,1039 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>362</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>378</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>384</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>400</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>420</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>417</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>463</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>464</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>488</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>498</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>526</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>715</v>
+        <v>655</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>784</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>782</v>
+        <v>741</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>795</v>
+        <v>740</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>805</v>
+        <v>748</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>801</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>768</v>
+        <v>792</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>815</v>
+        <v>794</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>610</v>
+        <v>710</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>602</v>
+        <v>637</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>603</v>
+        <v>616</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>584</v>
+        <v>622</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>450</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>443</v>
+        <v>593</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>442</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>293</v>
+        <v>559</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>213</v>
+        <v>632</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>636</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>155</v>
+        <v>669</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>137</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>140</v>
+        <v>678</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>135</v>
+        <v>661</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>129</v>
+        <v>608</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>131</v>
+        <v>672</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>151</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>156</v>
+        <v>549</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>140</v>
+        <v>587</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>142</v>
+        <v>557</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>151</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>149</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>186</v>
+        <v>614</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>185</v>
+        <v>574</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>143</v>
+        <v>577</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>163</v>
+        <v>606</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>185</v>
+        <v>611</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>186</v>
+        <v>609</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>202</v>
+        <v>633</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>378</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>437</v>
+        <v>750</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>446</v>
+        <v>759</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>607</v>
+        <v>796</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>868</v>
+        <v>958</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>862</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>852</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>846</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>718</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>707</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>660</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>666</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>698</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>566</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>575</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>668</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>741</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>736</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>757</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>808</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>677</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>658</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>656</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>650</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>560</v>
+        <v>967</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>562</v>
+        <v>939</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>559</v>
+        <v>931</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>549</v>
+        <v>932</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>498</v>
+        <v>839</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>497</v>
+        <v>840</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>499</v>
+        <v>843</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>498</v>
+        <v>842</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>547</v>
+        <v>797</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
-        <v>552</v>
+        <v>794</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
-        <v>518</v>
+        <v>795</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
-        <v>467</v>
+        <v>792</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
-        <v>480</v>
+        <v>783</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
-        <v>515</v>
+        <v>792</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
-        <v>460</v>
+        <v>791</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
-        <v>398</v>
+        <v>775</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
-        <v>400</v>
+        <v>778</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
-        <v>415</v>
+        <v>779</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
-        <v>419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
-        <v>434</v>
+        <v>778</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
-        <v>325</v>
+        <v>700</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
-        <v>329</v>
+        <v>697</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
-        <v>336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
-        <v>312</v>
+        <v>700</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>350</v>
+        <v>790</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
-        <v>371</v>
+        <v>789</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
-        <v>359</v>
+        <v>788</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
-        <v>417</v>
+        <v>796</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>655</v>
+        <v>842</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>740</v>
+        <v>843</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>748</v>
+        <v>948</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>788</v>
+        <v>969</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>973</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>801</v>
+        <v>976</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>792</v>
+        <v>944</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>793</v>
+        <v>932</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>794</v>
+        <v>926</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>889</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>645</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>516</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>577</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>574</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>593</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,255 +394,255 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
-        <v>547</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
-        <v>552</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
-        <v>518</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
-        <v>467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
-        <v>480</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
-        <v>515</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
-        <v>460</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
-        <v>398</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
-        <v>400</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
-        <v>415</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
-        <v>419</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
-        <v>434</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>350</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
-        <v>371</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
-        <v>359</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>417</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>750</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>741</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>740</v>
+        <v>665</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>748</v>
+        <v>670</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>788</v>
+        <v>677</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>676</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>801</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>792</v>
+        <v>473</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>793</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>794</v>
+        <v>436</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -650,695 +650,695 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>710</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>637</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>616</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>622</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>591</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>593</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>610</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>559</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>632</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>636</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>630</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>669</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>677</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>678</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>608</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>672</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>530</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>549</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>587</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>557</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>600</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>613</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>614</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>574</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>577</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>606</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>611</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>609</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>633</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>749</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>750</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>796</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>958</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>1033</v>
+        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>1031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>1045</v>
+        <v>410</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>1175</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>1206</v>
+        <v>894</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>1189</v>
+        <v>998</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>1221</v>
+        <v>997</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>1173</v>
+        <v>993</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>1205</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>1207</v>
+        <v>995</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>1210</v>
+        <v>998</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>1182</v>
+        <v>958</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>1169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>1178</v>
+        <v>951</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>1177</v>
+        <v>950</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>1109</v>
+        <v>854</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
-        <v>1090</v>
+        <v>849</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>1068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>1069</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>967</v>
+        <v>721</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>939</v>
+        <v>693</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>931</v>
+        <v>685</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>932</v>
+        <v>682</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
-        <v>839</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
-        <v>840</v>
+        <v>496</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
-        <v>843</v>
+        <v>492</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
-        <v>842</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
-        <v>797</v>
+        <v>490</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
-        <v>794</v>
+        <v>477</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
-        <v>795</v>
+        <v>481</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
-        <v>792</v>
+        <v>478</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
-        <v>783</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
-        <v>792</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
-        <v>791</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
-        <v>775</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
-        <v>778</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
-        <v>779</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
-        <v>778</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
-        <v>700</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
-        <v>697</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
-        <v>700</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>790</v>
+        <v>410</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
-        <v>789</v>
+        <v>421</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
-        <v>788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>796</v>
+        <v>430</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>842</v>
+        <v>534</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>543</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1346,199 +1346,199 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>843</v>
+        <v>533</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>948</v>
+        <v>460</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>969</v>
+        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>973</v>
+        <v>450</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>976</v>
+        <v>451</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>944</v>
+        <v>329</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>932</v>
+        <v>317</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>926</v>
+        <v>322</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>889</v>
+        <v>329</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>650</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>645</v>
+        <v>220</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>553</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>516</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>577</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>574</v>
+        <v>130</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>593</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>540</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,23 +1546,23 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,287 +1578,287 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>151</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>349</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>377</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>795</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>793</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>812</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>799</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>809</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>826</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>790</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>775</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>771</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>769</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>688</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>686</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>685</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,65 +1866,1601 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>598</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>592</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>594</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>589</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>478</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,255 +394,255 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
-        <v>603</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
-        <v>602</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
-        <v>576</v>
+        <v>816</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
-        <v>557</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
-        <v>530</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
-        <v>504</v>
+        <v>833</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
-        <v>367</v>
+        <v>837</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
-        <v>332</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
-        <v>328</v>
+        <v>822</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
-        <v>336</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
-        <v>328</v>
+        <v>818</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>324</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
-        <v>323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
-        <v>324</v>
+        <v>824</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
-        <v>329</v>
+        <v>825</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>467</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
-        <v>478</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
-        <v>477</v>
+        <v>848</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>490</v>
+        <v>852</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>648</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>649</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>653</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>665</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>670</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>677</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>676</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>669</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>473</v>
+        <v>614</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>448</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>436</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -650,695 +650,695 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>352</v>
+        <v>557</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>344</v>
+        <v>538</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>339</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>187</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>245</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>254</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>230</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>226</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>142</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>123</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>141</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>173</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>286</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>281</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>271</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>128</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>128</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>126</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>132</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>131</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>127</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>125</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>146</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>178</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>181</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>201</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>370</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>388</v>
+        <v>569</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>589</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>410</v>
+        <v>636</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>864</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>894</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>998</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>997</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>993</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>1002</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>998</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>958</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>951</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>854</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>849</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>844</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>721</v>
+        <v>999</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>693</v>
+        <v>977</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>685</v>
+        <v>965</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
-        <v>682</v>
+        <v>962</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>500</v>
+        <v>883</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
-        <v>496</v>
+        <v>870</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
-        <v>492</v>
+        <v>865</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
-        <v>489</v>
+        <v>863</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
-        <v>490</v>
+        <v>826</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
-        <v>477</v>
+        <v>821</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
-        <v>481</v>
+        <v>816</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
-        <v>478</v>
+        <v>817</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
-        <v>276</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
-        <v>271</v>
+        <v>492</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
-        <v>270</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
-        <v>268</v>
+        <v>491</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
-        <v>272</v>
+        <v>408</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
-        <v>267</v>
+        <v>407</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
-        <v>268</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
-        <v>266</v>
+        <v>410</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
-        <v>269</v>
+        <v>438</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
-        <v>267</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
-        <v>268</v>
+        <v>440</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
-        <v>277</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
-        <v>410</v>
+        <v>571</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
-        <v>421</v>
+        <v>574</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>577</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>430</v>
+        <v>584</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>534</v>
+        <v>706</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>543</v>
+        <v>718</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1346,991 +1346,991 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>533</v>
+        <v>706</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>460</v>
+        <v>605</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>455</v>
+        <v>594</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>451</v>
+        <v>616</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>329</v>
+        <v>871</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>317</v>
+        <v>899</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>322</v>
+        <v>891</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>329</v>
+        <v>880</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>228</v>
+        <v>794</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>220</v>
+        <v>574</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>201</v>
+        <v>594</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>632</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>136</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>133</v>
+        <v>594</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>130</v>
+        <v>575</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>133</v>
+        <v>578</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>146</v>
+        <v>270</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>149</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>114</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>121</v>
+        <v>180</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>101</v>
+        <v>144</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>89</v>
+        <v>151</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>91</v>
+        <v>183</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>93</v>
+        <v>230</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>100</v>
+        <v>281</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>99</v>
+        <v>289</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>103</v>
+        <v>305</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>102</v>
+        <v>333</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>114</v>
+        <v>669</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>119</v>
+        <v>684</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>124</v>
+        <v>698</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>151</v>
+        <v>715</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>329</v>
+        <v>742</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>341</v>
+        <v>762</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>349</v>
+        <v>760</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>377</v>
+        <v>797</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>795</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>800</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>793</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>812</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>799</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>810</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>809</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>826</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>790</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>775</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>769</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>688</v>
+        <v>975</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>686</v>
+        <v>977</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>685</v>
+        <v>964</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>962</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
-        <v>598</v>
+        <v>665</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
-        <v>592</v>
+        <v>654</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
-        <v>594</v>
+        <v>651</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
-        <v>589</v>
+        <v>649</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
-        <v>490</v>
+        <v>571</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
-        <v>482</v>
+        <v>564</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
-        <v>478</v>
+        <v>565</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
-        <v>475</v>
+        <v>562</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
-        <v>320</v>
+        <v>628</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
-        <v>319</v>
+        <v>625</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
-        <v>318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
-        <v>317</v>
+        <v>623</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
-        <v>173</v>
+        <v>648</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
-        <v>162</v>
+        <v>644</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
-        <v>174</v>
+        <v>645</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
-        <v>158</v>
+        <v>643</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
-        <v>141</v>
+        <v>636</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
-        <v>140</v>
+        <v>641</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
-        <v>141</v>
+        <v>642</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
-        <v>139</v>
+        <v>634</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>138</v>
+        <v>637</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
-        <v>128</v>
+        <v>646</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
-        <v>118</v>
+        <v>652</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
-        <v>125</v>
+        <v>646</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>121</v>
+        <v>657</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
-        <v>120</v>
+        <v>658</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>119</v>
+        <v>669</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>123</v>
+        <v>674</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>172</v>
+        <v>652</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>178</v>
+        <v>668</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>184</v>
+        <v>675</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>185</v>
+        <v>680</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>191</v>
+        <v>735</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>189</v>
+        <v>821</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>188</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>190</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>205</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>207</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>205</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>168</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>151</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>131</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>187</v>
+        <v>922</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>198</v>
+        <v>920</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>180</v>
+        <v>905</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>175</v>
+        <v>663</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>112</v>
+        <v>581</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>110</v>
+        <v>303</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>108</v>
+        <v>283</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>109</v>
+        <v>284</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>108</v>
+        <v>307</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>98</v>
+        <v>260</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -2346,15 +2346,15 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -2362,1105 +2362,337 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>530</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
-        <v>705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
-        <v>711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
-        <v>707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
-        <v>681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
-        <v>686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
-        <v>670</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
-        <v>619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:2">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:2">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:2">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:2">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="1:2">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,671 +394,671 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B2">
-        <v>805</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46140.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
-        <v>798</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46140.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
-        <v>816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46140.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>799</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46140.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
-        <v>837</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46140.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
-        <v>836</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46140.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
-        <v>833</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46140.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
-        <v>837</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46140.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
-        <v>796</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46140.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
-        <v>822</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46140.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
-        <v>820</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46140.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
-        <v>818</v>
+        <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46140.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
-        <v>823</v>
+        <v>637</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46140.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46140.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
-        <v>824</v>
+        <v>652</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46140.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
-        <v>825</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46140.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>836</v>
+        <v>657</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46140.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
-        <v>844</v>
+        <v>658</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46140.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>848</v>
+        <v>669</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46140.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>852</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46140.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>1055</v>
+        <v>652</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46140.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>1054</v>
+        <v>668</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46140.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>1055</v>
+        <v>675</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46140.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>1050</v>
+        <v>680</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46140.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>1111</v>
+        <v>735</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46140.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>1115</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46140.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>1085</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46140.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>1066</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46140.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>614</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46140.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>607</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46140.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>605</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46140.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46140.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>557</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46140.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>538</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46140.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>481</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46140.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
-        <v>407</v>
+        <v>922</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46140.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>334</v>
+        <v>920</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46140.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>325</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46140.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>329</v>
+        <v>663</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46140.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
-        <v>326</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46140.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>193</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46140.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46140.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>192</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46140.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>189</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46140.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>176</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46140.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>184</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46140.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>198</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46140.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>200</v>
+        <v>321</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46140.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B50">
-        <v>187</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46140.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B51">
-        <v>189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46140.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B52">
-        <v>191</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46140.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46140.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B54">
-        <v>174</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46140.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B55">
-        <v>188</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46140.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B56">
-        <v>189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46140.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B57">
-        <v>179</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46140.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B58">
-        <v>208</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46140.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B59">
-        <v>192</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46140.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B60">
-        <v>207</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46140.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B61">
-        <v>208</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46140.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46140.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B63">
-        <v>209</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46140.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B64">
-        <v>226</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46140.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B65">
-        <v>221</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46140.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B66">
-        <v>311</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46140.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B67">
-        <v>340</v>
+        <v>526</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46140.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B68">
-        <v>343</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46140.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B69">
-        <v>367</v>
+        <v>538</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46140.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B70">
-        <v>558</v>
+        <v>587</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46140.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B71">
-        <v>569</v>
+        <v>601</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46140.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B72">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46140.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B73">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46140.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B74">
-        <v>1122</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46140.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B75">
-        <v>1132</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46140.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B76">
-        <v>1127</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46140.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B77">
-        <v>1136</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46140.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B78">
-        <v>1131</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46140.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B79">
-        <v>1135</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46140.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46140.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B81">
-        <v>1134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46140.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B82">
-        <v>1133</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46140.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B83">
-        <v>1130</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46140.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B84">
-        <v>1131</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46140.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,1319 +1066,1319 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46140.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B86">
-        <v>1023</v>
+        <v>898</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46140.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B87">
-        <v>1017</v>
+        <v>888</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46140.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B88">
-        <v>1020</v>
+        <v>875</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46140.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B89">
-        <v>1015</v>
+        <v>876</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46140.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B90">
-        <v>999</v>
+        <v>783</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46140.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B91">
-        <v>977</v>
+        <v>778</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46140.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B92">
-        <v>965</v>
+        <v>771</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46140.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B93">
-        <v>962</v>
+        <v>769</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46140.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B94">
-        <v>883</v>
+        <v>691</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46140.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B95">
-        <v>870</v>
+        <v>674</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46140.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B96">
-        <v>865</v>
+        <v>692</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46140.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B97">
-        <v>863</v>
+        <v>683</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B98">
-        <v>826</v>
+        <v>674</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46141.01041666666</v>
+        <v>46143.01041666666</v>
       </c>
       <c r="B99">
-        <v>821</v>
+        <v>671</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46141.02083333334</v>
+        <v>46143.02083333334</v>
       </c>
       <c r="B100">
-        <v>816</v>
+        <v>661</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46141.03125</v>
+        <v>46143.03125</v>
       </c>
       <c r="B101">
-        <v>817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46141.04166666666</v>
+        <v>46143.04166666666</v>
       </c>
       <c r="B102">
-        <v>498</v>
+        <v>580</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46141.05208333334</v>
+        <v>46143.05208333334</v>
       </c>
       <c r="B103">
-        <v>492</v>
+        <v>572</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46141.0625</v>
+        <v>46143.0625</v>
       </c>
       <c r="B104">
-        <v>496</v>
+        <v>573</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46141.07291666666</v>
+        <v>46143.07291666666</v>
       </c>
       <c r="B105">
-        <v>491</v>
+        <v>571</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46141.08333333334</v>
+        <v>46143.08333333334</v>
       </c>
       <c r="B106">
-        <v>408</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46141.09375</v>
+        <v>46143.09375</v>
       </c>
       <c r="B107">
-        <v>407</v>
+        <v>576</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46141.10416666666</v>
+        <v>46143.10416666666</v>
       </c>
       <c r="B108">
-        <v>428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46141.11458333334</v>
+        <v>46143.11458333334</v>
       </c>
       <c r="B109">
-        <v>410</v>
+        <v>575</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46141.125</v>
+        <v>46143.125</v>
       </c>
       <c r="B110">
-        <v>438</v>
+        <v>566</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46141.13541666666</v>
+        <v>46143.13541666666</v>
       </c>
       <c r="B111">
-        <v>441</v>
+        <v>583</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46141.14583333334</v>
+        <v>46143.14583333334</v>
       </c>
       <c r="B112">
-        <v>440</v>
+        <v>586</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46141.15625</v>
+        <v>46143.15625</v>
       </c>
       <c r="B113">
-        <v>444</v>
+        <v>567</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46141.16666666666</v>
+        <v>46143.16666666666</v>
       </c>
       <c r="B114">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46141.17708333334</v>
+        <v>46143.17708333334</v>
       </c>
       <c r="B115">
-        <v>574</v>
+        <v>559</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46141.1875</v>
+        <v>46143.1875</v>
       </c>
       <c r="B116">
-        <v>577</v>
+        <v>483</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46141.19791666666</v>
+        <v>46143.19791666666</v>
       </c>
       <c r="B117">
-        <v>584</v>
+        <v>488</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46141.20833333334</v>
+        <v>46143.20833333334</v>
       </c>
       <c r="B118">
-        <v>706</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46141.21875</v>
+        <v>46143.21875</v>
       </c>
       <c r="B119">
-        <v>718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46141.22916666666</v>
+        <v>46143.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46141.23958333334</v>
+        <v>46143.23958333334</v>
       </c>
       <c r="B121">
-        <v>706</v>
+        <v>445</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46141.25</v>
+        <v>46143.25</v>
       </c>
       <c r="B122">
-        <v>605</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46141.26041666666</v>
+        <v>46143.26041666666</v>
       </c>
       <c r="B123">
-        <v>594</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46141.27083333334</v>
+        <v>46143.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46141.28125</v>
+        <v>46143.28125</v>
       </c>
       <c r="B125">
-        <v>616</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46141.29166666666</v>
+        <v>46143.29166666666</v>
       </c>
       <c r="B126">
-        <v>871</v>
+        <v>313</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46141.30208333334</v>
+        <v>46143.30208333334</v>
       </c>
       <c r="B127">
-        <v>899</v>
+        <v>296</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46141.3125</v>
+        <v>46143.3125</v>
       </c>
       <c r="B128">
-        <v>891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46141.32291666666</v>
+        <v>46143.32291666666</v>
       </c>
       <c r="B129">
-        <v>880</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46141.33333333334</v>
+        <v>46143.33333333334</v>
       </c>
       <c r="B130">
-        <v>794</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46141.34375</v>
+        <v>46143.34375</v>
       </c>
       <c r="B131">
-        <v>574</v>
+        <v>247</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46141.35416666666</v>
+        <v>46143.35416666666</v>
       </c>
       <c r="B132">
-        <v>594</v>
+        <v>265</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46141.36458333334</v>
+        <v>46143.36458333334</v>
       </c>
       <c r="B133">
-        <v>632</v>
+        <v>240</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46141.375</v>
+        <v>46143.375</v>
       </c>
       <c r="B134">
-        <v>562</v>
+        <v>147</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46141.38541666666</v>
+        <v>46143.38541666666</v>
       </c>
       <c r="B135">
-        <v>594</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46141.39583333334</v>
+        <v>46143.39583333334</v>
       </c>
       <c r="B136">
-        <v>575</v>
+        <v>127</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46141.40625</v>
+        <v>46143.40625</v>
       </c>
       <c r="B137">
-        <v>578</v>
+        <v>119</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46141.41666666666</v>
+        <v>46143.41666666666</v>
       </c>
       <c r="B138">
-        <v>270</v>
+        <v>181</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46141.42708333334</v>
+        <v>46143.42708333334</v>
       </c>
       <c r="B139">
-        <v>239</v>
+        <v>182</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46141.4375</v>
+        <v>46143.4375</v>
       </c>
       <c r="B140">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46141.44791666666</v>
+        <v>46143.44791666666</v>
       </c>
       <c r="B141">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46141.45833333334</v>
+        <v>46143.45833333334</v>
       </c>
       <c r="B142">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46141.46875</v>
+        <v>46143.46875</v>
       </c>
       <c r="B143">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46141.47916666666</v>
+        <v>46143.47916666666</v>
       </c>
       <c r="B144">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46141.48958333334</v>
+        <v>46143.48958333334</v>
       </c>
       <c r="B145">
-        <v>121</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46141.5</v>
+        <v>46143.5</v>
       </c>
       <c r="B146">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46141.51041666666</v>
+        <v>46143.51041666666</v>
       </c>
       <c r="B147">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46141.52083333334</v>
+        <v>46143.52083333334</v>
       </c>
       <c r="B148">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46141.53125</v>
+        <v>46143.53125</v>
       </c>
       <c r="B149">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46141.54166666666</v>
+        <v>46143.54166666666</v>
       </c>
       <c r="B150">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46141.55208333334</v>
+        <v>46143.55208333334</v>
       </c>
       <c r="B151">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46141.5625</v>
+        <v>46143.5625</v>
       </c>
       <c r="B152">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46141.57291666666</v>
+        <v>46143.57291666666</v>
       </c>
       <c r="B153">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46141.58333333334</v>
+        <v>46143.58333333334</v>
       </c>
       <c r="B154">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46141.59375</v>
+        <v>46143.59375</v>
       </c>
       <c r="B155">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46141.60416666666</v>
+        <v>46143.60416666666</v>
       </c>
       <c r="B156">
-        <v>183</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46141.61458333334</v>
+        <v>46143.61458333334</v>
       </c>
       <c r="B157">
-        <v>230</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46141.625</v>
+        <v>46143.625</v>
       </c>
       <c r="B158">
-        <v>281</v>
+        <v>107</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46141.63541666666</v>
+        <v>46143.63541666666</v>
       </c>
       <c r="B159">
-        <v>289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46141.64583333334</v>
+        <v>46143.64583333334</v>
       </c>
       <c r="B160">
-        <v>305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46141.65625</v>
+        <v>46143.65625</v>
       </c>
       <c r="B161">
-        <v>333</v>
+        <v>119</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46141.66666666666</v>
+        <v>46143.66666666666</v>
       </c>
       <c r="B162">
-        <v>669</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46141.67708333334</v>
+        <v>46143.67708333334</v>
       </c>
       <c r="B163">
-        <v>684</v>
+        <v>220</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46141.6875</v>
+        <v>46143.6875</v>
       </c>
       <c r="B164">
-        <v>698</v>
+        <v>247</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46141.69791666666</v>
+        <v>46143.69791666666</v>
       </c>
       <c r="B165">
-        <v>715</v>
+        <v>317</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46141.70833333334</v>
+        <v>46143.70833333334</v>
       </c>
       <c r="B166">
-        <v>742</v>
+        <v>699</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46141.71875</v>
+        <v>46143.71875</v>
       </c>
       <c r="B167">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46141.72916666666</v>
+        <v>46143.72916666666</v>
       </c>
       <c r="B168">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46141.73958333334</v>
+        <v>46143.73958333334</v>
       </c>
       <c r="B169">
-        <v>797</v>
+        <v>783</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46141.75</v>
+        <v>46143.75</v>
       </c>
       <c r="B170">
-        <v>1156</v>
+        <v>964</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46141.76041666666</v>
+        <v>46143.76041666666</v>
       </c>
       <c r="B171">
-        <v>1164</v>
+        <v>965</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46141.77083333334</v>
+        <v>46143.77083333334</v>
       </c>
       <c r="B172">
-        <v>1110</v>
+        <v>966</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46141.78125</v>
+        <v>46143.78125</v>
       </c>
       <c r="B173">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46141.79166666666</v>
+        <v>46143.79166666666</v>
       </c>
       <c r="B174">
-        <v>1173</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46141.80208333334</v>
+        <v>46143.80208333334</v>
       </c>
       <c r="B175">
-        <v>1131</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46141.8125</v>
+        <v>46143.8125</v>
       </c>
       <c r="B176">
-        <v>1119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46141.82291666666</v>
+        <v>46143.82291666666</v>
       </c>
       <c r="B177">
-        <v>1141</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46141.83333333334</v>
+        <v>46143.83333333334</v>
       </c>
       <c r="B178">
-        <v>1056</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46141.84375</v>
+        <v>46143.84375</v>
       </c>
       <c r="B179">
-        <v>1022</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46141.85416666666</v>
+        <v>46143.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46141.86458333334</v>
+        <v>46143.86458333334</v>
       </c>
       <c r="B181">
-        <v>1011</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46141.875</v>
+        <v>46143.875</v>
       </c>
       <c r="B182">
-        <v>975</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46141.88541666666</v>
+        <v>46143.88541666666</v>
       </c>
       <c r="B183">
-        <v>977</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46141.89583333334</v>
+        <v>46143.89583333334</v>
       </c>
       <c r="B184">
-        <v>964</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46141.90625</v>
+        <v>46143.90625</v>
       </c>
       <c r="B185">
-        <v>962</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46141.91666666666</v>
+        <v>46143.91666666666</v>
       </c>
       <c r="B186">
-        <v>665</v>
+        <v>925</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46141.92708333334</v>
+        <v>46143.92708333334</v>
       </c>
       <c r="B187">
-        <v>654</v>
+        <v>914</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46141.9375</v>
+        <v>46143.9375</v>
       </c>
       <c r="B188">
-        <v>651</v>
+        <v>911</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46141.94791666666</v>
+        <v>46143.94791666666</v>
       </c>
       <c r="B189">
-        <v>649</v>
+        <v>906</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46141.95833333334</v>
+        <v>46143.95833333334</v>
       </c>
       <c r="B190">
-        <v>571</v>
+        <v>644</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46141.96875</v>
+        <v>46143.96875</v>
       </c>
       <c r="B191">
-        <v>564</v>
+        <v>619</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46141.97916666666</v>
+        <v>46143.97916666666</v>
       </c>
       <c r="B192">
-        <v>565</v>
+        <v>603</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46141.98958333334</v>
+        <v>46143.98958333334</v>
       </c>
       <c r="B193">
-        <v>562</v>
+        <v>619</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="2">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B194">
-        <v>628</v>
+        <v>664</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="2">
-        <v>46142.01041666666</v>
+        <v>46144.01041666666</v>
       </c>
       <c r="B195">
-        <v>625</v>
+        <v>665</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="2">
-        <v>46142.02083333334</v>
+        <v>46144.02083333334</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>662</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="2">
-        <v>46142.03125</v>
+        <v>46144.03125</v>
       </c>
       <c r="B197">
-        <v>623</v>
+        <v>658</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="2">
-        <v>46142.04166666666</v>
+        <v>46144.04166666666</v>
       </c>
       <c r="B198">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="2">
-        <v>46142.05208333334</v>
+        <v>46144.05208333334</v>
       </c>
       <c r="B199">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="2">
-        <v>46142.0625</v>
+        <v>46144.0625</v>
       </c>
       <c r="B200">
-        <v>645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="2">
-        <v>46142.07291666666</v>
+        <v>46144.07291666666</v>
       </c>
       <c r="B201">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="2">
-        <v>46142.08333333334</v>
+        <v>46144.08333333334</v>
       </c>
       <c r="B202">
-        <v>636</v>
+        <v>571</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="2">
-        <v>46142.09375</v>
+        <v>46144.09375</v>
       </c>
       <c r="B203">
-        <v>641</v>
+        <v>567</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="2">
-        <v>46142.10416666666</v>
+        <v>46144.10416666666</v>
       </c>
       <c r="B204">
-        <v>642</v>
+        <v>568</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="2">
-        <v>46142.11458333334</v>
+        <v>46144.11458333334</v>
       </c>
       <c r="B205">
-        <v>634</v>
+        <v>580</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="2">
-        <v>46142.125</v>
+        <v>46144.125</v>
       </c>
       <c r="B206">
-        <v>637</v>
+        <v>382</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="2">
-        <v>46142.13541666666</v>
+        <v>46144.13541666666</v>
       </c>
       <c r="B207">
-        <v>646</v>
+        <v>426</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="2">
-        <v>46142.14583333334</v>
+        <v>46144.14583333334</v>
       </c>
       <c r="B208">
-        <v>652</v>
+        <v>439</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="2">
-        <v>46142.15625</v>
+        <v>46144.15625</v>
       </c>
       <c r="B209">
-        <v>646</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="2">
-        <v>46142.16666666666</v>
+        <v>46144.16666666666</v>
       </c>
       <c r="B210">
-        <v>657</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="2">
-        <v>46142.17708333334</v>
+        <v>46144.17708333334</v>
       </c>
       <c r="B211">
-        <v>658</v>
+        <v>441</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="2">
-        <v>46142.1875</v>
+        <v>46144.1875</v>
       </c>
       <c r="B212">
-        <v>669</v>
+        <v>439</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="2">
-        <v>46142.19791666666</v>
+        <v>46144.19791666666</v>
       </c>
       <c r="B213">
-        <v>674</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="2">
-        <v>46142.20833333334</v>
+        <v>46144.20833333334</v>
       </c>
       <c r="B214">
-        <v>652</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="2">
-        <v>46142.21875</v>
+        <v>46144.21875</v>
       </c>
       <c r="B215">
-        <v>668</v>
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="2">
-        <v>46142.22916666666</v>
+        <v>46144.22916666666</v>
       </c>
       <c r="B216">
-        <v>675</v>
+        <v>452</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="2">
-        <v>46142.23958333334</v>
+        <v>46144.23958333334</v>
       </c>
       <c r="B217">
-        <v>680</v>
+        <v>455</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="2">
-        <v>46142.25</v>
+        <v>46144.25</v>
       </c>
       <c r="B218">
-        <v>735</v>
+        <v>627</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="2">
-        <v>46142.26041666666</v>
+        <v>46144.26041666666</v>
       </c>
       <c r="B219">
-        <v>821</v>
+        <v>655</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="2">
-        <v>46142.27083333334</v>
+        <v>46144.27083333334</v>
       </c>
       <c r="B220">
-        <v>1052</v>
+        <v>653</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="2">
-        <v>46142.28125</v>
+        <v>46144.28125</v>
       </c>
       <c r="B221">
-        <v>1110</v>
+        <v>645</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="2">
-        <v>46142.29166666666</v>
+        <v>46144.29166666666</v>
       </c>
       <c r="B222">
-        <v>1034</v>
+        <v>608</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="2">
-        <v>46142.30208333334</v>
+        <v>46144.30208333334</v>
       </c>
       <c r="B223">
-        <v>1089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="2">
-        <v>46142.3125</v>
+        <v>46144.3125</v>
       </c>
       <c r="B224">
-        <v>1088</v>
+        <v>663</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="2">
-        <v>46142.32291666666</v>
+        <v>46144.32291666666</v>
       </c>
       <c r="B225">
-        <v>1078</v>
+        <v>661</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="2">
-        <v>46142.33333333334</v>
+        <v>46144.33333333334</v>
       </c>
       <c r="B226">
-        <v>1113</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="2">
-        <v>46142.34375</v>
+        <v>46144.34375</v>
       </c>
       <c r="B227">
-        <v>1087</v>
+        <v>438</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="2">
-        <v>46142.35416666666</v>
+        <v>46144.35416666666</v>
       </c>
       <c r="B228">
-        <v>1040</v>
+        <v>435</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="2">
-        <v>46142.36458333334</v>
+        <v>46144.36458333334</v>
       </c>
       <c r="B229">
-        <v>922</v>
+        <v>430</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="2">
-        <v>46142.375</v>
+        <v>46144.375</v>
       </c>
       <c r="B230">
-        <v>920</v>
+        <v>367</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" s="2">
-        <v>46142.38541666666</v>
+        <v>46144.38541666666</v>
       </c>
       <c r="B231">
-        <v>905</v>
+        <v>340</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" s="2">
-        <v>46142.39583333334</v>
+        <v>46144.39583333334</v>
       </c>
       <c r="B232">
-        <v>663</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" s="2">
-        <v>46142.40625</v>
+        <v>46144.40625</v>
       </c>
       <c r="B233">
-        <v>581</v>
+        <v>247</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" s="2">
-        <v>46142.41666666666</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="B234">
-        <v>303</v>
+        <v>164</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="2">
-        <v>46142.42708333334</v>
+        <v>46144.42708333334</v>
       </c>
       <c r="B235">
-        <v>283</v>
+        <v>187</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="2">
-        <v>46142.4375</v>
+        <v>46144.4375</v>
       </c>
       <c r="B236">
-        <v>284</v>
+        <v>229</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="2">
-        <v>46142.44791666666</v>
+        <v>46144.44791666666</v>
       </c>
       <c r="B237">
-        <v>307</v>
+        <v>243</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="2">
-        <v>46142.45833333334</v>
+        <v>46144.45833333334</v>
       </c>
       <c r="B238">
-        <v>260</v>
+        <v>162</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="2">
-        <v>46142.46875</v>
+        <v>46144.46875</v>
       </c>
       <c r="B239">
-        <v>0</v>
+        <v>173</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="2">
-        <v>46142.47916666666</v>
+        <v>46144.47916666666</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="2">
-        <v>46142.48958333334</v>
+        <v>46144.48958333334</v>
       </c>
       <c r="B241">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="2">
-        <v>46142.5</v>
+        <v>46144.5</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>173</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="2">
-        <v>46142.51041666666</v>
+        <v>46144.51041666666</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>167</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" s="2">
-        <v>46142.52083333334</v>
+        <v>46144.52083333334</v>
       </c>
       <c r="B244">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="2">
-        <v>46142.53125</v>
+        <v>46144.53125</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="2">
-        <v>46142.54166666666</v>
+        <v>46144.54166666666</v>
       </c>
       <c r="B246">
-        <v>0</v>
+        <v>111</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="2">
-        <v>46142.55208333334</v>
+        <v>46144.55208333334</v>
       </c>
       <c r="B247">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="2">
-        <v>46142.5625</v>
+        <v>46144.5625</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="2">
-        <v>46142.57291666666</v>
+        <v>46144.57291666666</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="2">
-        <v>46142.58333333334</v>
+        <v>46144.58333333334</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -2386,23 +2386,23 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="2">
-        <v>46142.59375</v>
+        <v>46144.59375</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="2">
-        <v>46142.60416666666</v>
+        <v>46144.60416666666</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="2">
-        <v>46142.61458333334</v>
+        <v>46144.61458333334</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -2410,289 +2410,1825 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="2">
-        <v>46142.625</v>
+        <v>46144.625</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>134</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="2">
-        <v>46142.63541666666</v>
+        <v>46144.63541666666</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="2">
-        <v>46142.64583333334</v>
+        <v>46144.64583333334</v>
       </c>
       <c r="B256">
-        <v>0</v>
+        <v>158</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="2">
-        <v>46142.65625</v>
+        <v>46144.65625</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="2">
-        <v>46142.66666666666</v>
+        <v>46144.66666666666</v>
       </c>
       <c r="B258">
-        <v>0</v>
+        <v>430</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="2">
-        <v>46142.67708333334</v>
+        <v>46144.67708333334</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>444</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="2">
-        <v>46142.6875</v>
+        <v>46144.6875</v>
       </c>
       <c r="B260">
-        <v>0</v>
+        <v>451</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="2">
-        <v>46142.69791666666</v>
+        <v>46144.69791666666</v>
       </c>
       <c r="B261">
-        <v>0</v>
+        <v>486</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="2">
-        <v>46142.70833333334</v>
+        <v>46144.70833333334</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>802</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="2">
-        <v>46142.71875</v>
+        <v>46144.71875</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>801</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="2">
-        <v>46142.72916666666</v>
+        <v>46144.72916666666</v>
       </c>
       <c r="B264">
-        <v>0</v>
+        <v>797</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="2">
-        <v>46142.73958333334</v>
+        <v>46144.73958333334</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>822</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="2">
-        <v>46142.75</v>
+        <v>46144.75</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="2">
-        <v>46142.76041666666</v>
+        <v>46144.76041666666</v>
       </c>
       <c r="B267">
-        <v>0</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="2">
-        <v>46142.77083333334</v>
+        <v>46144.77083333334</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="2">
-        <v>46142.78125</v>
+        <v>46144.78125</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="2">
-        <v>46142.79166666666</v>
+        <v>46144.79166666666</v>
       </c>
       <c r="B270">
-        <v>0</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="2">
-        <v>46142.80208333334</v>
+        <v>46144.80208333334</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="2">
-        <v>46142.8125</v>
+        <v>46144.8125</v>
       </c>
       <c r="B272">
-        <v>0</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="2">
-        <v>46142.82291666666</v>
+        <v>46144.82291666666</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" s="2">
-        <v>46142.83333333334</v>
+        <v>46144.83333333334</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="2">
-        <v>46142.84375</v>
+        <v>46144.84375</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="2">
-        <v>46142.85416666666</v>
+        <v>46144.85416666666</v>
       </c>
       <c r="B276">
-        <v>0</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" s="2">
-        <v>46142.86458333334</v>
+        <v>46144.86458333334</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="2">
-        <v>46142.875</v>
+        <v>46144.875</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" s="2">
-        <v>46142.88541666666</v>
+        <v>46144.88541666666</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" s="2">
-        <v>46142.89583333334</v>
+        <v>46144.89583333334</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="2">
-        <v>46142.90625</v>
+        <v>46144.90625</v>
       </c>
       <c r="B281">
-        <v>0</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="2">
-        <v>46142.91666666666</v>
+        <v>46144.91666666666</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" s="2">
-        <v>46142.92708333334</v>
+        <v>46144.92708333334</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>978</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="2">
-        <v>46142.9375</v>
+        <v>46144.9375</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>991</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" s="2">
-        <v>46142.94791666666</v>
+        <v>46144.94791666666</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>990</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="2">
-        <v>46142.95833333334</v>
+        <v>46144.95833333334</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>882</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="2">
-        <v>46142.96875</v>
+        <v>46144.96875</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>880</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="2">
-        <v>46142.97916666666</v>
+        <v>46144.97916666666</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>904</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="2">
-        <v>46142.98958333334</v>
+        <v>46144.98958333334</v>
       </c>
       <c r="B289">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B290">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46145.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46145.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46145.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46145.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46145.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46145.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46145.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46145.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46145.09375</v>
+      </c>
+      <c r="B299">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46145.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46145.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46145.125</v>
+      </c>
+      <c r="B302">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46145.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46145.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46145.15625</v>
+      </c>
+      <c r="B305">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46145.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46145.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46145.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46145.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46145.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46145.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46145.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46145.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46145.25</v>
+      </c>
+      <c r="B314">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46145.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46145.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46145.28125</v>
+      </c>
+      <c r="B317">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46145.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46145.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46145.3125</v>
+      </c>
+      <c r="B320">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46145.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46145.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46145.34375</v>
+      </c>
+      <c r="B323">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46145.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46145.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46145.375</v>
+      </c>
+      <c r="B326">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46145.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46145.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46145.40625</v>
+      </c>
+      <c r="B329">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46145.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46145.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46145.4375</v>
+      </c>
+      <c r="B332">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46145.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46145.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46145.46875</v>
+      </c>
+      <c r="B335">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46145.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46145.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46145.5</v>
+      </c>
+      <c r="B338">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46145.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46145.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46145.53125</v>
+      </c>
+      <c r="B341">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46145.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46145.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46145.5625</v>
+      </c>
+      <c r="B344">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46145.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46145.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46145.59375</v>
+      </c>
+      <c r="B347">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46145.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46145.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46145.625</v>
+      </c>
+      <c r="B350">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46145.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46145.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46145.65625</v>
+      </c>
+      <c r="B353">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46145.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46145.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46145.6875</v>
+      </c>
+      <c r="B356">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46145.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46145.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46145.71875</v>
+      </c>
+      <c r="B359">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46145.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46145.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46145.75</v>
+      </c>
+      <c r="B362">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46145.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46145.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46145.78125</v>
+      </c>
+      <c r="B365">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46145.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46145.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46145.8125</v>
+      </c>
+      <c r="B368">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46145.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46145.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46145.84375</v>
+      </c>
+      <c r="B371">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46145.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46145.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46145.875</v>
+      </c>
+      <c r="B374">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46145.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46145.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46145.90625</v>
+      </c>
+      <c r="B377">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46145.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46145.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46145.9375</v>
+      </c>
+      <c r="B380">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46145.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46145.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46145.96875</v>
+      </c>
+      <c r="B383">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46145.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46145.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B386">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46146.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46146.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46146.03125</v>
+      </c>
+      <c r="B389">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46146.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46146.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46146.0625</v>
+      </c>
+      <c r="B392">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46146.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46146.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46146.09375</v>
+      </c>
+      <c r="B395">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46146.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46146.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46146.125</v>
+      </c>
+      <c r="B398">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46146.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46146.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46146.15625</v>
+      </c>
+      <c r="B401">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46146.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46146.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46146.1875</v>
+      </c>
+      <c r="B404">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46146.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46146.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46146.21875</v>
+      </c>
+      <c r="B407">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46146.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46146.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46146.25</v>
+      </c>
+      <c r="B410">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46146.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46146.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46146.28125</v>
+      </c>
+      <c r="B413">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46146.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46146.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46146.3125</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46146.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46146.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46146.34375</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46146.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46146.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46146.375</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46146.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46146.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46146.40625</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46146.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46146.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46146.4375</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46146.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46146.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46146.46875</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46146.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46146.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46146.5</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46146.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46146.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46146.53125</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46146.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46146.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46146.5625</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46146.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46146.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46146.59375</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46146.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46146.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46146.625</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46146.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46146.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46146.65625</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46146.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46146.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46146.6875</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46146.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46146.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46146.71875</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46146.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46146.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46146.75</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46146.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46146.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46146.78125</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46146.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46146.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46146.8125</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46146.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46146.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46146.84375</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46146.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46146.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46146.875</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46146.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46146.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46146.90625</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46146.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46146.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46146.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46146.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46146.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46146.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46146.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46146.98958333334</v>
+      </c>
+      <c r="B481">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,839 +394,839 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>890</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
-        <v>698</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
-        <v>616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
-        <v>629</v>
+        <v>708</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
-        <v>658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
-        <v>665</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
-        <v>674</v>
+        <v>684</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
-        <v>646</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>641</v>
+        <v>702</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
-        <v>652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
-        <v>639</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
-        <v>646</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>696</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>819</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>835</v>
+        <v>681</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>848</v>
+        <v>688</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>894</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>900</v>
+        <v>748</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>960</v>
+        <v>754</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>972</v>
+        <v>755</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>1082</v>
+        <v>790</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>1137</v>
+        <v>788</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>1252</v>
+        <v>783</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>1247</v>
+        <v>793</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>833</v>
+        <v>823</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>809</v>
+        <v>824</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>792</v>
+        <v>840</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>808</v>
+        <v>835</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>794</v>
+        <v>759</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>792</v>
+        <v>763</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>862</v>
+        <v>766</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>840</v>
+        <v>767</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>863</v>
+        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>860</v>
+        <v>770</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>859</v>
+        <v>766</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>855</v>
+        <v>756</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>642</v>
+        <v>814</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>630</v>
+        <v>817</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>637</v>
+        <v>815</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>818</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>523</v>
+        <v>770</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>515</v>
+        <v>765</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>443</v>
+        <v>763</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>438</v>
+        <v>764</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>320</v>
+        <v>745</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>167</v>
+        <v>744</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>118</v>
+        <v>746</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>75</v>
+        <v>741</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>74</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>75</v>
+        <v>751</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>82</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>105</v>
+        <v>771</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>104</v>
+        <v>773</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>117</v>
+        <v>777</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>829</v>
+        <v>758</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>869</v>
+        <v>760</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>979</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>1029</v>
+        <v>874</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>872</v>
+        <v>787</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>828</v>
+        <v>803</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>839</v>
+        <v>813</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>1003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>1025</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>978</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>1016</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>1020</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>1018</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>992</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>990</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>997</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>990</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>949</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>950</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>967</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>966</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>860</v>
+        <v>991</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
-        <v>853</v>
+        <v>982</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>827</v>
+        <v>979</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>829</v>
+        <v>967</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>748</v>
+        <v>929</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>752</v>
+        <v>920</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>741</v>
+        <v>917</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>758</v>
+        <v>923</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>574</v>
+        <v>643</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
-        <v>567</v>
+        <v>627</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
-        <v>565</v>
+        <v>623</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
-        <v>562</v>
+        <v>616</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>639</v>
+        <v>663</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B99">
-        <v>648</v>
+        <v>656</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B100">
-        <v>636</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B102">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>647</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
-        <v>644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>653</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,39 +1234,39 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B108">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B109">
-        <v>645</v>
+        <v>655</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>712</v>
+        <v>659</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,143 +1274,143 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B112">
-        <v>713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
-        <v>714</v>
+        <v>660</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B114">
-        <v>735</v>
+        <v>693</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B115">
-        <v>736</v>
+        <v>691</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>739</v>
+        <v>682</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B117">
-        <v>745</v>
+        <v>706</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B118">
-        <v>817</v>
+        <v>756</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>820</v>
+        <v>759</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B120">
-        <v>819</v>
+        <v>755</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B121">
-        <v>820</v>
+        <v>750</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>909</v>
+        <v>854</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B123">
-        <v>893</v>
+        <v>860</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B124">
-        <v>875</v>
+        <v>861</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>876</v>
+        <v>862</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B126">
-        <v>777</v>
+        <v>868</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>872</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>867</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,87 +394,87 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>719</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>716</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>708</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>701</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>684</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>701</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>702</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,343 +482,343 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>700</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>694</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>692</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>700</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>696</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>681</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>688</v>
+        <v>530</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>747</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>748</v>
+        <v>575</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>754</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>755</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>790</v>
+        <v>711</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>788</v>
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>793</v>
+        <v>735</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>823</v>
+        <v>717</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>824</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>840</v>
+        <v>728</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>835</v>
+        <v>720</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>759</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>763</v>
+        <v>629</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>766</v>
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>767</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>777</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>770</v>
+        <v>621</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>766</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>814</v>
+        <v>521</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>817</v>
+        <v>522</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>815</v>
+        <v>523</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>770</v>
+        <v>612</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>765</v>
+        <v>635</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>763</v>
+        <v>641</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>764</v>
+        <v>643</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>745</v>
+        <v>638</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>744</v>
+        <v>636</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>746</v>
+        <v>640</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>741</v>
+        <v>625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>750</v>
+        <v>616</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,447 +826,447 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>751</v>
+        <v>603</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>771</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>773</v>
+        <v>585</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>777</v>
+        <v>566</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>569</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>758</v>
+        <v>573</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>760</v>
+        <v>583</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>571</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>814</v>
+        <v>587</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>874</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>787</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>803</v>
+        <v>547</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>813</v>
+        <v>558</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>1022</v>
+        <v>771</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>1027</v>
+        <v>815</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>879</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>1032</v>
+        <v>935</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>1106</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>1122</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>1113</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>1115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>1134</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>1135</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>1140</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>1152</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>1083</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>1078</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>1081</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>1078</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>991</v>
+        <v>970</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>982</v>
+        <v>969</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>979</v>
+        <v>966</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>967</v>
+        <v>953</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>929</v>
+        <v>906</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>920</v>
+        <v>907</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>917</v>
+        <v>909</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>923</v>
+        <v>911</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>643</v>
+        <v>746</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>627</v>
+        <v>732</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>623</v>
+        <v>751</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>616</v>
+        <v>750</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>663</v>
+        <v>604</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
-        <v>656</v>
+        <v>599</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
-        <v>655</v>
+        <v>595</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
-        <v>645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
-        <v>651</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
-        <v>647</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>577</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
-        <v>653</v>
+        <v>566</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
-        <v>646</v>
+        <v>570</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
-        <v>648</v>
+        <v>564</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
-        <v>655</v>
+        <v>528</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
-        <v>659</v>
+        <v>530</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,207 +1274,207 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>559</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
-        <v>660</v>
+        <v>581</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>693</v>
+        <v>637</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>691</v>
+        <v>650</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>682</v>
+        <v>634</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>706</v>
+        <v>639</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>756</v>
+        <v>686</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>759</v>
+        <v>688</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>750</v>
+        <v>691</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>854</v>
+        <v>711</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>860</v>
+        <v>759</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>861</v>
+        <v>750</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>862</v>
+        <v>749</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>868</v>
+        <v>745</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>872</v>
+        <v>733</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>867</v>
+        <v>731</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>644</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>723</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>782</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>826</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>804</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,23 +1482,23 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>914</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>672</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,879 +394,879 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>587</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>583</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>581</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>582</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>572</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>567</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>568</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>505</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>504</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>506</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>507</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>506</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>517</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>656</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>519</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>530</v>
+        <v>668</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>577</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>575</v>
+        <v>713</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>558</v>
+        <v>708</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>579</v>
+        <v>719</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>711</v>
+        <v>782</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>706</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>792</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>735</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>717</v>
+        <v>764</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>718</v>
+        <v>763</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>720</v>
+        <v>761</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>640</v>
+        <v>738</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>629</v>
+        <v>735</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>636</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>633</v>
+        <v>721</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>611</v>
+        <v>689</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>621</v>
+        <v>684</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>606</v>
+        <v>692</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>683</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>521</v>
+        <v>613</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>522</v>
+        <v>611</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>523</v>
+        <v>604</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>635</v>
+        <v>595</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>641</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>643</v>
+        <v>595</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>638</v>
+        <v>587</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>636</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>640</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>625</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>616</v>
+        <v>588</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>583</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>603</v>
+        <v>579</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>582</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>585</v>
+        <v>660</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>566</v>
+        <v>661</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>569</v>
+        <v>662</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>573</v>
+        <v>634</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>583</v>
+        <v>622</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>571</v>
+        <v>625</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>587</v>
+        <v>644</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>545</v>
+        <v>747</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>539</v>
+        <v>755</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>547</v>
+        <v>754</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>558</v>
+        <v>794</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>771</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>815</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>879</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>935</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>1049</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>1052</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>1057</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>1060</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>1066</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>1062</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>1057</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>1039</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>1049</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>1046</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>1045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>970</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>969</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>966</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>953</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>906</v>
+        <v>828</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>907</v>
+        <v>801</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>909</v>
+        <v>804</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>911</v>
+        <v>786</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>751</v>
+        <v>742</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>604</v>
+        <v>672</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>599</v>
+        <v>653</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>595</v>
+        <v>649</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>643</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>584</v>
+        <v>618</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>581</v>
+        <v>614</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>577</v>
+        <v>615</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>566</v>
+        <v>617</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>572</v>
+        <v>603</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>570</v>
+        <v>601</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>564</v>
+        <v>602</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>528</v>
+        <v>603</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>530</v>
+        <v>612</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,71 +1274,71 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>559</v>
+        <v>613</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>581</v>
+        <v>621</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>634</v>
+        <v>667</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>639</v>
+        <v>679</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>686</v>
+        <v>751</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>688</v>
+        <v>758</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1346,159 +1346,159 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>691</v>
+        <v>762</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>711</v>
+        <v>808</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>759</v>
+        <v>803</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>750</v>
+        <v>799</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>749</v>
+        <v>803</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>745</v>
+        <v>793</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>733</v>
+        <v>808</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>731</v>
+        <v>798</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>734</v>
+        <v>792</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>597</v>
+        <v>734</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>644</v>
+        <v>755</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>723</v>
+        <v>756</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>748</v>
+        <v>713</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>782</v>
+        <v>625</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>826</v>
+        <v>617</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>804</v>
+        <v>619</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>615</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>914</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,1119 +394,1119 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
-        <v>634</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
-        <v>636</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
-        <v>639</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>639</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>640</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>636</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>640</v>
+        <v>603</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>639</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>637</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>632</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>638</v>
+        <v>613</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>645</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>668</v>
+        <v>679</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>718</v>
+        <v>751</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>713</v>
+        <v>758</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>719</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>782</v>
+        <v>808</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>793</v>
+        <v>803</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>792</v>
+        <v>799</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>795</v>
+        <v>803</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>764</v>
+        <v>793</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>763</v>
+        <v>808</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>798</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>761</v>
+        <v>792</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>735</v>
+        <v>755</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>732</v>
+        <v>756</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>721</v>
+        <v>713</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>689</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>684</v>
+        <v>617</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>692</v>
+        <v>619</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>683</v>
+        <v>615</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>613</v>
+        <v>562</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>611</v>
+        <v>557</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>604</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>607</v>
+        <v>575</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>608</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>595</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>609</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>595</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>587</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>582</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>578</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>600</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>588</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>583</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>589</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>649</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>660</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>661</v>
+        <v>284</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>662</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>634</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>622</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>644</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>747</v>
+        <v>591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>755</v>
+        <v>592</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>754</v>
+        <v>581</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>794</v>
+        <v>564</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>1053</v>
+        <v>792</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>1045</v>
+        <v>888</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>1046</v>
+        <v>940</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>1047</v>
+        <v>952</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>1080</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>1096</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>1098</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>1111</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>1149</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>1164</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>1163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>1172</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>1150</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>1148</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>1145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>1025</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>1019</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>1016</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>1014</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>828</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>801</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>804</v>
+        <v>917</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>786</v>
+        <v>903</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>750</v>
+        <v>701</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
-        <v>733</v>
+        <v>697</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>742</v>
+        <v>698</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>696</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
-        <v>653</v>
+        <v>662</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
-        <v>649</v>
+        <v>661</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
-        <v>643</v>
+        <v>654</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
-        <v>618</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
-        <v>614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
-        <v>615</v>
+        <v>594</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
-        <v>617</v>
+        <v>598</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
-        <v>603</v>
+        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
-        <v>601</v>
+        <v>586</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
-        <v>602</v>
+        <v>588</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
-        <v>603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>612</v>
+        <v>633</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>632</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
-        <v>613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>621</v>
+        <v>633</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>645</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>667</v>
+        <v>647</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>679</v>
+        <v>669</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>751</v>
+        <v>722</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>758</v>
+        <v>726</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>724</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>762</v>
+        <v>727</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>808</v>
+        <v>722</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>799</v>
+        <v>715</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>803</v>
+        <v>706</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>793</v>
+        <v>698</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>808</v>
+        <v>680</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>798</v>
+        <v>686</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>792</v>
+        <v>675</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>734</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>755</v>
+        <v>573</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>756</v>
+        <v>574</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>713</v>
+        <v>572</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>625</v>
+        <v>576</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>617</v>
+        <v>551</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>619</v>
+        <v>562</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>615</v>
+        <v>595</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>562</v>
+        <v>544</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>477</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,439 +394,439 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>672</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>653</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
-        <v>649</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
-        <v>643</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>618</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>614</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>617</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>603</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>601</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>603</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>612</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>613</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>621</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>665</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>667</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>679</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>751</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>758</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>762</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>808</v>
+        <v>627</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>803</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>799</v>
+        <v>631</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>803</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>793</v>
+        <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>808</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>798</v>
+        <v>652</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>792</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>734</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>755</v>
+        <v>592</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>756</v>
+        <v>664</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>713</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>625</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>617</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>619</v>
+        <v>430</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>615</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>562</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>557</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>582</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>575</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>476</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>479</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>505</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>527</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>330</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>301</v>
+        <v>429</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>296</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,695 +834,695 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>285</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>269</v>
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>275</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>287</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>367</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>382</v>
+        <v>474</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>391</v>
+        <v>451</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>591</v>
+        <v>478</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>592</v>
+        <v>488</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>581</v>
+        <v>493</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>564</v>
+        <v>522</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>792</v>
+        <v>942</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>888</v>
+        <v>903</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>940</v>
+        <v>889</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>952</v>
+        <v>925</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>1045</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>1052</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>1050</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>1069</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>1070</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>1069</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>1078</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>1104</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>1092</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>1052</v>
+        <v>880</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>1050</v>
+        <v>878</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>1167</v>
+        <v>876</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>1161</v>
+        <v>858</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>1055</v>
+        <v>617</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>1050</v>
+        <v>615</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>903</v>
+        <v>609</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>701</v>
+        <v>412</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>697</v>
+        <v>402</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
-        <v>696</v>
+        <v>399</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>665</v>
+        <v>448</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
-        <v>662</v>
+        <v>447</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
-        <v>661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
-        <v>654</v>
+        <v>446</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
-        <v>600</v>
+        <v>418</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>416</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
-        <v>594</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
-        <v>598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
-        <v>590</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
-        <v>586</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
-        <v>588</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
-        <v>633</v>
+        <v>392</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
-        <v>632</v>
+        <v>390</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>633</v>
+        <v>390</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>660</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>645</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>669</v>
+        <v>404</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>722</v>
+        <v>507</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>726</v>
+        <v>505</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>724</v>
+        <v>506</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>727</v>
+        <v>520</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>722</v>
+        <v>615</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>638</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>715</v>
+        <v>635</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>706</v>
+        <v>600</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>698</v>
+        <v>571</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>680</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>686</v>
+        <v>585</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>611</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>573</v>
+        <v>456</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>574</v>
+        <v>468</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>572</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>576</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>551</v>
+        <v>421</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>562</v>
+        <v>457</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>595</v>
+        <v>451</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>544</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>482</v>
+        <v>288</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>477</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>189</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,47 +1530,47 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>175</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,759 +394,759 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>503</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>505</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>504</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>446</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>447</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>448</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>477</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>446</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>470</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>479</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>503</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>481</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>569</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>572</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>574</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>607</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>627</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>618</v>
+        <v>638</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>602</v>
+        <v>571</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>612</v>
+        <v>578</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>652</v>
+        <v>585</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>621</v>
+        <v>605</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>601</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>592</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>664</v>
+        <v>468</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>660</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>461</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>449</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>430</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>321</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>209</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>199</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>216</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>309</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>304</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>297</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>282</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>293</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>429</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>430</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>431</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>332</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>321</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>291</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>264</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>444</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>474</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>440</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>451</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>478</v>
+        <v>457</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>488</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>493</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>522</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>942</v>
+        <v>688</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>903</v>
+        <v>680</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>889</v>
+        <v>681</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>925</v>
+        <v>701</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>1197</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>1211</v>
+        <v>941</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>1208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>1239</v>
+        <v>949</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>1275</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>1283</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>1281</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>1276</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>1097</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>1089</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>1075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>1072</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>880</v>
+        <v>918</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>878</v>
+        <v>909</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>858</v>
+        <v>906</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>617</v>
+        <v>713</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>615</v>
+        <v>705</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>609</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,31 +1154,31 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>399</v>
+        <v>438</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>448</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
-        <v>447</v>
+        <v>320</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,391 +1186,391 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
-        <v>446</v>
+        <v>321</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
-        <v>418</v>
+        <v>457</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
-        <v>416</v>
+        <v>460</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
-        <v>415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>459</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
-        <v>399</v>
+        <v>454</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
-        <v>392</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>398</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>392</v>
+        <v>468</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>390</v>
+        <v>469</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>391</v>
+        <v>476</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>390</v>
+        <v>478</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>395</v>
+        <v>515</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>393</v>
+        <v>513</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>512</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>404</v>
+        <v>527</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>507</v>
+        <v>595</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>505</v>
+        <v>592</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>506</v>
+        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>520</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>615</v>
+        <v>717</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>638</v>
+        <v>724</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>635</v>
+        <v>725</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>600</v>
+        <v>732</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>578</v>
+        <v>566</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>585</v>
+        <v>569</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>605</v>
+        <v>638</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>467</v>
+        <v>543</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>456</v>
+        <v>541</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>468</v>
+        <v>492</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>457</v>
+        <v>425</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>190</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>288</v>
+        <v>411</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>276</v>
+        <v>414</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>189</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>156</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,23 +394,23 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>447</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,639 +418,639 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>446</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>418</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>416</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>399</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>392</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>398</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>392</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>390</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>391</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>390</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>395</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>393</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>404</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>507</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>505</v>
+        <v>592</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>506</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>520</v>
+        <v>619</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>615</v>
+        <v>717</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>638</v>
+        <v>724</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>635</v>
+        <v>725</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>600</v>
+        <v>732</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>578</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>585</v>
+        <v>569</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>605</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>467</v>
+        <v>543</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>456</v>
+        <v>541</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>468</v>
+        <v>492</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>457</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>190</v>
+        <v>413</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>288</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>276</v>
+        <v>414</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>189</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>156</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>207</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>334</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>322</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>387</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>386</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>181</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>296</v>
+        <v>267</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>457</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>462</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>467</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>484</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>688</v>
+        <v>819</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>680</v>
+        <v>850</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>681</v>
+        <v>851</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>701</v>
+        <v>868</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>1005</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>941</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>949</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>1104</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>1081</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>1077</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,159 +1058,159 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>1084</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>909</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>713</v>
+        <v>775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>705</v>
+        <v>765</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>716</v>
+        <v>779</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>710</v>
+        <v>760</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>447</v>
+        <v>509</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>440</v>
+        <v>492</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>438</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>328</v>
+        <v>414</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
-        <v>320</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
-        <v>321</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,391 +1218,391 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>478</v>
+        <v>452</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>515</v>
+        <v>450</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>513</v>
+        <v>448</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>527</v>
+        <v>459</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>595</v>
+        <v>463</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>592</v>
+        <v>461</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>591</v>
+        <v>465</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>619</v>
+        <v>469</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>717</v>
+        <v>505</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>724</v>
+        <v>504</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>725</v>
+        <v>510</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>732</v>
+        <v>541</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>575</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>566</v>
+        <v>450</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>569</v>
+        <v>503</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>638</v>
+        <v>496</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>543</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>541</v>
+        <v>391</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>478</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>432</v>
+        <v>334</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>429</v>
+        <v>340</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>425</v>
+        <v>284</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>413</v>
+        <v>147</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>411</v>
+        <v>141</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>414</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>411</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>216</v>
+        <v>191</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>194</v>
+        <v>149</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>192</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,55 +1610,55 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>178</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,265 +1666,1801 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>382</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>394</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>491</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>925</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>966</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>971</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>969</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>921</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>917</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>924</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>922</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>857</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>881</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>890</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>889</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>781</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>987</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>934</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>964</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>969</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>962</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,903 +394,903 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>489</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>499</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>482</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>513</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>518</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>520</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>512</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>475</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>475</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>478</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>458</v>
+        <v>607</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>440</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>479</v>
+        <v>630</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>493</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>492</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>501</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>525</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>517</v>
+        <v>581</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>514</v>
+        <v>723</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>528</v>
+        <v>735</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>614</v>
+        <v>709</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>619</v>
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>609</v>
+        <v>708</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>594</v>
+        <v>712</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>537</v>
+        <v>655</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>504</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>681</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>505</v>
+        <v>668</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>235</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>203</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>198</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>195</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>141</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>170</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>174</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>173</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>107</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>106</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>103</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>124</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>178</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>235</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>256</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>279</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>259</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>234</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>247</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>252</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>254</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>237</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>179</v>
+        <v>265</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>219</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>198</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>210</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>314</v>
+        <v>416</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>336</v>
+        <v>427</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>337</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>361</v>
+        <v>471</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>495</v>
+        <v>892</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>498</v>
+        <v>905</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>502</v>
+        <v>906</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>533</v>
+        <v>928</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>1066</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>1029</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>1047</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>1079</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>1076</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>1083</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>1104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>1118</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>1106</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>1116</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>1118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>1115</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>984</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>977</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>979</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>969</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>750</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>727</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>724</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>729</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>667</v>
+        <v>773</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>659</v>
+        <v>767</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>662</v>
+        <v>766</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>763</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>671</v>
+        <v>654</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>669</v>
+        <v>651</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>646</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
-        <v>609</v>
+        <v>669</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
-        <v>612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
-        <v>611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
-        <v>612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
-        <v>594</v>
+        <v>671</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
-        <v>593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>666</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
-        <v>582</v>
+        <v>668</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
-        <v>608</v>
+        <v>673</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
-        <v>607</v>
+        <v>672</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>630</v>
+        <v>673</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
         <v>674</v>
@@ -1298,159 +1298,159 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>534</v>
+        <v>673</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>519</v>
+        <v>670</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>533</v>
+        <v>684</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>570</v>
+        <v>774</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>581</v>
+        <v>777</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>723</v>
+        <v>773</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>735</v>
+        <v>777</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>709</v>
+        <v>865</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>706</v>
+        <v>868</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>708</v>
+        <v>869</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>712</v>
+        <v>871</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>655</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>658</v>
+        <v>531</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>681</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>668</v>
+        <v>531</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>410</v>
+        <v>574</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,135 +394,135 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>671</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>669</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>609</v>
+        <v>669</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>594</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>582</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>608</v>
+        <v>673</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>607</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>630</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
         <v>674</v>
@@ -530,919 +530,919 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>534</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>519</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>533</v>
+        <v>684</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>570</v>
+        <v>774</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>581</v>
+        <v>777</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>723</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>735</v>
+        <v>777</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>709</v>
+        <v>865</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>706</v>
+        <v>868</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>708</v>
+        <v>869</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>712</v>
+        <v>871</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>655</v>
+        <v>559</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>658</v>
+        <v>531</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>681</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>668</v>
+        <v>531</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>410</v>
+        <v>574</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>408</v>
+        <v>558</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>407</v>
+        <v>559</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>363</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>351</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>348</v>
+        <v>493</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>347</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>174</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>173</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>145</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>152</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>148</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>167</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>265</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>277</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>269</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>273</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>416</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>427</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>430</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>892</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>905</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>906</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>928</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>1211</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>1210</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>1225</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>1223</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>1256</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>1272</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>1271</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>1240</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>1237</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>1239</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>1141</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>1136</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>1132</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>1155</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>1081</v>
+        <v>977</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1085</v>
+        <v>973</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>1023</v>
+        <v>971</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>1025</v>
+        <v>977</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>773</v>
+        <v>660</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>767</v>
+        <v>650</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>766</v>
+        <v>648</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>763</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>654</v>
+        <v>544</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>651</v>
+        <v>542</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>646</v>
+        <v>546</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>649</v>
+        <v>553</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>865</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>940</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>671</v>
+        <v>926</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>950</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>666</v>
+        <v>956</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>668</v>
+        <v>976</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>673</v>
+        <v>959</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>957</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>673</v>
+        <v>955</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>674</v>
+        <v>966</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>673</v>
+        <v>978</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>670</v>
+        <v>839</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>684</v>
+        <v>706</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>774</v>
+        <v>746</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>777</v>
+        <v>741</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>773</v>
+        <v>745</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>777</v>
+        <v>752</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>865</v>
+        <v>696</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>868</v>
+        <v>695</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>871</v>
+        <v>885</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>559</v>
+        <v>877</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>531</v>
+        <v>864</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>528</v>
+        <v>703</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>531</v>
+        <v>668</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>574</v>
+        <v>653</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>645</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>639</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>654</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>651</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>646</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>649</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>671</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>666</v>
+        <v>956</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>668</v>
+        <v>976</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>673</v>
+        <v>959</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>673</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>674</v>
+        <v>966</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>673</v>
+        <v>978</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>670</v>
+        <v>839</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>684</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>774</v>
+        <v>746</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>777</v>
+        <v>741</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>773</v>
+        <v>745</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>777</v>
+        <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>865</v>
+        <v>696</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>868</v>
+        <v>695</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>871</v>
+        <v>885</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>559</v>
+        <v>877</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>531</v>
+        <v>864</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>528</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>531</v>
+        <v>668</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>574</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>645</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>558</v>
+        <v>639</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>559</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>502</v>
+        <v>557</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>500</v>
+        <v>553</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>493</v>
+        <v>548</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>489</v>
+        <v>549</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>169</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>274</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>279</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>275</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>265</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>184</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>178</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>175</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>181</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>370</v>
+        <v>419</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>378</v>
+        <v>434</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>380</v>
+        <v>539</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>459</v>
+        <v>641</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1090</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>1117</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>1127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>1150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>1246</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>1260</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>1250</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>1246</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>1294</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>1306</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>1317</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>1315</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>1263</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>1256</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>1251</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>1254</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>1105</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>1099</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>1102</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>1094</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>977</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>973</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>971</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>977</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
         <v>660</v>
@@ -1138,311 +1138,311 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>650</v>
+        <v>661</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>544</v>
+        <v>624</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>542</v>
+        <v>625</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>546</v>
+        <v>630</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>553</v>
+        <v>623</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>865</v>
+        <v>622</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>940</v>
+        <v>603</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>926</v>
+        <v>585</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>950</v>
+        <v>577</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>956</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>976</v>
+        <v>601</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>959</v>
+        <v>620</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>608</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>957</v>
+        <v>602</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>955</v>
+        <v>617</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>966</v>
+        <v>643</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>839</v>
+        <v>641</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>706</v>
+        <v>644</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>741</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>745</v>
+        <v>638</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>752</v>
+        <v>642</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>876</v>
+        <v>698</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>885</v>
+        <v>692</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>877</v>
+        <v>653</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>864</v>
+        <v>645</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>703</v>
+        <v>643</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>668</v>
+        <v>639</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>653</v>
+        <v>508</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>645</v>
+        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>639</v>
+        <v>488</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,423 +394,423 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B2">
-        <v>544</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B3">
-        <v>542</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B4">
-        <v>546</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B5">
-        <v>553</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B6">
-        <v>663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B7">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B8">
-        <v>865</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B9">
-        <v>940</v>
+        <v>603</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B10">
-        <v>926</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B11">
-        <v>950</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B12">
-        <v>956</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B13">
-        <v>976</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B14">
-        <v>959</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B16">
-        <v>957</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B17">
-        <v>955</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B18">
-        <v>966</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B19">
-        <v>978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B20">
-        <v>839</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B21">
-        <v>706</v>
+        <v>644</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B22">
-        <v>746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B23">
-        <v>741</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B24">
-        <v>745</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B25">
-        <v>752</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B26">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B27">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B28">
-        <v>876</v>
+        <v>698</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B29">
-        <v>885</v>
+        <v>692</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B30">
-        <v>877</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B31">
-        <v>864</v>
+        <v>645</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B32">
-        <v>703</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B33">
-        <v>668</v>
+        <v>639</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B34">
-        <v>653</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B35">
-        <v>645</v>
+        <v>491</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B36">
-        <v>639</v>
+        <v>488</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B37">
-        <v>640</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B38">
-        <v>557</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B39">
-        <v>553</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B40">
-        <v>548</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B41">
-        <v>549</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B42">
-        <v>212</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B43">
-        <v>187</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B44">
-        <v>202</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B45">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B46">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B47">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B48">
-        <v>147</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B50">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B51">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B52">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B53">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B54">
         <v>121</v>
@@ -818,327 +818,327 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B55">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B56">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B57">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B58">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B59">
-        <v>206</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B60">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B61">
-        <v>177</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B62">
-        <v>245</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B63">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B64">
-        <v>253</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B65">
-        <v>259</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B66">
-        <v>419</v>
+        <v>589</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B67">
-        <v>434</v>
+        <v>604</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B68">
-        <v>539</v>
+        <v>602</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B69">
-        <v>641</v>
+        <v>614</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B70">
-        <v>1159</v>
+        <v>876</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B71">
-        <v>1186</v>
+        <v>880</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>881</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>898</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B74">
-        <v>1328</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B75">
-        <v>1353</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B76">
-        <v>1356</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B77">
-        <v>1364</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B78">
-        <v>1428</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B79">
-        <v>1443</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B80">
-        <v>1441</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B81">
-        <v>1448</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B82">
-        <v>1370</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B83">
-        <v>1401</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B84">
-        <v>1408</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B85">
-        <v>1406</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B86">
-        <v>1335</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B87">
-        <v>1312</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B88">
-        <v>1305</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B89">
-        <v>1309</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B90">
-        <v>1060</v>
+        <v>879</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B91">
-        <v>1044</v>
+        <v>873</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B92">
-        <v>1034</v>
+        <v>859</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B93">
-        <v>1029</v>
+        <v>857</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B94">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B95">
         <v>647</v>
@@ -1146,207 +1146,207 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B96">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B97">
-        <v>661</v>
+        <v>648</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B98">
-        <v>624</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46171.01041666666</v>
+        <v>46172.01041666666</v>
       </c>
       <c r="B99">
-        <v>625</v>
+        <v>564</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46171.02083333334</v>
+        <v>46172.02083333334</v>
       </c>
       <c r="B100">
-        <v>630</v>
+        <v>563</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46171.03125</v>
+        <v>46172.03125</v>
       </c>
       <c r="B101">
-        <v>623</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46171.04166666666</v>
+        <v>46172.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>629</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46171.05208333334</v>
+        <v>46172.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>628</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46171.0625</v>
+        <v>46172.0625</v>
       </c>
       <c r="B104">
-        <v>622</v>
+        <v>631</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46171.07291666666</v>
+        <v>46172.07291666666</v>
       </c>
       <c r="B105">
-        <v>603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46171.08333333334</v>
+        <v>46172.08333333334</v>
       </c>
       <c r="B106">
-        <v>585</v>
+        <v>615</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46171.09375</v>
+        <v>46172.09375</v>
       </c>
       <c r="B107">
-        <v>577</v>
+        <v>627</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46171.10416666666</v>
+        <v>46172.10416666666</v>
       </c>
       <c r="B108">
-        <v>578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46171.11458333334</v>
+        <v>46172.11458333334</v>
       </c>
       <c r="B109">
-        <v>601</v>
+        <v>633</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46171.125</v>
+        <v>46172.125</v>
       </c>
       <c r="B110">
-        <v>620</v>
+        <v>634</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46171.13541666666</v>
+        <v>46172.13541666666</v>
       </c>
       <c r="B111">
-        <v>608</v>
+        <v>629</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46171.14583333334</v>
+        <v>46172.14583333334</v>
       </c>
       <c r="B112">
-        <v>602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46171.15625</v>
+        <v>46172.15625</v>
       </c>
       <c r="B113">
-        <v>617</v>
+        <v>630</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46171.16666666666</v>
+        <v>46172.16666666666</v>
       </c>
       <c r="B114">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46171.17708333334</v>
+        <v>46172.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>643</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46171.1875</v>
+        <v>46172.1875</v>
       </c>
       <c r="B116">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46171.19791666666</v>
+        <v>46172.19791666666</v>
       </c>
       <c r="B117">
-        <v>644</v>
+        <v>659</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46171.20833333334</v>
+        <v>46172.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>643</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46171.21875</v>
+        <v>46172.21875</v>
       </c>
       <c r="B119">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46171.22916666666</v>
+        <v>46172.22916666666</v>
       </c>
       <c r="B120">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46171.23958333334</v>
+        <v>46172.23958333334</v>
       </c>
       <c r="B121">
         <v>642</v>
@@ -1354,471 +1354,471 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46171.25</v>
+        <v>46172.25</v>
       </c>
       <c r="B122">
-        <v>692</v>
+        <v>641</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46171.26041666666</v>
+        <v>46172.26041666666</v>
       </c>
       <c r="B123">
-        <v>699</v>
+        <v>623</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46171.27083333334</v>
+        <v>46172.27083333334</v>
       </c>
       <c r="B124">
-        <v>698</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46171.28125</v>
+        <v>46172.28125</v>
       </c>
       <c r="B125">
-        <v>692</v>
+        <v>636</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46171.29166666666</v>
+        <v>46172.29166666666</v>
       </c>
       <c r="B126">
-        <v>653</v>
+        <v>590</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46171.30208333334</v>
+        <v>46172.30208333334</v>
       </c>
       <c r="B127">
-        <v>645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46171.3125</v>
+        <v>46172.3125</v>
       </c>
       <c r="B128">
-        <v>643</v>
+        <v>571</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46171.32291666666</v>
+        <v>46172.32291666666</v>
       </c>
       <c r="B129">
-        <v>639</v>
+        <v>615</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46171.33333333334</v>
+        <v>46172.33333333334</v>
       </c>
       <c r="B130">
-        <v>508</v>
+        <v>442</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46171.34375</v>
+        <v>46172.34375</v>
       </c>
       <c r="B131">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46171.35416666666</v>
+        <v>46172.35416666666</v>
       </c>
       <c r="B132">
-        <v>488</v>
+        <v>442</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46171.36458333334</v>
+        <v>46172.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46171.375</v>
+        <v>46172.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46171.38541666666</v>
+        <v>46172.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46171.39583333334</v>
+        <v>46172.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46171.40625</v>
+        <v>46172.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46171.41666666666</v>
+        <v>46172.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46171.42708333334</v>
+        <v>46172.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46171.4375</v>
+        <v>46172.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46171.44791666666</v>
+        <v>46172.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>234</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46171.45833333334</v>
+        <v>46172.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46171.46875</v>
+        <v>46172.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>253</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46171.47916666666</v>
+        <v>46172.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46171.48958333334</v>
+        <v>46172.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46171.5</v>
+        <v>46172.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46171.51041666666</v>
+        <v>46172.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46171.52083333334</v>
+        <v>46172.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46171.53125</v>
+        <v>46172.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46171.54166666666</v>
+        <v>46172.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46171.55208333334</v>
+        <v>46172.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46171.5625</v>
+        <v>46172.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46171.57291666666</v>
+        <v>46172.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46171.58333333334</v>
+        <v>46172.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46171.59375</v>
+        <v>46172.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46171.60416666666</v>
+        <v>46172.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>274</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46171.61458333334</v>
+        <v>46172.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46171.625</v>
+        <v>46172.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46171.63541666666</v>
+        <v>46172.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46171.64583333334</v>
+        <v>46172.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46171.65625</v>
+        <v>46172.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46171.66666666666</v>
+        <v>46172.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46171.67708333334</v>
+        <v>46172.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46171.6875</v>
+        <v>46172.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46171.69791666666</v>
+        <v>46172.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46171.70833333334</v>
+        <v>46172.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>454</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46171.71875</v>
+        <v>46172.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>462</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46171.72916666666</v>
+        <v>46172.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>468</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46171.73958333334</v>
+        <v>46172.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46171.75</v>
+        <v>46172.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46171.76041666666</v>
+        <v>46172.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46171.77083333334</v>
+        <v>46172.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46171.78125</v>
+        <v>46172.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46171.79166666666</v>
+        <v>46172.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46171.80208333334</v>
+        <v>46172.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46171.8125</v>
+        <v>46172.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46171.82291666666</v>
+        <v>46172.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46171.83333333334</v>
+        <v>46172.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46171.84375</v>
+        <v>46172.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46171.85416666666</v>
+        <v>46172.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,105 +1826,3177 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46171.86458333334</v>
+        <v>46172.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46171.875</v>
+        <v>46172.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46171.88541666666</v>
+        <v>46172.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46171.89583333334</v>
+        <v>46172.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46171.90625</v>
+        <v>46172.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46171.91666666666</v>
+        <v>46172.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>887</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46171.92708333334</v>
+        <v>46172.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>883</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46171.9375</v>
+        <v>46172.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>884</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46171.94791666666</v>
+        <v>46172.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>878</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46171.95833333334</v>
+        <v>46172.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>753</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46171.96875</v>
+        <v>46172.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>741</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46171.97916666666</v>
+        <v>46172.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>728</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46171.98958333334</v>
+        <v>46172.98958333334</v>
       </c>
       <c r="B193">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B194">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46173.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46173.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46173.03125</v>
+      </c>
+      <c r="B197">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46173.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46173.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46173.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46173.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46173.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46173.09375</v>
+      </c>
+      <c r="B203">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46173.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46173.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46173.125</v>
+      </c>
+      <c r="B206">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46173.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46173.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46173.15625</v>
+      </c>
+      <c r="B209">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46173.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46173.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46173.1875</v>
+      </c>
+      <c r="B212">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46173.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46173.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46173.21875</v>
+      </c>
+      <c r="B215">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46173.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46173.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46173.25</v>
+      </c>
+      <c r="B218">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46173.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46173.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46173.28125</v>
+      </c>
+      <c r="B221">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46173.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46173.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46173.3125</v>
+      </c>
+      <c r="B224">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46173.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46173.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46173.34375</v>
+      </c>
+      <c r="B227">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46173.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46173.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46173.375</v>
+      </c>
+      <c r="B230">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46173.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46173.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46173.40625</v>
+      </c>
+      <c r="B233">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46173.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46173.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46173.4375</v>
+      </c>
+      <c r="B236">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46173.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46173.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46173.46875</v>
+      </c>
+      <c r="B239">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46173.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46173.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46173.5</v>
+      </c>
+      <c r="B242">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46173.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46173.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46173.53125</v>
+      </c>
+      <c r="B245">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46173.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46173.5625</v>
+      </c>
+      <c r="B248">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46173.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46173.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46173.59375</v>
+      </c>
+      <c r="B251">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46173.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46173.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46173.625</v>
+      </c>
+      <c r="B254">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46173.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46173.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46173.65625</v>
+      </c>
+      <c r="B257">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46173.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46173.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46173.6875</v>
+      </c>
+      <c r="B260">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46173.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46173.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46173.71875</v>
+      </c>
+      <c r="B263">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46173.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46173.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46173.75</v>
+      </c>
+      <c r="B266">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46173.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46173.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46173.78125</v>
+      </c>
+      <c r="B269">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46173.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46173.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46173.8125</v>
+      </c>
+      <c r="B272">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46173.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46173.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46173.84375</v>
+      </c>
+      <c r="B275">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46173.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46173.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46173.875</v>
+      </c>
+      <c r="B278">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46173.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46173.90625</v>
+      </c>
+      <c r="B281">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46173.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46173.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46173.9375</v>
+      </c>
+      <c r="B284">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46173.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46173.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46173.96875</v>
+      </c>
+      <c r="B287">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46173.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46173.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B290">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46174.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46174.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46174.03125</v>
+      </c>
+      <c r="B293">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46174.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46174.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46174.0625</v>
+      </c>
+      <c r="B296">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46174.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46174.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46174.09375</v>
+      </c>
+      <c r="B299">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46174.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46174.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46174.125</v>
+      </c>
+      <c r="B302">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46174.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46174.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46174.15625</v>
+      </c>
+      <c r="B305">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46174.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46174.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46174.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46174.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46174.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46174.21875</v>
+      </c>
+      <c r="B311">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46174.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46174.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46174.25</v>
+      </c>
+      <c r="B314">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46174.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46174.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46174.28125</v>
+      </c>
+      <c r="B317">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46174.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46174.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46174.3125</v>
+      </c>
+      <c r="B320">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46174.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46174.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46174.34375</v>
+      </c>
+      <c r="B323">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46174.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46174.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46174.375</v>
+      </c>
+      <c r="B326">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46174.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46174.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46174.40625</v>
+      </c>
+      <c r="B329">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46174.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46174.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46174.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46174.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46174.46875</v>
+      </c>
+      <c r="B335">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46174.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46174.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46174.5</v>
+      </c>
+      <c r="B338">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46174.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46174.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46174.53125</v>
+      </c>
+      <c r="B341">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46174.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46174.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46174.5625</v>
+      </c>
+      <c r="B344">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46174.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46174.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46174.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46174.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46174.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46174.625</v>
+      </c>
+      <c r="B350">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46174.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46174.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46174.65625</v>
+      </c>
+      <c r="B353">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46174.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46174.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46174.6875</v>
+      </c>
+      <c r="B356">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46174.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46174.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46174.71875</v>
+      </c>
+      <c r="B359">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46174.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46174.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46174.75</v>
+      </c>
+      <c r="B362">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46174.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46174.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46174.78125</v>
+      </c>
+      <c r="B365">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46174.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46174.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46174.8125</v>
+      </c>
+      <c r="B368">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46174.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46174.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46174.84375</v>
+      </c>
+      <c r="B371">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46174.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46174.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46174.875</v>
+      </c>
+      <c r="B374">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46174.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46174.90625</v>
+      </c>
+      <c r="B377">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46174.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46174.9375</v>
+      </c>
+      <c r="B380">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46174.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46174.96875</v>
+      </c>
+      <c r="B383">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46174.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46174.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B386">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46175.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46175.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46175.03125</v>
+      </c>
+      <c r="B389">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46175.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46175.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46175.0625</v>
+      </c>
+      <c r="B392">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46175.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46175.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46175.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46175.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46175.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46175.125</v>
+      </c>
+      <c r="B398">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46175.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46175.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46175.15625</v>
+      </c>
+      <c r="B401">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46175.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46175.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46175.1875</v>
+      </c>
+      <c r="B404">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46175.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46175.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46175.21875</v>
+      </c>
+      <c r="B407">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46175.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46175.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46175.25</v>
+      </c>
+      <c r="B410">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46175.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46175.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46175.28125</v>
+      </c>
+      <c r="B413">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46175.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46175.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46175.3125</v>
+      </c>
+      <c r="B416">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46175.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46175.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46175.34375</v>
+      </c>
+      <c r="B419">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46175.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46175.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46175.375</v>
+      </c>
+      <c r="B422">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46175.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46175.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46175.40625</v>
+      </c>
+      <c r="B425">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46175.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46175.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46175.4375</v>
+      </c>
+      <c r="B428">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46175.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46175.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46175.46875</v>
+      </c>
+      <c r="B431">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46175.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46175.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46175.5</v>
+      </c>
+      <c r="B434">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46175.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46175.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46175.53125</v>
+      </c>
+      <c r="B437">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46175.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46175.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46175.5625</v>
+      </c>
+      <c r="B440">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46175.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46175.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46175.59375</v>
+      </c>
+      <c r="B443">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46175.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46175.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46175.625</v>
+      </c>
+      <c r="B446">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46175.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46175.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46175.65625</v>
+      </c>
+      <c r="B449">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46175.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46175.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46175.6875</v>
+      </c>
+      <c r="B452">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46175.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46175.71875</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46175.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46175.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46175.75</v>
+      </c>
+      <c r="B458">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46175.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46175.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46175.78125</v>
+      </c>
+      <c r="B461">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46175.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46175.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46175.8125</v>
+      </c>
+      <c r="B464">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46175.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46175.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46175.84375</v>
+      </c>
+      <c r="B467">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46175.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46175.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46175.875</v>
+      </c>
+      <c r="B470">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46175.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46175.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46175.90625</v>
+      </c>
+      <c r="B473">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46175.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46175.9375</v>
+      </c>
+      <c r="B476">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46175.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46175.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46175.96875</v>
+      </c>
+      <c r="B479">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46175.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46175.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B482">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46176.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46176.03125</v>
+      </c>
+      <c r="B485">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46176.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
+        <v>46176.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
+        <v>46176.0625</v>
+      </c>
+      <c r="B488">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
+        <v>46176.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
+        <v>46176.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
+        <v>46176.09375</v>
+      </c>
+      <c r="B491">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
+        <v>46176.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
+        <v>46176.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
+        <v>46176.125</v>
+      </c>
+      <c r="B494">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
+        <v>46176.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
+        <v>46176.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
+        <v>46176.15625</v>
+      </c>
+      <c r="B497">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
+        <v>46176.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
+        <v>46176.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
+        <v>46176.1875</v>
+      </c>
+      <c r="B500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
+        <v>46176.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="2">
+        <v>46176.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2">
+        <v>46176.21875</v>
+      </c>
+      <c r="B503">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2">
+        <v>46176.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2">
+        <v>46176.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2">
+        <v>46176.25</v>
+      </c>
+      <c r="B506">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2">
+        <v>46176.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="2">
+        <v>46176.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="2">
+        <v>46176.28125</v>
+      </c>
+      <c r="B509">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2">
+        <v>46176.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2">
+        <v>46176.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2">
+        <v>46176.3125</v>
+      </c>
+      <c r="B512">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2">
+        <v>46176.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2">
+        <v>46176.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2">
+        <v>46176.34375</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2">
+        <v>46176.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2">
+        <v>46176.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2">
+        <v>46176.375</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2">
+        <v>46176.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2">
+        <v>46176.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2">
+        <v>46176.40625</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2">
+        <v>46176.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2">
+        <v>46176.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2">
+        <v>46176.4375</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2">
+        <v>46176.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="2">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2">
+        <v>46176.46875</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2">
+        <v>46176.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2">
+        <v>46176.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2">
+        <v>46176.5</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2">
+        <v>46176.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2">
+        <v>46176.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2">
+        <v>46176.53125</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2">
+        <v>46176.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2">
+        <v>46176.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2">
+        <v>46176.5625</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2">
+        <v>46176.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2">
+        <v>46176.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2">
+        <v>46176.59375</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2">
+        <v>46176.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2">
+        <v>46176.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2">
+        <v>46176.625</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2">
+        <v>46176.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2">
+        <v>46176.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2">
+        <v>46176.65625</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2">
+        <v>46176.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2">
+        <v>46176.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2">
+        <v>46176.6875</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2">
+        <v>46176.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2">
+        <v>46176.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2">
+        <v>46176.71875</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2">
+        <v>46176.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2">
+        <v>46176.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2">
+        <v>46176.75</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2">
+        <v>46176.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2">
+        <v>46176.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2">
+        <v>46176.78125</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2">
+        <v>46176.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2">
+        <v>46176.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2">
+        <v>46176.8125</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2">
+        <v>46176.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2">
+        <v>46176.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2">
+        <v>46176.84375</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2">
+        <v>46176.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2">
+        <v>46176.875</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2">
+        <v>46176.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2">
+        <v>46176.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2">
+        <v>46176.90625</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2">
+        <v>46176.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="2">
+        <v>46176.9375</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="2">
+        <v>46176.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="2">
+        <v>46176.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="2">
+        <v>46176.96875</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="2">
+        <v>46176.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="2">
+        <v>46176.98958333334</v>
+      </c>
+      <c r="B577">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,879 +394,879 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>711</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
-        <v>667</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
-        <v>636</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
-        <v>638</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>659</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>650</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>647</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>635</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>650</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>664</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>642</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>640</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>643</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>655</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>640</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>634</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>667</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>668</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>695</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>687</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>683</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>679</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>686</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>699</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>749</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>781</v>
+        <v>591</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>779</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>786</v>
+        <v>622</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>782</v>
+        <v>624</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>777</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>732</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>728</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>713</v>
+        <v>581</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>633</v>
+        <v>586</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>611</v>
+        <v>579</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>537</v>
+        <v>673</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>502</v>
+        <v>660</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>465</v>
+        <v>513</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>446</v>
+        <v>508</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>453</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>472</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>502</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>590</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>589</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>654</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>615</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>618</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>634</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>654</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>660</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>673</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>671</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>669</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>729</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>744</v>
+        <v>555</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>754</v>
+        <v>567</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>767</v>
+        <v>746</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>715</v>
+        <v>785</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>719</v>
+        <v>789</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>784</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>788</v>
+        <v>802</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>814</v>
+        <v>869</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>817</v>
+        <v>871</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>844</v>
+        <v>892</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>1080</v>
+        <v>896</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>1087</v>
+        <v>907</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>1079</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>1076</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>1091</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>1095</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>1089</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>1066</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>1069</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>1077</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>1080</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>1048</v>
+        <v>823</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>1041</v>
+        <v>786</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>1049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>1083</v>
+        <v>779</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>739</v>
+        <v>666</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>719</v>
+        <v>611</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>734</v>
+        <v>628</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>718</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>635</v>
+        <v>362</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>632</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>634</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>602</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>477</v>
+        <v>455</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
-        <v>471</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
-        <v>469</v>
+        <v>444</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
-        <v>466</v>
+        <v>442</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
-        <v>467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>444</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
-        <v>494</v>
+        <v>434</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
-        <v>490</v>
+        <v>429</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
-        <v>494</v>
+        <v>435</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
-        <v>484</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>493</v>
+        <v>443</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,311 +1274,311 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>489</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>466</v>
+        <v>450</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>520</v>
+        <v>545</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>517</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>519</v>
+        <v>550</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>523</v>
+        <v>580</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>644</v>
+        <v>661</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>656</v>
+        <v>678</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>671</v>
+        <v>685</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>589</v>
+        <v>640</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>573</v>
+        <v>629</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>654</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>757</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>746</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>751</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>756</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>755</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>749</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>750</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>733</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>734</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>719</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>730</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>685</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>675</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>678</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>673</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,447 +394,447 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>500</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>503</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>502</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>499</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>486</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>477</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>478</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>475</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>465</v>
+        <v>741</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>468</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>469</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>468</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>465</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>470</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>468</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>467</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>475</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>473</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>471</v>
+        <v>725</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>485</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>510</v>
+        <v>716</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>516</v>
+        <v>709</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>514</v>
+        <v>721</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>520</v>
+        <v>734</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>593</v>
+        <v>689</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>594</v>
+        <v>685</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>591</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>595</v>
+        <v>690</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>630</v>
+        <v>708</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>622</v>
+        <v>690</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>624</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>619</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>589</v>
+        <v>657</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>570</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>581</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>586</v>
+        <v>557</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>579</v>
+        <v>551</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>673</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>660</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>513</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>508</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>507</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>505</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>138</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>128</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>131</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>126</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>178</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>173</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>130</v>
+        <v>381</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>137</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>175</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>173</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
         <v>119</v>
@@ -842,1090 +842,674 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>158</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>184</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>555</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>567</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>746</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>785</v>
+        <v>669</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>789</v>
+        <v>680</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46184.6875</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
-        <v>784</v>
+        <v>688</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46184.69791666666</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46184.70833333334</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
-        <v>802</v>
+        <v>735</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46184.71875</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
-        <v>869</v>
+        <v>660</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46184.72916666666</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
-        <v>871</v>
+        <v>634</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46184.73958333334</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
-        <v>892</v>
+        <v>639</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46184.75</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
-        <v>896</v>
+        <v>670</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46184.76041666666</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
-        <v>907</v>
+        <v>674</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46184.77083333334</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
-        <v>1009</v>
+        <v>585</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46184.78125</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
-        <v>1007</v>
+        <v>601</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46184.79166666666</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>1276</v>
+        <v>794</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46184.80208333334</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>1285</v>
+        <v>810</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46184.8125</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>1133</v>
+        <v>813</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46184.82291666666</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
-        <v>1122</v>
+        <v>896</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46184.83333333334</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
-        <v>1125</v>
+        <v>957</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46184.84375</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
-        <v>1114</v>
+        <v>961</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46184.85416666666</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
-        <v>1103</v>
+        <v>958</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46184.86458333334</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
-        <v>1098</v>
+        <v>956</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46184.875</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
-        <v>823</v>
+        <v>880</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46184.88541666666</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
-        <v>786</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46184.89583333334</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>753</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46184.90625</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
-        <v>779</v>
+        <v>543</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46184.91666666666</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>666</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46184.92708333334</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>611</v>
+        <v>384</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46184.9375</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>628</v>
+        <v>437</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46184.94791666666</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>621</v>
+        <v>453</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46184.95833333334</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>362</v>
+        <v>482</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46184.96875</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>352</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46184.97916666666</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>355</v>
+        <v>546</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46184.98958333334</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>350</v>
+        <v>552</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>455</v>
+        <v>626</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
-        <v>462</v>
+        <v>617</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
-        <v>450</v>
+        <v>699</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46185.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
-        <v>460</v>
+        <v>719</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
-        <v>444</v>
+        <v>766</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
-        <v>442</v>
+        <v>749</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46185.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>743</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
-        <v>444</v>
+        <v>660</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
-        <v>434</v>
+        <v>630</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46185.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
-        <v>429</v>
+        <v>648</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
-        <v>435</v>
+        <v>583</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
-        <v>438</v>
+        <v>573</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46185.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
-        <v>443</v>
+        <v>581</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>594</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
-        <v>445</v>
+        <v>596</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46185.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
-        <v>450</v>
+        <v>653</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
-        <v>478</v>
+        <v>659</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>659</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46185.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>475</v>
+        <v>675</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>484</v>
+        <v>674</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>545</v>
+        <v>642</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46185.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>548</v>
+        <v>731</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
-        <v>550</v>
+        <v>748</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
-        <v>580</v>
+        <v>747</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46185.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
-        <v>661</v>
+        <v>633</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
-        <v>654</v>
+        <v>618</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
-        <v>655</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46185.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
-        <v>678</v>
+        <v>575</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
-        <v>680</v>
+        <v>571</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46185.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
-        <v>685</v>
+        <v>550</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
-        <v>681</v>
+        <v>532</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>640</v>
+        <v>532</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46185.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>629</v>
+        <v>540</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>633</v>
+        <v>556</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
-        <v>654</v>
+        <v>551</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46185.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>757</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
-        <v>746</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
-        <v>751</v>
+        <v>88</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46185.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
-        <v>756</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
-        <v>755</v>
+        <v>96</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
-        <v>749</v>
+        <v>64</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46185.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
-        <v>750</v>
+        <v>58</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46185.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46185.46875</v>
-      </c>
-      <c r="B143">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46185.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46185.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46185.5</v>
-      </c>
-      <c r="B146">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46185.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46185.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46185.53125</v>
-      </c>
-      <c r="B149">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46185.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46185.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46185.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46185.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46185.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46185.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46185.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46185.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46185.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46185.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46185.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46185.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46185.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46185.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46185.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46185.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46185.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46185.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46185.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46185.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46185.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46185.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46185.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46185.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46185.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46185.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46185.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46185.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46185.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46185.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46185.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46185.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46185.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46185.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46185.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46185.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46185.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46185.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1122 +394,2714 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>736</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46212.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
-        <v>730</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46212.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
-        <v>730</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46212.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>728</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46212.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
-        <v>728</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46212.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46212.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>679</v>
+        <v>743</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46212.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
-        <v>688</v>
+        <v>660</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46212.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
-        <v>741</v>
+        <v>630</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46212.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>747</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46212.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
-        <v>735</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46212.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
-        <v>723</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46212.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
-        <v>723</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46212.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
-        <v>729</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46212.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
-        <v>727</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46212.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>744</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46212.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
-        <v>746</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46212.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>741</v>
+        <v>659</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46212.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>725</v>
+        <v>675</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46212.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>750</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46212.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>716</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46212.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>709</v>
+        <v>731</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46212.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>721</v>
+        <v>748</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46212.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>734</v>
+        <v>747</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46212.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>689</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46212.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>685</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46212.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
-        <v>692</v>
+        <v>622</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46212.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>690</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46212.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>708</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46212.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>690</v>
+        <v>571</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46212.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>703</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46212.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>730</v>
+        <v>532</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46212.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>657</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46212.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>625</v>
+        <v>540</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46212.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>607</v>
+        <v>556</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46212.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>596</v>
+        <v>551</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46212.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>557</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46212.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
-        <v>551</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46212.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
-        <v>367</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46212.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>364</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46212.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>191</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46212.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>181</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46212.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>182</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46212.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46212.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>285</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46212.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>360</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46212.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>367</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46212.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B49">
-        <v>364</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46212.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>351</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46212.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B51">
-        <v>364</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46212.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B52">
-        <v>381</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46212.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>371</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46212.54166666666</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B54">
-        <v>141</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46212.55208333334</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B55">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46212.5625</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>129</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46212.57291666666</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B57">
-        <v>119</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46212.58333333334</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B58">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46212.59375</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>93</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46212.60416666666</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B60">
-        <v>88</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46212.61458333334</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B61">
-        <v>124</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46212.625</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46212.63541666666</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B63">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46212.64583333334</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B64">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46212.65625</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>446</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B66">
-        <v>669</v>
+        <v>716</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46212.67708333334</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B67">
-        <v>680</v>
+        <v>715</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46212.6875</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
-        <v>688</v>
+        <v>699</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46212.69791666666</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B69">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46212.70833333334</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B70">
-        <v>735</v>
+        <v>718</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46212.71875</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46212.72916666666</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B72">
-        <v>634</v>
+        <v>727</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46212.73958333334</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B73">
-        <v>639</v>
+        <v>744</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46212.75</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>670</v>
+        <v>776</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46212.76041666666</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B75">
-        <v>674</v>
+        <v>797</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46212.77083333334</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B76">
-        <v>585</v>
+        <v>801</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46212.78125</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
-        <v>601</v>
+        <v>801</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46212.79166666666</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B78">
-        <v>794</v>
+        <v>868</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46212.80208333334</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B79">
-        <v>810</v>
+        <v>875</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46212.8125</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>813</v>
+        <v>873</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46212.82291666666</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B81">
-        <v>896</v>
+        <v>868</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46212.83333333334</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B82">
-        <v>957</v>
+        <v>904</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46212.84375</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>961</v>
+        <v>910</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46212.85416666666</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B84">
-        <v>958</v>
+        <v>912</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46212.86458333334</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B85">
-        <v>956</v>
+        <v>905</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46212.875</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>880</v>
+        <v>927</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46212.88541666666</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B87">
-        <v>799</v>
+        <v>904</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46212.89583333334</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B88">
-        <v>753</v>
+        <v>829</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46212.90625</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>543</v>
+        <v>806</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46212.91666666666</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B90">
-        <v>380</v>
+        <v>709</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46212.92708333334</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B91">
-        <v>384</v>
+        <v>700</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46212.9375</v>
+        <v>46213.9375</v>
       </c>
       <c r="B92">
-        <v>437</v>
+        <v>697</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46212.94791666666</v>
+        <v>46213.94791666666</v>
       </c>
       <c r="B93">
-        <v>453</v>
+        <v>705</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46212.95833333334</v>
+        <v>46213.95833333334</v>
       </c>
       <c r="B94">
-        <v>482</v>
+        <v>572</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46212.96875</v>
+        <v>46213.96875</v>
       </c>
       <c r="B95">
-        <v>489</v>
+        <v>580</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46212.97916666666</v>
+        <v>46213.97916666666</v>
       </c>
       <c r="B96">
-        <v>546</v>
+        <v>582</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46212.98958333334</v>
+        <v>46213.98958333334</v>
       </c>
       <c r="B97">
-        <v>552</v>
+        <v>584</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B98">
-        <v>626</v>
+        <v>520</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46213.01041666666</v>
+        <v>46214.01041666666</v>
       </c>
       <c r="B99">
-        <v>617</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46213.02083333334</v>
+        <v>46214.02083333334</v>
       </c>
       <c r="B100">
-        <v>699</v>
+        <v>503</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46213.03125</v>
+        <v>46214.03125</v>
       </c>
       <c r="B101">
-        <v>719</v>
+        <v>504</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46213.04166666666</v>
+        <v>46214.04166666666</v>
       </c>
       <c r="B102">
-        <v>766</v>
+        <v>487</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46213.05208333334</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="B103">
-        <v>749</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46213.0625</v>
+        <v>46214.0625</v>
       </c>
       <c r="B104">
-        <v>743</v>
+        <v>475</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46213.07291666666</v>
+        <v>46214.07291666666</v>
       </c>
       <c r="B105">
-        <v>660</v>
+        <v>478</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46213.08333333334</v>
+        <v>46214.08333333334</v>
       </c>
       <c r="B106">
-        <v>630</v>
+        <v>505</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46213.09375</v>
+        <v>46214.09375</v>
       </c>
       <c r="B107">
-        <v>648</v>
+        <v>509</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46213.10416666666</v>
+        <v>46214.10416666666</v>
       </c>
       <c r="B108">
-        <v>583</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46213.11458333334</v>
+        <v>46214.11458333334</v>
       </c>
       <c r="B109">
-        <v>573</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46213.125</v>
+        <v>46214.125</v>
       </c>
       <c r="B110">
-        <v>581</v>
+        <v>509</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46213.13541666666</v>
+        <v>46214.13541666666</v>
       </c>
       <c r="B111">
-        <v>594</v>
+        <v>495</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46213.14583333334</v>
+        <v>46214.14583333334</v>
       </c>
       <c r="B112">
-        <v>596</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46213.15625</v>
+        <v>46214.15625</v>
       </c>
       <c r="B113">
-        <v>653</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46213.16666666666</v>
+        <v>46214.16666666666</v>
       </c>
       <c r="B114">
-        <v>659</v>
+        <v>519</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46213.17708333334</v>
+        <v>46214.17708333334</v>
       </c>
       <c r="B115">
-        <v>659</v>
+        <v>513</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46213.1875</v>
+        <v>46214.1875</v>
       </c>
       <c r="B116">
-        <v>675</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46213.19791666666</v>
+        <v>46214.19791666666</v>
       </c>
       <c r="B117">
-        <v>674</v>
+        <v>519</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46213.20833333334</v>
+        <v>46214.20833333334</v>
       </c>
       <c r="B118">
-        <v>642</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46213.21875</v>
+        <v>46214.21875</v>
       </c>
       <c r="B119">
-        <v>731</v>
+        <v>482</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46213.22916666666</v>
+        <v>46214.22916666666</v>
       </c>
       <c r="B120">
-        <v>748</v>
+        <v>478</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46213.23958333334</v>
+        <v>46214.23958333334</v>
       </c>
       <c r="B121">
-        <v>747</v>
+        <v>475</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46213.25</v>
+        <v>46214.25</v>
       </c>
       <c r="B122">
-        <v>633</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46213.26041666666</v>
+        <v>46214.26041666666</v>
       </c>
       <c r="B123">
-        <v>618</v>
+        <v>413</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46213.27083333334</v>
+        <v>46214.27083333334</v>
       </c>
       <c r="B124">
-        <v>622</v>
+        <v>412</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46213.28125</v>
+        <v>46214.28125</v>
       </c>
       <c r="B125">
-        <v>630</v>
+        <v>431</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46213.29166666666</v>
+        <v>46214.29166666666</v>
       </c>
       <c r="B126">
-        <v>575</v>
+        <v>502</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46213.30208333334</v>
+        <v>46214.30208333334</v>
       </c>
       <c r="B127">
-        <v>571</v>
+        <v>487</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46213.3125</v>
+        <v>46214.3125</v>
       </c>
       <c r="B128">
-        <v>550</v>
+        <v>464</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46213.32291666666</v>
+        <v>46214.32291666666</v>
       </c>
       <c r="B129">
-        <v>532</v>
+        <v>462</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46213.33333333334</v>
+        <v>46214.33333333334</v>
       </c>
       <c r="B130">
-        <v>532</v>
+        <v>406</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46213.34375</v>
+        <v>46214.34375</v>
       </c>
       <c r="B131">
-        <v>540</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46213.35416666666</v>
+        <v>46214.35416666666</v>
       </c>
       <c r="B132">
-        <v>556</v>
+        <v>404</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46213.36458333334</v>
+        <v>46214.36458333334</v>
       </c>
       <c r="B133">
-        <v>551</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46213.375</v>
+        <v>46214.375</v>
       </c>
       <c r="B134">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46213.38541666666</v>
+        <v>46214.38541666666</v>
       </c>
       <c r="B135">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46213.39583333334</v>
+        <v>46214.39583333334</v>
       </c>
       <c r="B136">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46213.40625</v>
+        <v>46214.40625</v>
       </c>
       <c r="B137">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46213.41666666666</v>
+        <v>46214.41666666666</v>
       </c>
       <c r="B138">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46213.42708333334</v>
+        <v>46214.42708333334</v>
       </c>
       <c r="B139">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46213.4375</v>
+        <v>46214.4375</v>
       </c>
       <c r="B140">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46213.44791666666</v>
+        <v>46214.44791666666</v>
       </c>
       <c r="B141">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46214.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46214.46875</v>
+      </c>
+      <c r="B143">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46214.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46214.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46214.5</v>
+      </c>
+      <c r="B146">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46214.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46214.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46214.53125</v>
+      </c>
+      <c r="B149">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46214.54166666666</v>
+      </c>
+      <c r="B150">
         <v>66</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46214.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46214.5625</v>
+      </c>
+      <c r="B152">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46214.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46214.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46214.59375</v>
+      </c>
+      <c r="B155">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46214.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46214.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46214.625</v>
+      </c>
+      <c r="B158">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46214.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46214.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46214.65625</v>
+      </c>
+      <c r="B161">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46214.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46214.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46214.6875</v>
+      </c>
+      <c r="B164">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46214.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46214.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46214.71875</v>
+      </c>
+      <c r="B167">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46214.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46214.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46214.75</v>
+      </c>
+      <c r="B170">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46214.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46214.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46214.78125</v>
+      </c>
+      <c r="B173">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46214.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46214.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46214.8125</v>
+      </c>
+      <c r="B176">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46214.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46214.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46214.84375</v>
+      </c>
+      <c r="B179">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46214.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46214.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46214.875</v>
+      </c>
+      <c r="B182">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46214.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46214.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46214.90625</v>
+      </c>
+      <c r="B185">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46214.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46214.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46214.9375</v>
+      </c>
+      <c r="B188">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46214.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46214.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46214.96875</v>
+      </c>
+      <c r="B191">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46214.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46214.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46215</v>
+      </c>
+      <c r="B194">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46215.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46215.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46215.03125</v>
+      </c>
+      <c r="B197">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46215.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46215.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46215.0625</v>
+      </c>
+      <c r="B200">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46215.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46215.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46215.09375</v>
+      </c>
+      <c r="B203">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46215.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46215.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46215.125</v>
+      </c>
+      <c r="B206">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46215.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46215.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46215.15625</v>
+      </c>
+      <c r="B209">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46215.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46215.1875</v>
+      </c>
+      <c r="B212">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46215.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46215.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46215.21875</v>
+      </c>
+      <c r="B215">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46215.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46215.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46215.25</v>
+      </c>
+      <c r="B218">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46215.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46215.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46215.28125</v>
+      </c>
+      <c r="B221">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46215.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46215.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46215.3125</v>
+      </c>
+      <c r="B224">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46215.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46215.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46215.34375</v>
+      </c>
+      <c r="B227">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46215.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46215.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46215.375</v>
+      </c>
+      <c r="B230">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46215.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46215.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46215.40625</v>
+      </c>
+      <c r="B233">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46215.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46215.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46215.4375</v>
+      </c>
+      <c r="B236">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46215.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46215.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46215.46875</v>
+      </c>
+      <c r="B239">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46215.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46215.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46215.5</v>
+      </c>
+      <c r="B242">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46215.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46215.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46215.53125</v>
+      </c>
+      <c r="B245">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46215.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46215.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46215.5625</v>
+      </c>
+      <c r="B248">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46215.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46215.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46215.59375</v>
+      </c>
+      <c r="B251">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46215.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46215.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46215.625</v>
+      </c>
+      <c r="B254">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46215.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46215.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46215.65625</v>
+      </c>
+      <c r="B257">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46215.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46215.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46215.6875</v>
+      </c>
+      <c r="B260">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46215.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46215.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46215.71875</v>
+      </c>
+      <c r="B263">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46215.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46215.75</v>
+      </c>
+      <c r="B266">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46215.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46215.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46215.78125</v>
+      </c>
+      <c r="B269">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46215.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46215.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46215.8125</v>
+      </c>
+      <c r="B272">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46215.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46215.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46215.84375</v>
+      </c>
+      <c r="B275">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46215.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46215.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46215.875</v>
+      </c>
+      <c r="B278">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46215.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46215.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46215.90625</v>
+      </c>
+      <c r="B281">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46215.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46215.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46215.9375</v>
+      </c>
+      <c r="B284">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46215.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46215.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46215.96875</v>
+      </c>
+      <c r="B287">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46215.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46215.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B290">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46216.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46216.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46216.03125</v>
+      </c>
+      <c r="B293">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46216.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46216.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46216.0625</v>
+      </c>
+      <c r="B296">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46216.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46216.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46216.09375</v>
+      </c>
+      <c r="B299">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46216.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46216.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46216.125</v>
+      </c>
+      <c r="B302">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46216.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46216.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46216.15625</v>
+      </c>
+      <c r="B305">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46216.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46216.1875</v>
+      </c>
+      <c r="B308">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46216.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46216.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46216.21875</v>
+      </c>
+      <c r="B311">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46216.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46216.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46216.25</v>
+      </c>
+      <c r="B314">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46216.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46216.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46216.28125</v>
+      </c>
+      <c r="B317">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46216.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46216.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46216.3125</v>
+      </c>
+      <c r="B320">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46216.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46216.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46216.34375</v>
+      </c>
+      <c r="B323">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46216.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46216.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="B326">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46216.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46216.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46216.40625</v>
+      </c>
+      <c r="B329">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46216.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46216.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46216.4375</v>
+      </c>
+      <c r="B332">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46216.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46216.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46216.46875</v>
+      </c>
+      <c r="B335">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46216.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46216.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46216.5</v>
+      </c>
+      <c r="B338">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46216.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46216.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1130 +394,1106 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>756</v>
+        <v>774</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46217.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46217.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
-        <v>753</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46217.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>752</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46217.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
-        <v>750</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46217.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46217.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46217.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46217.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>710</v>
+        <v>788</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46217.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>706</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46217.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>708</v>
+        <v>791</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46217.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>707</v>
+        <v>790</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46217.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>684</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46217.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>686</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46217.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>687</v>
+        <v>788</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46217.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>686</v>
+        <v>788</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46217.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
-        <v>717</v>
+        <v>826</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46217.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
-        <v>716</v>
+        <v>824</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46217.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>714</v>
+        <v>827</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46217.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>723</v>
+        <v>834</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46217.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>779</v>
+        <v>890</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46217.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>772</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46217.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>768</v>
+        <v>895</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46217.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>768</v>
+        <v>899</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46217.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>860</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46217.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>859</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46217.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>850</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46217.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>850</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46217.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>886</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46217.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>875</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46217.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>876</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46217.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>887</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46217.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46217.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>895</v>
+        <v>888</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46217.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>782</v>
+        <v>895</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46217.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>736</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46217.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>738</v>
+        <v>871</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46217.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>724</v>
+        <v>848</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46217.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>597</v>
+        <v>840</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46217.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>579</v>
+        <v>853</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46217.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>497</v>
+        <v>757</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46217.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>496</v>
+        <v>755</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46217.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>395</v>
+        <v>756</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46217.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>388</v>
+        <v>755</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46217.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>249</v>
+        <v>617</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46217.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
-        <v>254</v>
+        <v>639</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46217.47916666666</v>
+        <v>46218.47916666666</v>
       </c>
       <c r="B48">
-        <v>250</v>
+        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46217.48958333334</v>
+        <v>46218.48958333334</v>
       </c>
       <c r="B49">
-        <v>246</v>
+        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46217.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>174</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46217.51041666666</v>
+        <v>46218.51041666666</v>
       </c>
       <c r="B51">
-        <v>157</v>
+        <v>606</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46217.52083333334</v>
+        <v>46218.52083333334</v>
       </c>
       <c r="B52">
-        <v>165</v>
+        <v>602</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46217.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>168</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46217.54166666666</v>
+        <v>46218.54166666666</v>
       </c>
       <c r="B54">
-        <v>208</v>
+        <v>601</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46217.55208333334</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="B55">
-        <v>184</v>
+        <v>597</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46217.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>196</v>
+        <v>592</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46217.57291666666</v>
+        <v>46218.57291666666</v>
       </c>
       <c r="B57">
-        <v>211</v>
+        <v>502</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46217.58333333334</v>
+        <v>46218.58333333334</v>
       </c>
       <c r="B58">
-        <v>208</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46217.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>222</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46217.60416666666</v>
+        <v>46218.60416666666</v>
       </c>
       <c r="B60">
-        <v>213</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46217.61458333334</v>
+        <v>46218.61458333334</v>
       </c>
       <c r="B61">
-        <v>243</v>
+        <v>611</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46217.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>745</v>
+        <v>712</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46217.63541666666</v>
+        <v>46218.63541666666</v>
       </c>
       <c r="B63">
-        <v>754</v>
+        <v>722</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46217.64583333334</v>
+        <v>46218.64583333334</v>
       </c>
       <c r="B64">
-        <v>755</v>
+        <v>786</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46217.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>764</v>
+        <v>821</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46217.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="B66">
-        <v>892</v>
+        <v>991</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46217.67708333334</v>
+        <v>46218.67708333334</v>
       </c>
       <c r="B67">
-        <v>908</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46217.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>917</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46217.69791666666</v>
+        <v>46218.69791666666</v>
       </c>
       <c r="B69">
-        <v>918</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46217.70833333334</v>
+        <v>46218.70833333334</v>
       </c>
       <c r="B70">
-        <v>999</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46217.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
-        <v>1009</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46217.72916666666</v>
+        <v>46218.72916666666</v>
       </c>
       <c r="B72">
-        <v>1011</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46217.73958333334</v>
+        <v>46218.73958333334</v>
       </c>
       <c r="B73">
-        <v>1013</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46217.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46217.76041666666</v>
+        <v>46218.76041666666</v>
       </c>
       <c r="B75">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46217.77083333334</v>
+        <v>46218.77083333334</v>
       </c>
       <c r="B76">
-        <v>1054</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46217.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46217.79166666666</v>
+        <v>46218.79166666666</v>
       </c>
       <c r="B78">
-        <v>1035</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46217.80208333334</v>
+        <v>46218.80208333334</v>
       </c>
       <c r="B79">
-        <v>1045</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46217.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
-        <v>954</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46217.82291666666</v>
+        <v>46218.82291666666</v>
       </c>
       <c r="B81">
-        <v>943</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46217.83333333334</v>
+        <v>46218.83333333334</v>
       </c>
       <c r="B82">
-        <v>1007</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46217.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
-        <v>1015</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46217.85416666666</v>
+        <v>46218.85416666666</v>
       </c>
       <c r="B84">
-        <v>1021</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46217.86458333334</v>
+        <v>46218.86458333334</v>
       </c>
       <c r="B85">
-        <v>1021</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46217.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>963</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46217.88541666666</v>
+        <v>46218.88541666666</v>
       </c>
       <c r="B87">
-        <v>960</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46217.89583333334</v>
+        <v>46218.89583333334</v>
       </c>
       <c r="B88">
-        <v>951</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46217.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
-        <v>949</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46217.91666666666</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="B90">
-        <v>916</v>
+        <v>961</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46217.92708333334</v>
+        <v>46218.92708333334</v>
       </c>
       <c r="B91">
-        <v>905</v>
+        <v>953</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46217.9375</v>
+        <v>46218.9375</v>
       </c>
       <c r="B92">
-        <v>885</v>
+        <v>955</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46217.94791666666</v>
+        <v>46218.94791666666</v>
       </c>
       <c r="B93">
-        <v>883</v>
+        <v>964</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46217.95833333334</v>
+        <v>46218.95833333334</v>
       </c>
       <c r="B94">
-        <v>795</v>
+        <v>891</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46217.96875</v>
+        <v>46218.96875</v>
       </c>
       <c r="B95">
-        <v>794</v>
+        <v>877</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46217.97916666666</v>
+        <v>46218.97916666666</v>
       </c>
       <c r="B96">
-        <v>793</v>
+        <v>871</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46217.98958333334</v>
+        <v>46218.98958333334</v>
       </c>
       <c r="B97">
-        <v>782</v>
+        <v>854</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B98">
-        <v>774</v>
+        <v>875</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.01041666666</v>
       </c>
       <c r="B99">
-        <v>774</v>
+        <v>869</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.02083333334</v>
       </c>
       <c r="B100">
-        <v>771</v>
+        <v>868</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B101">
-        <v>772</v>
+        <v>867</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.04166666666</v>
       </c>
       <c r="B102">
-        <v>761</v>
+        <v>841</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.05208333334</v>
       </c>
       <c r="B103">
-        <v>743</v>
+        <v>839</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B104">
-        <v>742</v>
+        <v>839</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.07291666666</v>
       </c>
       <c r="B105">
-        <v>745</v>
+        <v>837</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.08333333334</v>
       </c>
       <c r="B106">
-        <v>788</v>
+        <v>831</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B107">
-        <v>789</v>
+        <v>821</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.10416666666</v>
       </c>
       <c r="B108">
-        <v>791</v>
+        <v>822</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.11458333334</v>
       </c>
       <c r="B109">
-        <v>790</v>
+        <v>827</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B110">
-        <v>790</v>
+        <v>823</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.13541666666</v>
       </c>
       <c r="B111">
-        <v>787</v>
+        <v>823</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.14583333334</v>
       </c>
       <c r="B112">
-        <v>788</v>
+        <v>822</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B113">
-        <v>788</v>
+        <v>823</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.16666666666</v>
       </c>
       <c r="B114">
-        <v>826</v>
+        <v>857</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.17708333334</v>
       </c>
       <c r="B115">
-        <v>824</v>
+        <v>871</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B116">
-        <v>827</v>
+        <v>866</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.19791666666</v>
       </c>
       <c r="B117">
-        <v>834</v>
+        <v>874</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.20833333334</v>
       </c>
       <c r="B118">
-        <v>890</v>
+        <v>914</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B119">
-        <v>892</v>
+        <v>910</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.22916666666</v>
       </c>
       <c r="B120">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.23958333334</v>
       </c>
       <c r="B121">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B122">
-        <v>1027</v>
+        <v>944</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.26041666666</v>
       </c>
       <c r="B123">
-        <v>1042</v>
+        <v>956</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.27083333334</v>
       </c>
       <c r="B124">
-        <v>1028</v>
+        <v>946</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B125">
-        <v>1031</v>
+        <v>946</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.29166666666</v>
       </c>
       <c r="B126">
-        <v>1000</v>
+        <v>930</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.30208333334</v>
       </c>
       <c r="B127">
-        <v>1002</v>
+        <v>935</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B128">
-        <v>1002</v>
+        <v>939</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46218.32291666666</v>
+        <v>46219.32291666666</v>
       </c>
       <c r="B129">
-        <v>1002</v>
+        <v>934</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46218.33333333334</v>
+        <v>46219.33333333334</v>
       </c>
       <c r="B130">
-        <v>904</v>
+        <v>933</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B131">
-        <v>888</v>
+        <v>944</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.35416666666</v>
       </c>
       <c r="B132">
-        <v>895</v>
+        <v>951</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.36458333334</v>
       </c>
       <c r="B133">
-        <v>900</v>
+        <v>934</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B134">
-        <v>871</v>
+        <v>759</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="B135">
-        <v>848</v>
+        <v>749</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.39583333334</v>
       </c>
       <c r="B136">
-        <v>840</v>
+        <v>808</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B137">
-        <v>853</v>
+        <v>811</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.41666666666</v>
       </c>
       <c r="B138">
-        <v>757</v>
+        <v>655</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.42708333334</v>
       </c>
       <c r="B139">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46218.4375</v>
-      </c>
-      <c r="B140">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46218.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46218.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>617</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1106 +394,2554 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B2">
-        <v>774</v>
+        <v>797</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46220.01041666666</v>
       </c>
       <c r="B3">
-        <v>774</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46220.02083333334</v>
       </c>
       <c r="B4">
-        <v>771</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46220.03125</v>
       </c>
       <c r="B5">
-        <v>772</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46220.04166666666</v>
       </c>
       <c r="B6">
-        <v>761</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46220.05208333334</v>
       </c>
       <c r="B7">
-        <v>743</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46220.0625</v>
       </c>
       <c r="B8">
-        <v>742</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46220.07291666666</v>
       </c>
       <c r="B9">
-        <v>745</v>
+        <v>774</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46220.08333333334</v>
       </c>
       <c r="B10">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46220.09375</v>
       </c>
       <c r="B11">
-        <v>789</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46220.10416666666</v>
       </c>
       <c r="B12">
-        <v>791</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46220.11458333334</v>
       </c>
       <c r="B13">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46220.125</v>
       </c>
       <c r="B14">
-        <v>790</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46220.13541666666</v>
       </c>
       <c r="B15">
-        <v>787</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46220.14583333334</v>
       </c>
       <c r="B16">
-        <v>788</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46220.15625</v>
       </c>
       <c r="B17">
-        <v>788</v>
+        <v>799</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46220.16666666666</v>
       </c>
       <c r="B18">
-        <v>826</v>
+        <v>832</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46220.17708333334</v>
       </c>
       <c r="B19">
-        <v>824</v>
+        <v>833</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46220.1875</v>
       </c>
       <c r="B20">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46220.19791666666</v>
       </c>
       <c r="B21">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46220.20833333334</v>
       </c>
       <c r="B22">
-        <v>890</v>
+        <v>872</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46220.21875</v>
       </c>
       <c r="B23">
-        <v>892</v>
+        <v>873</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46220.22916666666</v>
       </c>
       <c r="B24">
-        <v>895</v>
+        <v>875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46220.23958333334</v>
       </c>
       <c r="B25">
-        <v>899</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46220.25</v>
       </c>
       <c r="B26">
-        <v>1027</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46218.26041666666</v>
+        <v>46220.26041666666</v>
       </c>
       <c r="B27">
-        <v>1042</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46218.27083333334</v>
+        <v>46220.27083333334</v>
       </c>
       <c r="B28">
-        <v>1028</v>
+        <v>899</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46220.28125</v>
       </c>
       <c r="B29">
-        <v>1031</v>
+        <v>898</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46218.29166666666</v>
+        <v>46220.29166666666</v>
       </c>
       <c r="B30">
-        <v>1000</v>
+        <v>928</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46218.30208333334</v>
+        <v>46220.30208333334</v>
       </c>
       <c r="B31">
-        <v>1002</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46220.3125</v>
       </c>
       <c r="B32">
-        <v>1002</v>
+        <v>927</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46218.32291666666</v>
+        <v>46220.32291666666</v>
       </c>
       <c r="B33">
-        <v>1002</v>
+        <v>933</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46218.33333333334</v>
+        <v>46220.33333333334</v>
       </c>
       <c r="B34">
-        <v>904</v>
+        <v>862</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46220.34375</v>
       </c>
       <c r="B35">
-        <v>888</v>
+        <v>823</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46218.35416666666</v>
+        <v>46220.35416666666</v>
       </c>
       <c r="B36">
-        <v>895</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46218.36458333334</v>
+        <v>46220.36458333334</v>
       </c>
       <c r="B37">
-        <v>900</v>
+        <v>854</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46220.375</v>
       </c>
       <c r="B38">
-        <v>871</v>
+        <v>732</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46218.38541666666</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="B39">
-        <v>848</v>
+        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46220.39583333334</v>
       </c>
       <c r="B40">
-        <v>840</v>
+        <v>702</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46220.40625</v>
       </c>
       <c r="B41">
-        <v>853</v>
+        <v>696</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46220.41666666666</v>
       </c>
       <c r="B42">
-        <v>757</v>
+        <v>646</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46220.42708333334</v>
       </c>
       <c r="B43">
-        <v>755</v>
+        <v>646</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46220.4375</v>
       </c>
       <c r="B44">
-        <v>756</v>
+        <v>691</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46218.44791666666</v>
+        <v>46220.44791666666</v>
       </c>
       <c r="B45">
-        <v>755</v>
+        <v>733</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46218.45833333334</v>
+        <v>46220.45833333334</v>
       </c>
       <c r="B46">
-        <v>617</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46218.46875</v>
+        <v>46220.46875</v>
       </c>
       <c r="B47">
-        <v>639</v>
+        <v>688</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46218.47916666666</v>
+        <v>46220.47916666666</v>
       </c>
       <c r="B48">
-        <v>665</v>
+        <v>686</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46218.48958333334</v>
+        <v>46220.48958333334</v>
       </c>
       <c r="B49">
-        <v>665</v>
+        <v>698</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46218.5</v>
+        <v>46220.5</v>
       </c>
       <c r="B50">
-        <v>607</v>
+        <v>676</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46218.51041666666</v>
+        <v>46220.51041666666</v>
       </c>
       <c r="B51">
-        <v>606</v>
+        <v>667</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46218.52083333334</v>
+        <v>46220.52083333334</v>
       </c>
       <c r="B52">
-        <v>602</v>
+        <v>664</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46218.53125</v>
+        <v>46220.53125</v>
       </c>
       <c r="B53">
-        <v>600</v>
+        <v>667</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46218.54166666666</v>
+        <v>46220.54166666666</v>
       </c>
       <c r="B54">
-        <v>601</v>
+        <v>682</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46218.55208333334</v>
+        <v>46220.55208333334</v>
       </c>
       <c r="B55">
-        <v>597</v>
+        <v>681</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46218.5625</v>
+        <v>46220.5625</v>
       </c>
       <c r="B56">
-        <v>592</v>
+        <v>675</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46218.57291666666</v>
+        <v>46220.57291666666</v>
       </c>
       <c r="B57">
-        <v>502</v>
+        <v>675</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46218.58333333334</v>
+        <v>46220.58333333334</v>
       </c>
       <c r="B58">
-        <v>426</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46218.59375</v>
+        <v>46220.59375</v>
       </c>
       <c r="B59">
-        <v>288</v>
+        <v>711</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46218.60416666666</v>
+        <v>46220.60416666666</v>
       </c>
       <c r="B60">
-        <v>497</v>
+        <v>692</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46218.61458333334</v>
+        <v>46220.61458333334</v>
       </c>
       <c r="B61">
-        <v>611</v>
+        <v>717</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46218.625</v>
+        <v>46220.625</v>
       </c>
       <c r="B62">
-        <v>712</v>
+        <v>753</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46218.63541666666</v>
+        <v>46220.63541666666</v>
       </c>
       <c r="B63">
-        <v>722</v>
+        <v>761</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46218.64583333334</v>
+        <v>46220.64583333334</v>
       </c>
       <c r="B64">
-        <v>786</v>
+        <v>755</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46218.65625</v>
+        <v>46220.65625</v>
       </c>
       <c r="B65">
-        <v>821</v>
+        <v>783</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46218.66666666666</v>
+        <v>46220.66666666666</v>
       </c>
       <c r="B66">
-        <v>991</v>
+        <v>793</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46218.67708333334</v>
+        <v>46220.67708333334</v>
       </c>
       <c r="B67">
-        <v>1009</v>
+        <v>786</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46218.6875</v>
+        <v>46220.6875</v>
       </c>
       <c r="B68">
-        <v>1002</v>
+        <v>783</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46218.69791666666</v>
+        <v>46220.69791666666</v>
       </c>
       <c r="B69">
-        <v>1000</v>
+        <v>796</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46218.70833333334</v>
+        <v>46220.70833333334</v>
       </c>
       <c r="B70">
-        <v>1067</v>
+        <v>884</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46218.71875</v>
+        <v>46220.71875</v>
       </c>
       <c r="B71">
-        <v>1060</v>
+        <v>901</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46218.72916666666</v>
+        <v>46220.72916666666</v>
       </c>
       <c r="B72">
-        <v>1034</v>
+        <v>902</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46218.73958333334</v>
+        <v>46220.73958333334</v>
       </c>
       <c r="B73">
-        <v>1035</v>
+        <v>922</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46218.75</v>
+        <v>46220.75</v>
       </c>
       <c r="B74">
-        <v>1035</v>
+        <v>949</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46218.76041666666</v>
+        <v>46220.76041666666</v>
       </c>
       <c r="B75">
-        <v>1056</v>
+        <v>954</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46218.77083333334</v>
+        <v>46220.77083333334</v>
       </c>
       <c r="B76">
-        <v>1066</v>
+        <v>959</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46218.78125</v>
+        <v>46220.78125</v>
       </c>
       <c r="B77">
-        <v>1064</v>
+        <v>979</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46218.79166666666</v>
+        <v>46220.79166666666</v>
       </c>
       <c r="B78">
-        <v>1134</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46218.80208333334</v>
+        <v>46220.80208333334</v>
       </c>
       <c r="B79">
-        <v>1188</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46218.8125</v>
+        <v>46220.8125</v>
       </c>
       <c r="B80">
-        <v>1211</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46218.82291666666</v>
+        <v>46220.82291666666</v>
       </c>
       <c r="B81">
-        <v>1217</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46218.83333333334</v>
+        <v>46220.83333333334</v>
       </c>
       <c r="B82">
-        <v>1134</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46218.84375</v>
+        <v>46220.84375</v>
       </c>
       <c r="B83">
-        <v>1126</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46218.85416666666</v>
+        <v>46220.85416666666</v>
       </c>
       <c r="B84">
-        <v>1092</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46218.86458333334</v>
+        <v>46220.86458333334</v>
       </c>
       <c r="B85">
-        <v>1090</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46218.875</v>
+        <v>46220.875</v>
       </c>
       <c r="B86">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46218.88541666666</v>
+        <v>46220.88541666666</v>
       </c>
       <c r="B87">
-        <v>1078</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46218.89583333334</v>
+        <v>46220.89583333334</v>
       </c>
       <c r="B88">
-        <v>1063</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46218.90625</v>
+        <v>46220.90625</v>
       </c>
       <c r="B89">
-        <v>1064</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46218.91666666666</v>
+        <v>46220.91666666666</v>
       </c>
       <c r="B90">
-        <v>961</v>
+        <v>893</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46218.92708333334</v>
+        <v>46220.92708333334</v>
       </c>
       <c r="B91">
-        <v>953</v>
+        <v>882</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46218.9375</v>
+        <v>46220.9375</v>
       </c>
       <c r="B92">
-        <v>955</v>
+        <v>880</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46218.94791666666</v>
+        <v>46220.94791666666</v>
       </c>
       <c r="B93">
-        <v>964</v>
+        <v>877</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46218.95833333334</v>
+        <v>46220.95833333334</v>
       </c>
       <c r="B94">
-        <v>891</v>
+        <v>690</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46218.96875</v>
+        <v>46220.96875</v>
       </c>
       <c r="B95">
-        <v>877</v>
+        <v>706</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46218.97916666666</v>
+        <v>46220.97916666666</v>
       </c>
       <c r="B96">
-        <v>871</v>
+        <v>709</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46218.98958333334</v>
+        <v>46220.98958333334</v>
       </c>
       <c r="B97">
-        <v>854</v>
+        <v>707</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="B98">
-        <v>875</v>
+        <v>652</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46219.01041666666</v>
+        <v>46221.01041666666</v>
       </c>
       <c r="B99">
-        <v>869</v>
+        <v>644</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46219.02083333334</v>
+        <v>46221.02083333334</v>
       </c>
       <c r="B100">
-        <v>868</v>
+        <v>644</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46219.03125</v>
+        <v>46221.03125</v>
       </c>
       <c r="B101">
-        <v>867</v>
+        <v>643</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46219.04166666666</v>
+        <v>46221.04166666666</v>
       </c>
       <c r="B102">
-        <v>841</v>
+        <v>616</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46219.05208333334</v>
+        <v>46221.05208333334</v>
       </c>
       <c r="B103">
-        <v>839</v>
+        <v>613</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46219.0625</v>
+        <v>46221.0625</v>
       </c>
       <c r="B104">
-        <v>839</v>
+        <v>614</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46219.07291666666</v>
+        <v>46221.07291666666</v>
       </c>
       <c r="B105">
-        <v>837</v>
+        <v>613</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46219.08333333334</v>
+        <v>46221.08333333334</v>
       </c>
       <c r="B106">
-        <v>831</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46219.09375</v>
+        <v>46221.09375</v>
       </c>
       <c r="B107">
-        <v>821</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46219.10416666666</v>
+        <v>46221.10416666666</v>
       </c>
       <c r="B108">
-        <v>822</v>
+        <v>601</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46219.11458333334</v>
+        <v>46221.11458333334</v>
       </c>
       <c r="B109">
-        <v>827</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46219.125</v>
+        <v>46221.125</v>
       </c>
       <c r="B110">
-        <v>823</v>
+        <v>606</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46219.13541666666</v>
+        <v>46221.13541666666</v>
       </c>
       <c r="B111">
-        <v>823</v>
+        <v>611</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46219.14583333334</v>
+        <v>46221.14583333334</v>
       </c>
       <c r="B112">
-        <v>822</v>
+        <v>599</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46219.15625</v>
+        <v>46221.15625</v>
       </c>
       <c r="B113">
-        <v>823</v>
+        <v>603</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46219.16666666666</v>
+        <v>46221.16666666666</v>
       </c>
       <c r="B114">
-        <v>857</v>
+        <v>619</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46219.17708333334</v>
+        <v>46221.17708333334</v>
       </c>
       <c r="B115">
-        <v>871</v>
+        <v>614</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46219.1875</v>
+        <v>46221.1875</v>
       </c>
       <c r="B116">
-        <v>866</v>
+        <v>615</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46219.19791666666</v>
+        <v>46221.19791666666</v>
       </c>
       <c r="B117">
-        <v>874</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46219.20833333334</v>
+        <v>46221.20833333334</v>
       </c>
       <c r="B118">
-        <v>914</v>
+        <v>632</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46219.21875</v>
+        <v>46221.21875</v>
       </c>
       <c r="B119">
-        <v>910</v>
+        <v>610</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46219.22916666666</v>
+        <v>46221.22916666666</v>
       </c>
       <c r="B120">
-        <v>894</v>
+        <v>607</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46219.23958333334</v>
+        <v>46221.23958333334</v>
       </c>
       <c r="B121">
-        <v>901</v>
+        <v>605</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46219.25</v>
+        <v>46221.25</v>
       </c>
       <c r="B122">
-        <v>944</v>
+        <v>598</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46219.26041666666</v>
+        <v>46221.26041666666</v>
       </c>
       <c r="B123">
-        <v>956</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46219.27083333334</v>
+        <v>46221.27083333334</v>
       </c>
       <c r="B124">
-        <v>946</v>
+        <v>589</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46219.28125</v>
+        <v>46221.28125</v>
       </c>
       <c r="B125">
-        <v>946</v>
+        <v>590</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46219.29166666666</v>
+        <v>46221.29166666666</v>
       </c>
       <c r="B126">
-        <v>930</v>
+        <v>563</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46219.30208333334</v>
+        <v>46221.30208333334</v>
       </c>
       <c r="B127">
-        <v>935</v>
+        <v>565</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46219.3125</v>
+        <v>46221.3125</v>
       </c>
       <c r="B128">
-        <v>939</v>
+        <v>564</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46219.32291666666</v>
+        <v>46221.32291666666</v>
       </c>
       <c r="B129">
-        <v>934</v>
+        <v>562</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46219.33333333334</v>
+        <v>46221.33333333334</v>
       </c>
       <c r="B130">
-        <v>933</v>
+        <v>536</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46219.34375</v>
+        <v>46221.34375</v>
       </c>
       <c r="B131">
-        <v>944</v>
+        <v>526</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46219.35416666666</v>
+        <v>46221.35416666666</v>
       </c>
       <c r="B132">
-        <v>951</v>
+        <v>524</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46219.36458333334</v>
+        <v>46221.36458333334</v>
       </c>
       <c r="B133">
-        <v>934</v>
+        <v>513</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46219.375</v>
+        <v>46221.375</v>
       </c>
       <c r="B134">
-        <v>759</v>
+        <v>276</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46219.38541666666</v>
+        <v>46221.38541666666</v>
       </c>
       <c r="B135">
-        <v>749</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46219.39583333334</v>
+        <v>46221.39583333334</v>
       </c>
       <c r="B136">
-        <v>808</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46219.40625</v>
+        <v>46221.40625</v>
       </c>
       <c r="B137">
-        <v>811</v>
+        <v>230</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46219.41666666666</v>
+        <v>46221.41666666666</v>
       </c>
       <c r="B138">
-        <v>655</v>
+        <v>129</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46219.42708333334</v>
+        <v>46221.42708333334</v>
       </c>
       <c r="B139">
-        <v>596</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46221.4375</v>
+      </c>
+      <c r="B140">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46221.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46221.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46221.46875</v>
+      </c>
+      <c r="B143">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46221.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46221.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46221.5</v>
+      </c>
+      <c r="B146">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46221.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46221.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46221.53125</v>
+      </c>
+      <c r="B149">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46221.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46221.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46221.5625</v>
+      </c>
+      <c r="B152">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46221.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46221.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46221.59375</v>
+      </c>
+      <c r="B155">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46221.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46221.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46221.625</v>
+      </c>
+      <c r="B158">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46221.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46221.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46221.65625</v>
+      </c>
+      <c r="B161">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46221.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46221.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46221.6875</v>
+      </c>
+      <c r="B164">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46221.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46221.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46221.71875</v>
+      </c>
+      <c r="B167">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46221.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46221.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46221.75</v>
+      </c>
+      <c r="B170">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46221.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46221.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46221.78125</v>
+      </c>
+      <c r="B173">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46221.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46221.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46221.8125</v>
+      </c>
+      <c r="B176">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46221.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46221.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46221.84375</v>
+      </c>
+      <c r="B179">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46221.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46221.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46221.875</v>
+      </c>
+      <c r="B182">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46221.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46221.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46221.90625</v>
+      </c>
+      <c r="B185">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46221.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46221.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46221.9375</v>
+      </c>
+      <c r="B188">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46221.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46221.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46221.96875</v>
+      </c>
+      <c r="B191">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46221.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46221.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B194">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46222.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46222.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46222.03125</v>
+      </c>
+      <c r="B197">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46222.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46222.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46222.0625</v>
+      </c>
+      <c r="B200">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46222.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46222.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46222.09375</v>
+      </c>
+      <c r="B203">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46222.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46222.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46222.125</v>
+      </c>
+      <c r="B206">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46222.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46222.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46222.15625</v>
+      </c>
+      <c r="B209">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46222.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46222.1875</v>
+      </c>
+      <c r="B212">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46222.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46222.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46222.21875</v>
+      </c>
+      <c r="B215">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46222.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46222.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46222.25</v>
+      </c>
+      <c r="B218">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46222.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46222.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46222.28125</v>
+      </c>
+      <c r="B221">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46222.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46222.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46222.3125</v>
+      </c>
+      <c r="B224">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46222.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46222.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46222.34375</v>
+      </c>
+      <c r="B227">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46222.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46222.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46222.375</v>
+      </c>
+      <c r="B230">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46222.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46222.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46222.40625</v>
+      </c>
+      <c r="B233">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46222.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46222.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46222.4375</v>
+      </c>
+      <c r="B236">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46222.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46222.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46222.46875</v>
+      </c>
+      <c r="B239">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46222.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46222.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46222.5</v>
+      </c>
+      <c r="B242">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46222.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46222.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46222.53125</v>
+      </c>
+      <c r="B245">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46222.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46222.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46222.5625</v>
+      </c>
+      <c r="B248">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46222.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46222.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46222.59375</v>
+      </c>
+      <c r="B251">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46222.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46222.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46222.625</v>
+      </c>
+      <c r="B254">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46222.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46222.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46222.65625</v>
+      </c>
+      <c r="B257">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46222.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46222.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46222.6875</v>
+      </c>
+      <c r="B260">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46222.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46222.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46222.71875</v>
+      </c>
+      <c r="B263">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46222.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46222.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46222.75</v>
+      </c>
+      <c r="B266">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46222.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46222.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46222.78125</v>
+      </c>
+      <c r="B269">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46222.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46222.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46222.8125</v>
+      </c>
+      <c r="B272">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46222.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46222.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46222.84375</v>
+      </c>
+      <c r="B275">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46222.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46222.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46222.875</v>
+      </c>
+      <c r="B278">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46222.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46222.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46222.90625</v>
+      </c>
+      <c r="B281">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46222.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46222.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46222.9375</v>
+      </c>
+      <c r="B284">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46222.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46222.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46222.96875</v>
+      </c>
+      <c r="B287">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46222.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46222.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B290">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46223.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46223.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46223.03125</v>
+      </c>
+      <c r="B293">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46223.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46223.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46223.0625</v>
+      </c>
+      <c r="B296">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46223.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46223.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46223.09375</v>
+      </c>
+      <c r="B299">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46223.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46223.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46223.125</v>
+      </c>
+      <c r="B302">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46223.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46223.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46223.15625</v>
+      </c>
+      <c r="B305">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46223.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46223.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46223.1875</v>
+      </c>
+      <c r="B308">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46223.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46223.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46223.21875</v>
+      </c>
+      <c r="B311">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46223.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46223.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46223.25</v>
+      </c>
+      <c r="B314">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46223.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46223.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46223.28125</v>
+      </c>
+      <c r="B317">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46223.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46223.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46223.3125</v>
+      </c>
+      <c r="B320">
+        <v>823</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1002 +394,1018 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>622</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46225.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
-        <v>619</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46225.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
-        <v>617</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46225.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>612</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46225.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
-        <v>556</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46225.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
-        <v>556</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46225.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>559</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46225.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
-        <v>560</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46225.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
-        <v>526</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46225.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>511</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46225.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
-        <v>511</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46225.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
-        <v>517</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46225.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>533</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46225.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
-        <v>537</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46225.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
-        <v>531</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46225.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>536</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46225.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
-        <v>540</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46225.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
-        <v>539</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46225.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>538</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46225.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
-        <v>566</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46225.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>609</v>
+        <v>539</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46225.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>606</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46225.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>608</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46225.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>610</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46225.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>715</v>
+        <v>538</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46225.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>723</v>
+        <v>527</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46225.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>721</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46225.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>729</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46225.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>774</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46225.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>749</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46225.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>783</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46225.32291666666</v>
+        <v>46226.32291666666</v>
       </c>
       <c r="B33">
-        <v>806</v>
+        <v>446</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46225.33333333334</v>
+        <v>46226.33333333334</v>
       </c>
       <c r="B34">
-        <v>1005</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46225.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>997</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46225.35416666666</v>
+        <v>46226.35416666666</v>
       </c>
       <c r="B36">
-        <v>1028</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46225.36458333334</v>
+        <v>46226.36458333334</v>
       </c>
       <c r="B37">
-        <v>1000</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46225.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>557</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46225.38541666666</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="B39">
-        <v>496</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46225.39583333334</v>
+        <v>46226.39583333334</v>
       </c>
       <c r="B40">
-        <v>579</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46225.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>588</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46225.41666666666</v>
+        <v>46226.41666666666</v>
       </c>
       <c r="B42">
-        <v>539</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46225.42708333334</v>
+        <v>46226.42708333334</v>
       </c>
       <c r="B43">
-        <v>529</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46225.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
-        <v>459</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46225.44791666666</v>
+        <v>46226.44791666666</v>
       </c>
       <c r="B45">
-        <v>396</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46225.45833333334</v>
+        <v>46226.45833333334</v>
       </c>
       <c r="B46">
-        <v>376</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46225.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>382</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46225.47916666666</v>
+        <v>46226.47916666666</v>
       </c>
       <c r="B48">
-        <v>375</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46225.48958333334</v>
+        <v>46226.48958333334</v>
       </c>
       <c r="B49">
-        <v>377</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46225.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>372</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46225.51041666666</v>
+        <v>46226.51041666666</v>
       </c>
       <c r="B51">
-        <v>374</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46225.52083333334</v>
+        <v>46226.52083333334</v>
       </c>
       <c r="B52">
-        <v>375</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46225.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>379</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46225.54166666666</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="B54">
-        <v>431</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46225.55208333334</v>
+        <v>46226.55208333334</v>
       </c>
       <c r="B55">
-        <v>581</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46225.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>551</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46225.57291666666</v>
+        <v>46226.57291666666</v>
       </c>
       <c r="B57">
-        <v>545</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46225.58333333334</v>
+        <v>46226.58333333334</v>
       </c>
       <c r="B58">
-        <v>614</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46225.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
-        <v>549</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46225.60416666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="B60">
-        <v>392</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46225.61458333334</v>
+        <v>46226.61458333334</v>
       </c>
       <c r="B61">
-        <v>363</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46225.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
-        <v>286</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46225.63541666666</v>
+        <v>46226.63541666666</v>
       </c>
       <c r="B63">
-        <v>278</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46225.64583333334</v>
+        <v>46226.64583333334</v>
       </c>
       <c r="B64">
-        <v>283</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46225.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>291</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46225.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="B66">
-        <v>337</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46225.67708333334</v>
+        <v>46226.67708333334</v>
       </c>
       <c r="B67">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46225.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>347</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46225.69791666666</v>
+        <v>46226.69791666666</v>
       </c>
       <c r="B69">
-        <v>384</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46225.70833333334</v>
+        <v>46226.70833333334</v>
       </c>
       <c r="B70">
-        <v>825</v>
+        <v>654</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46225.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>837</v>
+        <v>659</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46225.72916666666</v>
+        <v>46226.72916666666</v>
       </c>
       <c r="B72">
-        <v>837</v>
+        <v>662</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46225.73958333334</v>
+        <v>46226.73958333334</v>
       </c>
       <c r="B73">
-        <v>838</v>
+        <v>660</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46225.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
-        <v>896</v>
+        <v>711</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46225.76041666666</v>
+        <v>46226.76041666666</v>
       </c>
       <c r="B75">
-        <v>909</v>
+        <v>723</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46225.77083333334</v>
+        <v>46226.77083333334</v>
       </c>
       <c r="B76">
-        <v>813</v>
+        <v>724</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46225.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
-        <v>816</v>
+        <v>728</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46225.79166666666</v>
+        <v>46226.79166666666</v>
       </c>
       <c r="B78">
-        <v>867</v>
+        <v>858</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46225.80208333334</v>
+        <v>46226.80208333334</v>
       </c>
       <c r="B79">
-        <v>879</v>
+        <v>868</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46225.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
-        <v>875</v>
+        <v>865</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46225.82291666666</v>
+        <v>46226.82291666666</v>
       </c>
       <c r="B81">
-        <v>875</v>
+        <v>867</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46225.83333333334</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="B82">
-        <v>875</v>
+        <v>856</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46225.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
-        <v>874</v>
+        <v>859</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46225.85416666666</v>
+        <v>46226.85416666666</v>
       </c>
       <c r="B84">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46225.86458333334</v>
+        <v>46226.86458333334</v>
       </c>
       <c r="B85">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46225.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>822</v>
+        <v>775</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46225.88541666666</v>
+        <v>46226.88541666666</v>
       </c>
       <c r="B87">
-        <v>825</v>
+        <v>771</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46225.89583333334</v>
+        <v>46226.89583333334</v>
       </c>
       <c r="B88">
-        <v>821</v>
+        <v>760</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46225.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
-        <v>790</v>
+        <v>751</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46225.91666666666</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="B90">
-        <v>620</v>
+        <v>676</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46225.92708333334</v>
+        <v>46226.92708333334</v>
       </c>
       <c r="B91">
-        <v>611</v>
+        <v>675</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46225.9375</v>
+        <v>46226.9375</v>
       </c>
       <c r="B92">
-        <v>613</v>
+        <v>675</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46225.94791666666</v>
+        <v>46226.94791666666</v>
       </c>
       <c r="B93">
-        <v>611</v>
+        <v>671</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46225.95833333334</v>
+        <v>46226.95833333334</v>
       </c>
       <c r="B94">
-        <v>491</v>
+        <v>526</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46225.96875</v>
+        <v>46226.96875</v>
       </c>
       <c r="B95">
-        <v>475</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46225.97916666666</v>
+        <v>46226.97916666666</v>
       </c>
       <c r="B96">
-        <v>474</v>
+        <v>523</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46225.98958333334</v>
+        <v>46226.98958333334</v>
       </c>
       <c r="B97">
-        <v>490</v>
+        <v>516</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B98">
-        <v>405</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B99">
-        <v>401</v>
+        <v>511</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B100">
-        <v>411</v>
+        <v>511</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B101">
-        <v>414</v>
+        <v>510</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B102">
-        <v>355</v>
+        <v>476</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B103">
-        <v>367</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B104">
-        <v>370</v>
+        <v>475</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B105">
-        <v>385</v>
+        <v>486</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B106">
-        <v>396</v>
+        <v>466</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B107">
-        <v>389</v>
+        <v>463</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B108">
-        <v>449</v>
+        <v>465</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B109">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B110">
-        <v>456</v>
+        <v>475</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B111">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B112">
-        <v>452</v>
+        <v>474</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B113">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B114">
-        <v>452</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B115">
-        <v>455</v>
+        <v>490</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B116">
-        <v>450</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B117">
-        <v>453</v>
+        <v>507</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B118">
-        <v>539</v>
+        <v>553</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B119">
-        <v>563</v>
+        <v>552</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B120">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B121">
-        <v>576</v>
+        <v>565</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B122">
-        <v>538</v>
+        <v>642</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B123">
-        <v>527</v>
+        <v>629</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B124">
-        <v>531</v>
+        <v>615</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B125">
-        <v>528</v>
+        <v>620</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B126">
-        <v>445</v>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46227.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46227.3125</v>
+      </c>
+      <c r="B128">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -394,1018 +394,1018 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="B2">
-        <v>405</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46226.01041666666</v>
+        <v>46228.01041666666</v>
       </c>
       <c r="B3">
-        <v>401</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46226.02083333334</v>
+        <v>46228.02083333334</v>
       </c>
       <c r="B4">
-        <v>411</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46228.03125</v>
       </c>
       <c r="B5">
-        <v>414</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46226.04166666666</v>
+        <v>46228.04166666666</v>
       </c>
       <c r="B6">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46226.05208333334</v>
+        <v>46228.05208333334</v>
       </c>
       <c r="B7">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46228.0625</v>
       </c>
       <c r="B8">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46226.07291666666</v>
+        <v>46228.07291666666</v>
       </c>
       <c r="B9">
-        <v>385</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46226.08333333334</v>
+        <v>46228.08333333334</v>
       </c>
       <c r="B10">
-        <v>396</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46228.09375</v>
       </c>
       <c r="B11">
-        <v>389</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46226.10416666666</v>
+        <v>46228.10416666666</v>
       </c>
       <c r="B12">
-        <v>449</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46226.11458333334</v>
+        <v>46228.11458333334</v>
       </c>
       <c r="B13">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46228.125</v>
       </c>
       <c r="B14">
-        <v>456</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46226.13541666666</v>
+        <v>46228.13541666666</v>
       </c>
       <c r="B15">
-        <v>459</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46226.14583333334</v>
+        <v>46228.14583333334</v>
       </c>
       <c r="B16">
-        <v>452</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46228.15625</v>
       </c>
       <c r="B17">
-        <v>446</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46226.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="B18">
-        <v>452</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46226.17708333334</v>
+        <v>46228.17708333334</v>
       </c>
       <c r="B19">
-        <v>455</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46228.1875</v>
       </c>
       <c r="B20">
-        <v>450</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46226.19791666666</v>
+        <v>46228.19791666666</v>
       </c>
       <c r="B21">
-        <v>453</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46226.20833333334</v>
+        <v>46228.20833333334</v>
       </c>
       <c r="B22">
-        <v>539</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46228.21875</v>
       </c>
       <c r="B23">
-        <v>563</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46226.22916666666</v>
+        <v>46228.22916666666</v>
       </c>
       <c r="B24">
-        <v>568</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46226.23958333334</v>
+        <v>46228.23958333334</v>
       </c>
       <c r="B25">
-        <v>576</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46228.25</v>
       </c>
       <c r="B26">
-        <v>538</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46226.26041666666</v>
+        <v>46228.26041666666</v>
       </c>
       <c r="B27">
-        <v>527</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46226.27083333334</v>
+        <v>46228.27083333334</v>
       </c>
       <c r="B28">
-        <v>531</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46228.28125</v>
       </c>
       <c r="B29">
-        <v>528</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46226.29166666666</v>
+        <v>46228.29166666666</v>
       </c>
       <c r="B30">
-        <v>445</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46226.30208333334</v>
+        <v>46228.30208333334</v>
       </c>
       <c r="B31">
-        <v>439</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46226.3125</v>
+        <v>46228.3125</v>
       </c>
       <c r="B32">
-        <v>438</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46226.32291666666</v>
+        <v>46228.32291666666</v>
       </c>
       <c r="B33">
-        <v>446</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46226.33333333334</v>
+        <v>46228.33333333334</v>
       </c>
       <c r="B34">
-        <v>323</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46226.34375</v>
+        <v>46228.34375</v>
       </c>
       <c r="B35">
-        <v>319</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46226.35416666666</v>
+        <v>46228.35416666666</v>
       </c>
       <c r="B36">
-        <v>292</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46226.36458333334</v>
+        <v>46228.36458333334</v>
       </c>
       <c r="B37">
-        <v>288</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46226.375</v>
+        <v>46228.375</v>
       </c>
       <c r="B38">
-        <v>207</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46226.38541666666</v>
+        <v>46228.38541666666</v>
       </c>
       <c r="B39">
-        <v>190</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46226.39583333334</v>
+        <v>46228.39583333334</v>
       </c>
       <c r="B40">
-        <v>182</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46226.40625</v>
+        <v>46228.40625</v>
       </c>
       <c r="B41">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46226.41666666666</v>
+        <v>46228.41666666666</v>
       </c>
       <c r="B42">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46226.42708333334</v>
+        <v>46228.42708333334</v>
       </c>
       <c r="B43">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46226.4375</v>
+        <v>46228.4375</v>
       </c>
       <c r="B44">
-        <v>137</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46226.44791666666</v>
+        <v>46228.44791666666</v>
       </c>
       <c r="B45">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46226.45833333334</v>
+        <v>46228.45833333334</v>
       </c>
       <c r="B46">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46226.46875</v>
+        <v>46228.46875</v>
       </c>
       <c r="B47">
-        <v>161</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46226.47916666666</v>
+        <v>46228.47916666666</v>
       </c>
       <c r="B48">
-        <v>151</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46226.48958333334</v>
+        <v>46228.48958333334</v>
       </c>
       <c r="B49">
-        <v>146</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46226.5</v>
+        <v>46228.5</v>
       </c>
       <c r="B50">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46226.51041666666</v>
+        <v>46228.51041666666</v>
       </c>
       <c r="B51">
-        <v>167</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46226.52083333334</v>
+        <v>46228.52083333334</v>
       </c>
       <c r="B52">
-        <v>171</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46226.53125</v>
+        <v>46228.53125</v>
       </c>
       <c r="B53">
-        <v>163</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46226.54166666666</v>
+        <v>46228.54166666666</v>
       </c>
       <c r="B54">
-        <v>170</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46226.55208333334</v>
+        <v>46228.55208333334</v>
       </c>
       <c r="B55">
-        <v>178</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46226.5625</v>
+        <v>46228.5625</v>
       </c>
       <c r="B56">
-        <v>181</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46226.57291666666</v>
+        <v>46228.57291666666</v>
       </c>
       <c r="B57">
-        <v>161</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46226.58333333334</v>
+        <v>46228.58333333334</v>
       </c>
       <c r="B58">
-        <v>167</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46226.59375</v>
+        <v>46228.59375</v>
       </c>
       <c r="B59">
-        <v>164</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46226.60416666666</v>
+        <v>46228.60416666666</v>
       </c>
       <c r="B60">
-        <v>158</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46226.61458333334</v>
+        <v>46228.61458333334</v>
       </c>
       <c r="B61">
-        <v>144</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46226.625</v>
+        <v>46228.625</v>
       </c>
       <c r="B62">
-        <v>142</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46226.63541666666</v>
+        <v>46228.63541666666</v>
       </c>
       <c r="B63">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46226.64583333334</v>
+        <v>46228.64583333334</v>
       </c>
       <c r="B64">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46226.65625</v>
+        <v>46228.65625</v>
       </c>
       <c r="B65">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46226.66666666666</v>
+        <v>46228.66666666666</v>
       </c>
       <c r="B66">
-        <v>244</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46226.67708333334</v>
+        <v>46228.67708333334</v>
       </c>
       <c r="B67">
-        <v>250</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46226.6875</v>
+        <v>46228.6875</v>
       </c>
       <c r="B68">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46226.69791666666</v>
+        <v>46228.69791666666</v>
       </c>
       <c r="B69">
-        <v>275</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46226.70833333334</v>
+        <v>46228.70833333334</v>
       </c>
       <c r="B70">
-        <v>654</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46226.71875</v>
+        <v>46228.71875</v>
       </c>
       <c r="B71">
-        <v>659</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46226.72916666666</v>
+        <v>46228.72916666666</v>
       </c>
       <c r="B72">
-        <v>662</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46226.73958333334</v>
+        <v>46228.73958333334</v>
       </c>
       <c r="B73">
-        <v>660</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46226.75</v>
+        <v>46228.75</v>
       </c>
       <c r="B74">
-        <v>711</v>
+        <v>553</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46226.76041666666</v>
+        <v>46228.76041666666</v>
       </c>
       <c r="B75">
-        <v>723</v>
+        <v>571</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46226.77083333334</v>
+        <v>46228.77083333334</v>
       </c>
       <c r="B76">
-        <v>724</v>
+        <v>564</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46226.78125</v>
+        <v>46228.78125</v>
       </c>
       <c r="B77">
-        <v>728</v>
+        <v>576</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46226.79166666666</v>
+        <v>46228.79166666666</v>
       </c>
       <c r="B78">
-        <v>858</v>
+        <v>628</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46226.80208333334</v>
+        <v>46228.80208333334</v>
       </c>
       <c r="B79">
-        <v>868</v>
+        <v>622</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46226.8125</v>
+        <v>46228.8125</v>
       </c>
       <c r="B80">
-        <v>865</v>
+        <v>618</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46226.82291666666</v>
+        <v>46228.82291666666</v>
       </c>
       <c r="B81">
-        <v>867</v>
+        <v>619</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46226.83333333334</v>
+        <v>46228.83333333334</v>
       </c>
       <c r="B82">
-        <v>856</v>
+        <v>649</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46226.84375</v>
+        <v>46228.84375</v>
       </c>
       <c r="B83">
-        <v>859</v>
+        <v>641</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46226.85416666666</v>
+        <v>46228.85416666666</v>
       </c>
       <c r="B84">
-        <v>859</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46226.86458333334</v>
+        <v>46228.86458333334</v>
       </c>
       <c r="B85">
-        <v>857</v>
+        <v>631</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46226.875</v>
+        <v>46228.875</v>
       </c>
       <c r="B86">
-        <v>775</v>
+        <v>575</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46226.88541666666</v>
+        <v>46228.88541666666</v>
       </c>
       <c r="B87">
-        <v>771</v>
+        <v>580</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46226.89583333334</v>
+        <v>46228.89583333334</v>
       </c>
       <c r="B88">
-        <v>760</v>
+        <v>585</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46226.90625</v>
+        <v>46228.90625</v>
       </c>
       <c r="B89">
-        <v>751</v>
+        <v>585</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46226.91666666666</v>
+        <v>46228.91666666666</v>
       </c>
       <c r="B90">
-        <v>676</v>
+        <v>505</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46226.92708333334</v>
+        <v>46228.92708333334</v>
       </c>
       <c r="B91">
-        <v>675</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46226.9375</v>
+        <v>46228.9375</v>
       </c>
       <c r="B92">
-        <v>675</v>
+        <v>501</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46226.94791666666</v>
+        <v>46228.94791666666</v>
       </c>
       <c r="B93">
-        <v>671</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46226.95833333334</v>
+        <v>46228.95833333334</v>
       </c>
       <c r="B94">
-        <v>526</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46226.96875</v>
+        <v>46228.96875</v>
       </c>
       <c r="B95">
-        <v>524</v>
+        <v>448</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46226.97916666666</v>
+        <v>46228.97916666666</v>
       </c>
       <c r="B96">
-        <v>523</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46226.98958333334</v>
+        <v>46228.98958333334</v>
       </c>
       <c r="B97">
-        <v>516</v>
+        <v>448</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B98">
-        <v>472</v>
+        <v>388</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B99">
-        <v>511</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B100">
-        <v>511</v>
+        <v>384</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B101">
-        <v>510</v>
+        <v>384</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B102">
-        <v>476</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B103">
-        <v>475</v>
+        <v>307</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B104">
-        <v>475</v>
+        <v>305</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B105">
-        <v>486</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B106">
-        <v>466</v>
+        <v>293</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B107">
-        <v>463</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B108">
-        <v>465</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B109">
-        <v>463</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B110">
-        <v>475</v>
+        <v>307</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B111">
-        <v>474</v>
+        <v>306</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B112">
-        <v>474</v>
+        <v>306</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B113">
-        <v>475</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B114">
-        <v>500</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B115">
-        <v>490</v>
+        <v>313</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B116">
-        <v>485</v>
+        <v>314</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B117">
-        <v>507</v>
+        <v>322</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B118">
-        <v>553</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B119">
-        <v>552</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B120">
-        <v>550</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B121">
-        <v>565</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B122">
-        <v>642</v>
+        <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B123">
-        <v>629</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B124">
-        <v>615</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B125">
-        <v>620</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B126">
-        <v>586</v>
+        <v>134</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B127">
-        <v>486</v>
+        <v>129</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B128">
-        <v>484</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1018 +394,1178 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46228</v>
+        <v>46245</v>
       </c>
       <c r="B2">
-        <v>378</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46228.01041666666</v>
+        <v>46245.01041666666</v>
       </c>
       <c r="B3">
-        <v>368</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46228.02083333334</v>
+        <v>46245.02083333334</v>
       </c>
       <c r="B4">
-        <v>364</v>
+        <v>725</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46228.03125</v>
+        <v>46245.03125</v>
       </c>
       <c r="B5">
-        <v>364</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46228.04166666666</v>
+        <v>46245.04166666666</v>
       </c>
       <c r="B6">
-        <v>362</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46228.05208333334</v>
+        <v>46245.05208333334</v>
       </c>
       <c r="B7">
-        <v>360</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46228.0625</v>
+        <v>46245.0625</v>
       </c>
       <c r="B8">
-        <v>361</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46228.07291666666</v>
+        <v>46245.07291666666</v>
       </c>
       <c r="B9">
-        <v>360</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46228.08333333334</v>
+        <v>46245.08333333334</v>
       </c>
       <c r="B10">
-        <v>360</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46228.09375</v>
+        <v>46245.09375</v>
       </c>
       <c r="B11">
-        <v>361</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46228.10416666666</v>
+        <v>46245.10416666666</v>
       </c>
       <c r="B12">
-        <v>360</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46228.11458333334</v>
+        <v>46245.11458333334</v>
       </c>
       <c r="B13">
-        <v>355</v>
+        <v>684</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46228.125</v>
+        <v>46245.125</v>
       </c>
       <c r="B14">
-        <v>340</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46228.13541666666</v>
+        <v>46245.13541666666</v>
       </c>
       <c r="B15">
-        <v>350</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46228.14583333334</v>
+        <v>46245.14583333334</v>
       </c>
       <c r="B16">
-        <v>339</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46228.15625</v>
+        <v>46245.15625</v>
       </c>
       <c r="B17">
-        <v>340</v>
+        <v>681</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46228.16666666666</v>
+        <v>46245.16666666666</v>
       </c>
       <c r="B18">
-        <v>341</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46228.17708333334</v>
+        <v>46245.17708333334</v>
       </c>
       <c r="B19">
-        <v>341</v>
+        <v>711</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46228.1875</v>
+        <v>46245.1875</v>
       </c>
       <c r="B20">
-        <v>340</v>
+        <v>712</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46228.19791666666</v>
+        <v>46245.19791666666</v>
       </c>
       <c r="B21">
-        <v>346</v>
+        <v>714</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46228.20833333334</v>
+        <v>46245.20833333334</v>
       </c>
       <c r="B22">
-        <v>382</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46228.21875</v>
+        <v>46245.21875</v>
       </c>
       <c r="B23">
-        <v>320</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46228.22916666666</v>
+        <v>46245.22916666666</v>
       </c>
       <c r="B24">
-        <v>318</v>
+        <v>715</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46228.23958333334</v>
+        <v>46245.23958333334</v>
       </c>
       <c r="B25">
-        <v>318</v>
+        <v>717</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46228.25</v>
+        <v>46245.25</v>
       </c>
       <c r="B26">
-        <v>361</v>
+        <v>775</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46228.26041666666</v>
+        <v>46245.26041666666</v>
       </c>
       <c r="B27">
-        <v>358</v>
+        <v>779</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46228.27083333334</v>
+        <v>46245.27083333334</v>
       </c>
       <c r="B28">
-        <v>344</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46228.28125</v>
+        <v>46245.28125</v>
       </c>
       <c r="B29">
-        <v>334</v>
+        <v>776</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46228.29166666666</v>
+        <v>46245.29166666666</v>
       </c>
       <c r="B30">
-        <v>146</v>
+        <v>739</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46228.30208333334</v>
+        <v>46245.30208333334</v>
       </c>
       <c r="B31">
-        <v>132</v>
+        <v>724</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46228.3125</v>
+        <v>46245.3125</v>
       </c>
       <c r="B32">
-        <v>138</v>
+        <v>721</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46228.32291666666</v>
+        <v>46245.32291666666</v>
       </c>
       <c r="B33">
-        <v>138</v>
+        <v>723</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46228.33333333334</v>
+        <v>46245.33333333334</v>
       </c>
       <c r="B34">
-        <v>151</v>
+        <v>633</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46228.34375</v>
+        <v>46245.34375</v>
       </c>
       <c r="B35">
-        <v>138</v>
+        <v>624</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46228.35416666666</v>
+        <v>46245.35416666666</v>
       </c>
       <c r="B36">
-        <v>121</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46228.36458333334</v>
+        <v>46245.36458333334</v>
       </c>
       <c r="B37">
-        <v>125</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46228.375</v>
+        <v>46245.375</v>
       </c>
       <c r="B38">
-        <v>107</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46228.38541666666</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="B39">
-        <v>102</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46228.39583333334</v>
+        <v>46245.39583333334</v>
       </c>
       <c r="B40">
-        <v>104</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46228.40625</v>
+        <v>46245.40625</v>
       </c>
       <c r="B41">
-        <v>102</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46228.41666666666</v>
+        <v>46245.41666666666</v>
       </c>
       <c r="B42">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46228.42708333334</v>
+        <v>46245.42708333334</v>
       </c>
       <c r="B43">
-        <v>96</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46228.4375</v>
+        <v>46245.4375</v>
       </c>
       <c r="B44">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46228.44791666666</v>
+        <v>46245.44791666666</v>
       </c>
       <c r="B45">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46228.45833333334</v>
+        <v>46245.45833333334</v>
       </c>
       <c r="B46">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46228.46875</v>
+        <v>46245.46875</v>
       </c>
       <c r="B47">
-        <v>91</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46228.47916666666</v>
+        <v>46245.47916666666</v>
       </c>
       <c r="B48">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46228.48958333334</v>
+        <v>46245.48958333334</v>
       </c>
       <c r="B49">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46228.5</v>
+        <v>46245.5</v>
       </c>
       <c r="B50">
-        <v>94</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46228.51041666666</v>
+        <v>46245.51041666666</v>
       </c>
       <c r="B51">
-        <v>92</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46228.52083333334</v>
+        <v>46245.52083333334</v>
       </c>
       <c r="B52">
-        <v>90</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46228.53125</v>
+        <v>46245.53125</v>
       </c>
       <c r="B53">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46228.54166666666</v>
+        <v>46245.54166666666</v>
       </c>
       <c r="B54">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46228.55208333334</v>
+        <v>46245.55208333334</v>
       </c>
       <c r="B55">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46228.5625</v>
+        <v>46245.5625</v>
       </c>
       <c r="B56">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46228.57291666666</v>
+        <v>46245.57291666666</v>
       </c>
       <c r="B57">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46228.58333333334</v>
+        <v>46245.58333333334</v>
       </c>
       <c r="B58">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46228.59375</v>
+        <v>46245.59375</v>
       </c>
       <c r="B59">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46228.60416666666</v>
+        <v>46245.60416666666</v>
       </c>
       <c r="B60">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46228.61458333334</v>
+        <v>46245.61458333334</v>
       </c>
       <c r="B61">
-        <v>91</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46228.625</v>
+        <v>46245.625</v>
       </c>
       <c r="B62">
-        <v>91</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46228.63541666666</v>
+        <v>46245.63541666666</v>
       </c>
       <c r="B63">
-        <v>91</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46228.64583333334</v>
+        <v>46245.64583333334</v>
       </c>
       <c r="B64">
-        <v>92</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46228.65625</v>
+        <v>46245.65625</v>
       </c>
       <c r="B65">
-        <v>92</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46228.66666666666</v>
+        <v>46245.66666666666</v>
       </c>
       <c r="B66">
-        <v>102</v>
+        <v>910</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46228.67708333334</v>
+        <v>46245.67708333334</v>
       </c>
       <c r="B67">
-        <v>102</v>
+        <v>938</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46228.6875</v>
+        <v>46245.6875</v>
       </c>
       <c r="B68">
-        <v>108</v>
+        <v>939</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46228.69791666666</v>
+        <v>46245.69791666666</v>
       </c>
       <c r="B69">
-        <v>117</v>
+        <v>943</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46228.70833333334</v>
+        <v>46245.70833333334</v>
       </c>
       <c r="B70">
-        <v>130</v>
+        <v>868</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46228.71875</v>
+        <v>46245.71875</v>
       </c>
       <c r="B71">
-        <v>134</v>
+        <v>860</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46228.72916666666</v>
+        <v>46245.72916666666</v>
       </c>
       <c r="B72">
-        <v>134</v>
+        <v>858</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46228.73958333334</v>
+        <v>46245.73958333334</v>
       </c>
       <c r="B73">
-        <v>161</v>
+        <v>856</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46228.75</v>
+        <v>46245.75</v>
       </c>
       <c r="B74">
-        <v>553</v>
+        <v>751</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46228.76041666666</v>
+        <v>46245.76041666666</v>
       </c>
       <c r="B75">
-        <v>571</v>
+        <v>754</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46228.77083333334</v>
+        <v>46245.77083333334</v>
       </c>
       <c r="B76">
-        <v>564</v>
+        <v>763</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46228.78125</v>
+        <v>46245.78125</v>
       </c>
       <c r="B77">
-        <v>576</v>
+        <v>773</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46228.79166666666</v>
+        <v>46245.79166666666</v>
       </c>
       <c r="B78">
-        <v>628</v>
+        <v>795</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46228.80208333334</v>
+        <v>46245.80208333334</v>
       </c>
       <c r="B79">
-        <v>622</v>
+        <v>829</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46228.8125</v>
+        <v>46245.8125</v>
       </c>
       <c r="B80">
-        <v>618</v>
+        <v>815</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46228.82291666666</v>
+        <v>46245.82291666666</v>
       </c>
       <c r="B81">
-        <v>619</v>
+        <v>821</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46228.83333333334</v>
+        <v>46245.83333333334</v>
       </c>
       <c r="B82">
-        <v>649</v>
+        <v>850</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46228.84375</v>
+        <v>46245.84375</v>
       </c>
       <c r="B83">
-        <v>641</v>
+        <v>853</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46228.85416666666</v>
+        <v>46245.85416666666</v>
       </c>
       <c r="B84">
-        <v>653</v>
+        <v>853</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46228.86458333334</v>
+        <v>46245.86458333334</v>
       </c>
       <c r="B85">
-        <v>631</v>
+        <v>850</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46228.875</v>
+        <v>46245.875</v>
       </c>
       <c r="B86">
-        <v>575</v>
+        <v>814</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46228.88541666666</v>
+        <v>46245.88541666666</v>
       </c>
       <c r="B87">
-        <v>580</v>
+        <v>803</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46228.89583333334</v>
+        <v>46245.89583333334</v>
       </c>
       <c r="B88">
-        <v>585</v>
+        <v>793</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46228.90625</v>
+        <v>46245.90625</v>
       </c>
       <c r="B89">
-        <v>585</v>
+        <v>789</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46228.91666666666</v>
+        <v>46245.91666666666</v>
       </c>
       <c r="B90">
-        <v>505</v>
+        <v>659</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46228.92708333334</v>
+        <v>46245.92708333334</v>
       </c>
       <c r="B91">
-        <v>500</v>
+        <v>642</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46228.9375</v>
+        <v>46245.9375</v>
       </c>
       <c r="B92">
-        <v>501</v>
+        <v>642</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46228.94791666666</v>
+        <v>46245.94791666666</v>
       </c>
       <c r="B93">
-        <v>500</v>
+        <v>641</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46228.95833333334</v>
+        <v>46245.95833333334</v>
       </c>
       <c r="B94">
-        <v>452</v>
+        <v>593</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46228.96875</v>
+        <v>46245.96875</v>
       </c>
       <c r="B95">
-        <v>448</v>
+        <v>582</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46228.97916666666</v>
+        <v>46245.97916666666</v>
       </c>
       <c r="B96">
-        <v>449</v>
+        <v>581</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46228.98958333334</v>
+        <v>46245.98958333334</v>
       </c>
       <c r="B97">
-        <v>448</v>
+        <v>580</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B98">
-        <v>388</v>
+        <v>633</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B99">
-        <v>386</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B100">
-        <v>384</v>
+        <v>629</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B101">
-        <v>384</v>
+        <v>628</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B102">
-        <v>305</v>
+        <v>616</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B103">
-        <v>307</v>
+        <v>614</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B104">
-        <v>305</v>
+        <v>615</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B105">
-        <v>303</v>
+        <v>614</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B106">
-        <v>293</v>
+        <v>667</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B107">
-        <v>291</v>
+        <v>664</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B108">
-        <v>289</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B109">
-        <v>288</v>
+        <v>639</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B110">
-        <v>307</v>
+        <v>630</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B111">
-        <v>306</v>
+        <v>631</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B112">
-        <v>306</v>
+        <v>635</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B113">
-        <v>307</v>
+        <v>634</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B114">
-        <v>314</v>
+        <v>661</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B115">
-        <v>313</v>
+        <v>662</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B116">
-        <v>314</v>
+        <v>663</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B117">
-        <v>322</v>
+        <v>671</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B118">
-        <v>290</v>
+        <v>708</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B119">
-        <v>287</v>
+        <v>706</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B120">
-        <v>284</v>
+        <v>698</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B121">
-        <v>284</v>
+        <v>718</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B122">
-        <v>306</v>
+        <v>731</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B123">
-        <v>309</v>
+        <v>709</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B124">
-        <v>313</v>
+        <v>700</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B125">
-        <v>317</v>
+        <v>699</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B126">
-        <v>134</v>
+        <v>719</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B127">
-        <v>129</v>
+        <v>732</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B128">
-        <v>128</v>
+        <v>763</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46246.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46246.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46246.34375</v>
+      </c>
+      <c r="B131">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46246.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46246.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46246.375</v>
+      </c>
+      <c r="B134">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46246.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46246.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46246.40625</v>
+      </c>
+      <c r="B137">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46246.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46246.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46246.4375</v>
+      </c>
+      <c r="B140">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46246.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46246.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46246.46875</v>
+      </c>
+      <c r="B143">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46246.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46246.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46246.5</v>
+      </c>
+      <c r="B146">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46246.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46246.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B419"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,455 +394,455 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B2">
-        <v>729</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46245.01041666666</v>
+        <v>46247.01041666666</v>
       </c>
       <c r="B3">
-        <v>724</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46245.02083333334</v>
+        <v>46247.02083333334</v>
       </c>
       <c r="B4">
-        <v>725</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46245.03125</v>
+        <v>46247.03125</v>
       </c>
       <c r="B5">
-        <v>724</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46245.04166666666</v>
+        <v>46247.04166666666</v>
       </c>
       <c r="B6">
-        <v>702</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46245.05208333334</v>
+        <v>46247.05208333334</v>
       </c>
       <c r="B7">
-        <v>700</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46245.0625</v>
+        <v>46247.0625</v>
       </c>
       <c r="B8">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46245.07291666666</v>
+        <v>46247.07291666666</v>
       </c>
       <c r="B9">
-        <v>698</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46245.08333333334</v>
+        <v>46247.08333333334</v>
       </c>
       <c r="B10">
-        <v>686</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46245.09375</v>
+        <v>46247.09375</v>
       </c>
       <c r="B11">
-        <v>684</v>
+        <v>709</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46245.10416666666</v>
+        <v>46247.10416666666</v>
       </c>
       <c r="B12">
-        <v>683</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46245.11458333334</v>
+        <v>46247.11458333334</v>
       </c>
       <c r="B13">
-        <v>684</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46245.125</v>
+        <v>46247.125</v>
       </c>
       <c r="B14">
-        <v>685</v>
+        <v>709</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46245.13541666666</v>
+        <v>46247.13541666666</v>
       </c>
       <c r="B15">
-        <v>683</v>
+        <v>708</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46245.14583333334</v>
+        <v>46247.14583333334</v>
       </c>
       <c r="B16">
-        <v>684</v>
+        <v>708</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46245.15625</v>
+        <v>46247.15625</v>
       </c>
       <c r="B17">
-        <v>681</v>
+        <v>708</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46245.16666666666</v>
+        <v>46247.16666666666</v>
       </c>
       <c r="B18">
-        <v>704</v>
+        <v>726</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46245.17708333334</v>
+        <v>46247.17708333334</v>
       </c>
       <c r="B19">
-        <v>711</v>
+        <v>727</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46245.1875</v>
+        <v>46247.1875</v>
       </c>
       <c r="B20">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46245.19791666666</v>
+        <v>46247.19791666666</v>
       </c>
       <c r="B21">
-        <v>714</v>
+        <v>731</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46245.20833333334</v>
+        <v>46247.20833333334</v>
       </c>
       <c r="B22">
-        <v>731</v>
+        <v>691</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46245.21875</v>
+        <v>46247.21875</v>
       </c>
       <c r="B23">
-        <v>719</v>
+        <v>683</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46245.22916666666</v>
+        <v>46247.22916666666</v>
       </c>
       <c r="B24">
-        <v>715</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46245.23958333334</v>
+        <v>46247.23958333334</v>
       </c>
       <c r="B25">
-        <v>717</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46245.25</v>
+        <v>46247.25</v>
       </c>
       <c r="B26">
-        <v>775</v>
+        <v>883</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46245.26041666666</v>
+        <v>46247.26041666666</v>
       </c>
       <c r="B27">
-        <v>779</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46245.27083333334</v>
+        <v>46247.27083333334</v>
       </c>
       <c r="B28">
-        <v>771</v>
+        <v>914</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46245.28125</v>
+        <v>46247.28125</v>
       </c>
       <c r="B29">
-        <v>776</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46245.29166666666</v>
+        <v>46247.29166666666</v>
       </c>
       <c r="B30">
-        <v>739</v>
+        <v>988</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46245.30208333334</v>
+        <v>46247.30208333334</v>
       </c>
       <c r="B31">
-        <v>724</v>
+        <v>978</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46245.3125</v>
+        <v>46247.3125</v>
       </c>
       <c r="B32">
-        <v>721</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46245.32291666666</v>
+        <v>46247.32291666666</v>
       </c>
       <c r="B33">
-        <v>723</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46245.33333333334</v>
+        <v>46247.33333333334</v>
       </c>
       <c r="B34">
-        <v>633</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46245.34375</v>
+        <v>46247.34375</v>
       </c>
       <c r="B35">
-        <v>624</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46245.35416666666</v>
+        <v>46247.35416666666</v>
       </c>
       <c r="B36">
-        <v>611</v>
+        <v>868</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46245.36458333334</v>
+        <v>46247.36458333334</v>
       </c>
       <c r="B37">
-        <v>609</v>
+        <v>843</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46245.375</v>
+        <v>46247.375</v>
       </c>
       <c r="B38">
-        <v>463</v>
+        <v>770</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46245.38541666666</v>
+        <v>46247.38541666666</v>
       </c>
       <c r="B39">
-        <v>463</v>
+        <v>765</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46245.39583333334</v>
+        <v>46247.39583333334</v>
       </c>
       <c r="B40">
-        <v>474</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46245.40625</v>
+        <v>46247.40625</v>
       </c>
       <c r="B41">
-        <v>462</v>
+        <v>707</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46245.41666666666</v>
+        <v>46247.41666666666</v>
       </c>
       <c r="B42">
-        <v>94</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46245.42708333334</v>
+        <v>46247.42708333334</v>
       </c>
       <c r="B43">
-        <v>70</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46245.4375</v>
+        <v>46247.4375</v>
       </c>
       <c r="B44">
-        <v>67</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46245.44791666666</v>
+        <v>46247.44791666666</v>
       </c>
       <c r="B45">
-        <v>66</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46245.45833333334</v>
+        <v>46247.45833333334</v>
       </c>
       <c r="B46">
-        <v>59</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46245.46875</v>
+        <v>46247.46875</v>
       </c>
       <c r="B47">
-        <v>56</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46245.47916666666</v>
+        <v>46247.47916666666</v>
       </c>
       <c r="B48">
-        <v>54</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46245.48958333334</v>
+        <v>46247.48958333334</v>
       </c>
       <c r="B49">
-        <v>54</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46245.5</v>
+        <v>46247.5</v>
       </c>
       <c r="B50">
-        <v>55</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46245.51041666666</v>
+        <v>46247.51041666666</v>
       </c>
       <c r="B51">
-        <v>54</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46245.52083333334</v>
+        <v>46247.52083333334</v>
       </c>
       <c r="B52">
-        <v>55</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46245.53125</v>
+        <v>46247.53125</v>
       </c>
       <c r="B53">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46245.54166666666</v>
+        <v>46247.54166666666</v>
       </c>
       <c r="B54">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46245.55208333334</v>
+        <v>46247.55208333334</v>
       </c>
       <c r="B55">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46245.5625</v>
+        <v>46247.5625</v>
       </c>
       <c r="B56">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46245.57291666666</v>
+        <v>46247.57291666666</v>
       </c>
       <c r="B57">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46245.58333333334</v>
+        <v>46247.58333333334</v>
       </c>
       <c r="B58">
         <v>50</v>
@@ -850,722 +850,2890 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46245.59375</v>
+        <v>46247.59375</v>
       </c>
       <c r="B59">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46245.60416666666</v>
+        <v>46247.60416666666</v>
       </c>
       <c r="B60">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46245.61458333334</v>
+        <v>46247.61458333334</v>
       </c>
       <c r="B61">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46245.625</v>
+        <v>46247.625</v>
       </c>
       <c r="B62">
-        <v>352</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46245.63541666666</v>
+        <v>46247.63541666666</v>
       </c>
       <c r="B63">
-        <v>363</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46245.64583333334</v>
+        <v>46247.64583333334</v>
       </c>
       <c r="B64">
-        <v>362</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46245.65625</v>
+        <v>46247.65625</v>
       </c>
       <c r="B65">
-        <v>384</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46245.66666666666</v>
+        <v>46247.66666666666</v>
       </c>
       <c r="B66">
-        <v>910</v>
+        <v>684</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46245.67708333334</v>
+        <v>46247.67708333334</v>
       </c>
       <c r="B67">
-        <v>938</v>
+        <v>718</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46245.6875</v>
+        <v>46247.6875</v>
       </c>
       <c r="B68">
-        <v>939</v>
+        <v>697</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46245.69791666666</v>
+        <v>46247.69791666666</v>
       </c>
       <c r="B69">
-        <v>943</v>
+        <v>719</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46245.70833333334</v>
+        <v>46247.70833333334</v>
       </c>
       <c r="B70">
-        <v>868</v>
+        <v>757</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46245.71875</v>
+        <v>46247.71875</v>
       </c>
       <c r="B71">
-        <v>860</v>
+        <v>679</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46245.72916666666</v>
+        <v>46247.72916666666</v>
       </c>
       <c r="B72">
-        <v>858</v>
+        <v>759</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46245.73958333334</v>
+        <v>46247.73958333334</v>
       </c>
       <c r="B73">
-        <v>856</v>
+        <v>778</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46245.75</v>
+        <v>46247.75</v>
       </c>
       <c r="B74">
-        <v>751</v>
+        <v>795</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46245.76041666666</v>
+        <v>46247.76041666666</v>
       </c>
       <c r="B75">
-        <v>754</v>
+        <v>801</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46245.77083333334</v>
+        <v>46247.77083333334</v>
       </c>
       <c r="B76">
-        <v>763</v>
+        <v>787</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46245.78125</v>
+        <v>46247.78125</v>
       </c>
       <c r="B77">
-        <v>773</v>
+        <v>805</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46245.79166666666</v>
+        <v>46247.79166666666</v>
       </c>
       <c r="B78">
-        <v>795</v>
+        <v>833</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46245.80208333334</v>
+        <v>46247.80208333334</v>
       </c>
       <c r="B79">
-        <v>829</v>
+        <v>851</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46245.8125</v>
+        <v>46247.8125</v>
       </c>
       <c r="B80">
-        <v>815</v>
+        <v>804</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46245.82291666666</v>
+        <v>46247.82291666666</v>
       </c>
       <c r="B81">
-        <v>821</v>
+        <v>784</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46245.83333333334</v>
+        <v>46247.83333333334</v>
       </c>
       <c r="B82">
-        <v>850</v>
+        <v>797</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46245.84375</v>
+        <v>46247.84375</v>
       </c>
       <c r="B83">
-        <v>853</v>
+        <v>802</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46245.85416666666</v>
+        <v>46247.85416666666</v>
       </c>
       <c r="B84">
-        <v>853</v>
+        <v>820</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46245.86458333334</v>
+        <v>46247.86458333334</v>
       </c>
       <c r="B85">
-        <v>850</v>
+        <v>817</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46245.875</v>
+        <v>46247.875</v>
       </c>
       <c r="B86">
-        <v>814</v>
+        <v>757</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46245.88541666666</v>
+        <v>46247.88541666666</v>
       </c>
       <c r="B87">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46245.89583333334</v>
+        <v>46247.89583333334</v>
       </c>
       <c r="B88">
-        <v>793</v>
+        <v>809</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46245.90625</v>
+        <v>46247.90625</v>
       </c>
       <c r="B89">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46245.91666666666</v>
+        <v>46247.91666666666</v>
       </c>
       <c r="B90">
-        <v>659</v>
+        <v>680</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46245.92708333334</v>
+        <v>46247.92708333334</v>
       </c>
       <c r="B91">
-        <v>642</v>
+        <v>675</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46245.9375</v>
+        <v>46247.9375</v>
       </c>
       <c r="B92">
-        <v>642</v>
+        <v>680</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46245.94791666666</v>
+        <v>46247.94791666666</v>
       </c>
       <c r="B93">
-        <v>641</v>
+        <v>680</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46245.95833333334</v>
+        <v>46247.95833333334</v>
       </c>
       <c r="B94">
-        <v>593</v>
+        <v>790</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46245.96875</v>
+        <v>46247.96875</v>
       </c>
       <c r="B95">
-        <v>582</v>
+        <v>787</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46245.97916666666</v>
+        <v>46247.97916666666</v>
       </c>
       <c r="B96">
-        <v>581</v>
+        <v>789</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46245.98958333334</v>
+        <v>46247.98958333334</v>
       </c>
       <c r="B97">
-        <v>580</v>
+        <v>775</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B98">
-        <v>633</v>
+        <v>769</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46246.01041666666</v>
+        <v>46248.01041666666</v>
       </c>
       <c r="B99">
-        <v>632</v>
+        <v>762</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46246.02083333334</v>
+        <v>46248.02083333334</v>
       </c>
       <c r="B100">
-        <v>629</v>
+        <v>762</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46246.03125</v>
+        <v>46248.03125</v>
       </c>
       <c r="B101">
-        <v>628</v>
+        <v>763</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46246.04166666666</v>
+        <v>46248.04166666666</v>
       </c>
       <c r="B102">
-        <v>616</v>
+        <v>743</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46246.05208333334</v>
+        <v>46248.05208333334</v>
       </c>
       <c r="B103">
-        <v>614</v>
+        <v>739</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46246.0625</v>
+        <v>46248.0625</v>
       </c>
       <c r="B104">
-        <v>615</v>
+        <v>740</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46246.07291666666</v>
+        <v>46248.07291666666</v>
       </c>
       <c r="B105">
-        <v>614</v>
+        <v>740</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46246.08333333334</v>
+        <v>46248.08333333334</v>
       </c>
       <c r="B106">
-        <v>667</v>
+        <v>741</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46246.09375</v>
+        <v>46248.09375</v>
       </c>
       <c r="B107">
-        <v>664</v>
+        <v>740</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46246.10416666666</v>
+        <v>46248.10416666666</v>
       </c>
       <c r="B108">
-        <v>600</v>
+        <v>741</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46246.11458333334</v>
+        <v>46248.11458333334</v>
       </c>
       <c r="B109">
-        <v>639</v>
+        <v>739</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46246.125</v>
+        <v>46248.125</v>
       </c>
       <c r="B110">
-        <v>630</v>
+        <v>741</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46246.13541666666</v>
+        <v>46248.13541666666</v>
       </c>
       <c r="B111">
-        <v>631</v>
+        <v>740</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46246.14583333334</v>
+        <v>46248.14583333334</v>
       </c>
       <c r="B112">
-        <v>635</v>
+        <v>740</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46246.15625</v>
+        <v>46248.15625</v>
       </c>
       <c r="B113">
-        <v>634</v>
+        <v>738</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46246.16666666666</v>
+        <v>46248.16666666666</v>
       </c>
       <c r="B114">
-        <v>661</v>
+        <v>739</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46246.17708333334</v>
+        <v>46248.17708333334</v>
       </c>
       <c r="B115">
-        <v>662</v>
+        <v>742</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46246.1875</v>
+        <v>46248.1875</v>
       </c>
       <c r="B116">
-        <v>663</v>
+        <v>742</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46246.19791666666</v>
+        <v>46248.19791666666</v>
       </c>
       <c r="B117">
-        <v>671</v>
+        <v>747</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46246.20833333334</v>
+        <v>46248.20833333334</v>
       </c>
       <c r="B118">
-        <v>708</v>
+        <v>773</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46246.21875</v>
+        <v>46248.21875</v>
       </c>
       <c r="B119">
-        <v>706</v>
+        <v>770</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46246.22916666666</v>
+        <v>46248.22916666666</v>
       </c>
       <c r="B120">
-        <v>698</v>
+        <v>764</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46246.23958333334</v>
+        <v>46248.23958333334</v>
       </c>
       <c r="B121">
-        <v>718</v>
+        <v>757</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46246.25</v>
+        <v>46248.25</v>
       </c>
       <c r="B122">
-        <v>731</v>
+        <v>835</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46246.26041666666</v>
+        <v>46248.26041666666</v>
       </c>
       <c r="B123">
-        <v>709</v>
+        <v>843</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46246.27083333334</v>
+        <v>46248.27083333334</v>
       </c>
       <c r="B124">
-        <v>700</v>
+        <v>843</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46246.28125</v>
+        <v>46248.28125</v>
       </c>
       <c r="B125">
-        <v>699</v>
+        <v>843</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46246.29166666666</v>
+        <v>46248.29166666666</v>
       </c>
       <c r="B126">
-        <v>719</v>
+        <v>847</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46246.30208333334</v>
+        <v>46248.30208333334</v>
       </c>
       <c r="B127">
-        <v>732</v>
+        <v>842</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46246.3125</v>
+        <v>46248.3125</v>
       </c>
       <c r="B128">
-        <v>763</v>
+        <v>840</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46246.32291666666</v>
+        <v>46248.32291666666</v>
       </c>
       <c r="B129">
-        <v>770</v>
+        <v>843</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46246.33333333334</v>
+        <v>46248.33333333334</v>
       </c>
       <c r="B130">
-        <v>437</v>
+        <v>725</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46246.34375</v>
+        <v>46248.34375</v>
       </c>
       <c r="B131">
-        <v>419</v>
+        <v>750</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46246.35416666666</v>
+        <v>46248.35416666666</v>
       </c>
       <c r="B132">
-        <v>422</v>
+        <v>743</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46246.36458333334</v>
+        <v>46248.36458333334</v>
       </c>
       <c r="B133">
-        <v>422</v>
+        <v>721</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46246.375</v>
+        <v>46248.375</v>
       </c>
       <c r="B134">
-        <v>143</v>
+        <v>479</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46246.38541666666</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="B135">
-        <v>114</v>
+        <v>470</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46246.39583333334</v>
+        <v>46248.39583333334</v>
       </c>
       <c r="B136">
-        <v>113</v>
+        <v>464</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46246.40625</v>
+        <v>46248.40625</v>
       </c>
       <c r="B137">
-        <v>101</v>
+        <v>462</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46246.41666666666</v>
+        <v>46248.41666666666</v>
       </c>
       <c r="B138">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46246.42708333334</v>
+        <v>46248.42708333334</v>
       </c>
       <c r="B139">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46246.4375</v>
+        <v>46248.4375</v>
       </c>
       <c r="B140">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46246.44791666666</v>
+        <v>46248.44791666666</v>
       </c>
       <c r="B141">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46246.45833333334</v>
+        <v>46248.45833333334</v>
       </c>
       <c r="B142">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46246.46875</v>
+        <v>46248.46875</v>
       </c>
       <c r="B143">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46246.47916666666</v>
+        <v>46248.47916666666</v>
       </c>
       <c r="B144">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46246.48958333334</v>
+        <v>46248.48958333334</v>
       </c>
       <c r="B145">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46246.5</v>
+        <v>46248.5</v>
       </c>
       <c r="B146">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46246.51041666666</v>
+        <v>46248.51041666666</v>
       </c>
       <c r="B147">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46246.52083333334</v>
+        <v>46248.52083333334</v>
       </c>
       <c r="B148">
-        <v>27</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46248.53125</v>
+      </c>
+      <c r="B149">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46248.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46248.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46248.5625</v>
+      </c>
+      <c r="B152">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46248.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46248.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46248.59375</v>
+      </c>
+      <c r="B155">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46248.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46248.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46248.625</v>
+      </c>
+      <c r="B158">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46248.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46248.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46248.65625</v>
+      </c>
+      <c r="B161">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46248.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46248.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46248.6875</v>
+      </c>
+      <c r="B164">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46248.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46248.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46248.71875</v>
+      </c>
+      <c r="B167">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46248.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46248.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46248.75</v>
+      </c>
+      <c r="B170">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46248.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46248.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46248.78125</v>
+      </c>
+      <c r="B173">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46248.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46248.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46248.8125</v>
+      </c>
+      <c r="B176">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46248.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46248.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46248.84375</v>
+      </c>
+      <c r="B179">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46248.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46248.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46248.875</v>
+      </c>
+      <c r="B182">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46248.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46248.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46248.90625</v>
+      </c>
+      <c r="B185">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46248.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46248.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46248.9375</v>
+      </c>
+      <c r="B188">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46248.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46248.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46248.96875</v>
+      </c>
+      <c r="B191">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46248.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46248.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B194">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46249.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46249.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46249.03125</v>
+      </c>
+      <c r="B197">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46249.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46249.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46249.0625</v>
+      </c>
+      <c r="B200">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46249.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46249.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46249.09375</v>
+      </c>
+      <c r="B203">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46249.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46249.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46249.125</v>
+      </c>
+      <c r="B206">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46249.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46249.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46249.15625</v>
+      </c>
+      <c r="B209">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46249.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46249.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46249.1875</v>
+      </c>
+      <c r="B212">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46249.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46249.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46249.21875</v>
+      </c>
+      <c r="B215">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46249.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46249.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46249.25</v>
+      </c>
+      <c r="B218">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46249.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46249.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46249.28125</v>
+      </c>
+      <c r="B221">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46249.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46249.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46249.3125</v>
+      </c>
+      <c r="B224">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46249.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46249.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46249.34375</v>
+      </c>
+      <c r="B227">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46249.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46249.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46249.375</v>
+      </c>
+      <c r="B230">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46249.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46249.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46249.40625</v>
+      </c>
+      <c r="B233">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46249.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46249.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46249.4375</v>
+      </c>
+      <c r="B236">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46249.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46249.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46249.46875</v>
+      </c>
+      <c r="B239">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46249.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46249.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46249.5</v>
+      </c>
+      <c r="B242">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46249.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46249.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46249.53125</v>
+      </c>
+      <c r="B245">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46249.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46249.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46249.5625</v>
+      </c>
+      <c r="B248">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46249.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46249.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46249.59375</v>
+      </c>
+      <c r="B251">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46249.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46249.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46249.625</v>
+      </c>
+      <c r="B254">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46249.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46249.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46249.65625</v>
+      </c>
+      <c r="B257">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46249.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46249.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46249.6875</v>
+      </c>
+      <c r="B260">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46249.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46249.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46249.71875</v>
+      </c>
+      <c r="B263">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46249.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46249.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46249.75</v>
+      </c>
+      <c r="B266">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46249.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46249.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46249.78125</v>
+      </c>
+      <c r="B269">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46249.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46249.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46249.8125</v>
+      </c>
+      <c r="B272">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46249.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46249.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46249.84375</v>
+      </c>
+      <c r="B275">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46249.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46249.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46249.875</v>
+      </c>
+      <c r="B278">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46249.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46249.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46249.90625</v>
+      </c>
+      <c r="B281">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46249.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46249.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46249.9375</v>
+      </c>
+      <c r="B284">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46249.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46249.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46249.96875</v>
+      </c>
+      <c r="B287">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46249.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46249.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B290">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46250.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46250.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46250.03125</v>
+      </c>
+      <c r="B293">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46250.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46250.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46250.0625</v>
+      </c>
+      <c r="B296">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46250.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46250.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46250.09375</v>
+      </c>
+      <c r="B299">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46250.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46250.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46250.125</v>
+      </c>
+      <c r="B302">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46250.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46250.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46250.15625</v>
+      </c>
+      <c r="B305">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46250.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46250.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46250.1875</v>
+      </c>
+      <c r="B308">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46250.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46250.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46250.21875</v>
+      </c>
+      <c r="B311">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46250.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46250.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46250.25</v>
+      </c>
+      <c r="B314">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46250.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46250.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46250.28125</v>
+      </c>
+      <c r="B317">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46250.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46250.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46250.3125</v>
+      </c>
+      <c r="B320">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46250.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46250.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46250.34375</v>
+      </c>
+      <c r="B323">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46250.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46250.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46250.375</v>
+      </c>
+      <c r="B326">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46250.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46250.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46250.40625</v>
+      </c>
+      <c r="B329">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46250.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46250.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46250.4375</v>
+      </c>
+      <c r="B332">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46250.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46250.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46250.46875</v>
+      </c>
+      <c r="B335">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46250.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46250.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46250.5</v>
+      </c>
+      <c r="B338">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46250.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46250.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46250.53125</v>
+      </c>
+      <c r="B341">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46250.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46250.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46250.5625</v>
+      </c>
+      <c r="B344">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46250.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46250.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46250.59375</v>
+      </c>
+      <c r="B347">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46250.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46250.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46250.625</v>
+      </c>
+      <c r="B350">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46250.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46250.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46250.65625</v>
+      </c>
+      <c r="B353">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46250.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46250.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46250.6875</v>
+      </c>
+      <c r="B356">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46250.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46250.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46250.71875</v>
+      </c>
+      <c r="B359">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46250.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46250.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46250.75</v>
+      </c>
+      <c r="B362">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46250.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46250.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46250.78125</v>
+      </c>
+      <c r="B365">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46250.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46250.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46250.8125</v>
+      </c>
+      <c r="B368">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46250.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46250.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46250.84375</v>
+      </c>
+      <c r="B371">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46250.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46250.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46250.875</v>
+      </c>
+      <c r="B374">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46250.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46250.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46250.90625</v>
+      </c>
+      <c r="B377">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46250.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46250.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46250.9375</v>
+      </c>
+      <c r="B380">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46250.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46250.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46250.96875</v>
+      </c>
+      <c r="B383">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46250.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46250.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B386">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46251.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46251.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46251.03125</v>
+      </c>
+      <c r="B389">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46251.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46251.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46251.0625</v>
+      </c>
+      <c r="B392">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46251.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46251.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46251.09375</v>
+      </c>
+      <c r="B395">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46251.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46251.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46251.125</v>
+      </c>
+      <c r="B398">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46251.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46251.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46251.15625</v>
+      </c>
+      <c r="B401">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46251.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46251.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46251.1875</v>
+      </c>
+      <c r="B404">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46251.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46251.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46251.21875</v>
+      </c>
+      <c r="B407">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46251.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46251.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46251.25</v>
+      </c>
+      <c r="B410">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46251.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46251.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46251.28125</v>
+      </c>
+      <c r="B413">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46251.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46251.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46251.3125</v>
+      </c>
+      <c r="B416">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46251.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46251.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46251.34375</v>
+      </c>
+      <c r="B419">
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,935 +394,935 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B2">
-        <v>626</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46251.01041666666</v>
+        <v>46253.01041666666</v>
       </c>
       <c r="B3">
-        <v>627</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46251.02083333334</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="B4">
-        <v>626</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46251.03125</v>
+        <v>46253.03125</v>
       </c>
       <c r="B5">
-        <v>625</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46251.04166666666</v>
+        <v>46253.04166666666</v>
       </c>
       <c r="B6">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46251.05208333334</v>
+        <v>46253.05208333334</v>
       </c>
       <c r="B7">
-        <v>701</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46251.0625</v>
+        <v>46253.0625</v>
       </c>
       <c r="B8">
-        <v>701</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46251.07291666666</v>
+        <v>46253.07291666666</v>
       </c>
       <c r="B9">
-        <v>701</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46251.08333333334</v>
+        <v>46253.08333333334</v>
       </c>
       <c r="B10">
-        <v>691</v>
+        <v>766</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46251.09375</v>
+        <v>46253.09375</v>
       </c>
       <c r="B11">
-        <v>690</v>
+        <v>766</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46251.10416666666</v>
+        <v>46253.10416666666</v>
       </c>
       <c r="B12">
-        <v>665</v>
+        <v>767</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46251.11458333334</v>
+        <v>46253.11458333334</v>
       </c>
       <c r="B13">
-        <v>686</v>
+        <v>766</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46251.125</v>
+        <v>46253.125</v>
       </c>
       <c r="B14">
-        <v>692</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46251.13541666666</v>
+        <v>46253.13541666666</v>
       </c>
       <c r="B15">
-        <v>691</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46251.14583333334</v>
+        <v>46253.14583333334</v>
       </c>
       <c r="B16">
-        <v>691</v>
+        <v>789</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46251.15625</v>
+        <v>46253.15625</v>
       </c>
       <c r="B17">
-        <v>692</v>
+        <v>790</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46251.16666666666</v>
+        <v>46253.16666666666</v>
       </c>
       <c r="B18">
-        <v>640</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46251.17708333334</v>
+        <v>46253.17708333334</v>
       </c>
       <c r="B19">
-        <v>635</v>
+        <v>730</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46251.1875</v>
+        <v>46253.1875</v>
       </c>
       <c r="B20">
-        <v>634</v>
+        <v>728</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46251.19791666666</v>
+        <v>46253.19791666666</v>
       </c>
       <c r="B21">
-        <v>638</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46251.20833333334</v>
+        <v>46253.20833333334</v>
       </c>
       <c r="B22">
-        <v>683</v>
+        <v>701</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46251.21875</v>
+        <v>46253.21875</v>
       </c>
       <c r="B23">
-        <v>688</v>
+        <v>702</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46251.22916666666</v>
+        <v>46253.22916666666</v>
       </c>
       <c r="B24">
-        <v>690</v>
+        <v>719</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46251.23958333334</v>
+        <v>46253.23958333334</v>
       </c>
       <c r="B25">
-        <v>701</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46251.25</v>
+        <v>46253.25</v>
       </c>
       <c r="B26">
-        <v>772</v>
+        <v>755</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46251.26041666666</v>
+        <v>46253.26041666666</v>
       </c>
       <c r="B27">
-        <v>776</v>
+        <v>751</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46251.27083333334</v>
+        <v>46253.27083333334</v>
       </c>
       <c r="B28">
-        <v>766</v>
+        <v>744</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46251.28125</v>
+        <v>46253.28125</v>
       </c>
       <c r="B29">
-        <v>762</v>
+        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46251.29166666666</v>
+        <v>46253.29166666666</v>
       </c>
       <c r="B30">
-        <v>770</v>
+        <v>741</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46251.30208333334</v>
+        <v>46253.30208333334</v>
       </c>
       <c r="B31">
-        <v>772</v>
+        <v>737</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46251.3125</v>
+        <v>46253.3125</v>
       </c>
       <c r="B32">
-        <v>766</v>
+        <v>723</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46251.32291666666</v>
+        <v>46253.32291666666</v>
       </c>
       <c r="B33">
-        <v>780</v>
+        <v>725</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46251.33333333334</v>
+        <v>46253.33333333334</v>
       </c>
       <c r="B34">
-        <v>661</v>
+        <v>652</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46251.34375</v>
+        <v>46253.34375</v>
       </c>
       <c r="B35">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46251.35416666666</v>
+        <v>46253.35416666666</v>
       </c>
       <c r="B36">
-        <v>640</v>
+        <v>651</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46251.36458333334</v>
+        <v>46253.36458333334</v>
       </c>
       <c r="B37">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46251.375</v>
+        <v>46253.375</v>
       </c>
       <c r="B38">
-        <v>388</v>
+        <v>574</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46251.38541666666</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="B39">
-        <v>381</v>
+        <v>570</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46251.39583333334</v>
+        <v>46253.39583333334</v>
       </c>
       <c r="B40">
-        <v>379</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46251.40625</v>
+        <v>46253.40625</v>
       </c>
       <c r="B41">
-        <v>377</v>
+        <v>570</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46251.41666666666</v>
+        <v>46253.41666666666</v>
       </c>
       <c r="B42">
-        <v>295</v>
+        <v>629</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46251.42708333334</v>
+        <v>46253.42708333334</v>
       </c>
       <c r="B43">
-        <v>289</v>
+        <v>825</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46251.4375</v>
+        <v>46253.4375</v>
       </c>
       <c r="B44">
-        <v>289</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46251.44791666666</v>
+        <v>46253.44791666666</v>
       </c>
       <c r="B45">
-        <v>292</v>
+        <v>921</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46251.45833333334</v>
+        <v>46253.45833333334</v>
       </c>
       <c r="B46">
-        <v>456</v>
+        <v>859</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46251.46875</v>
+        <v>46253.46875</v>
       </c>
       <c r="B47">
-        <v>464</v>
+        <v>831</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46251.47916666666</v>
+        <v>46253.47916666666</v>
       </c>
       <c r="B48">
-        <v>466</v>
+        <v>610</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46251.48958333334</v>
+        <v>46253.48958333334</v>
       </c>
       <c r="B49">
-        <v>465</v>
+        <v>551</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46251.5</v>
+        <v>46253.5</v>
       </c>
       <c r="B50">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46251.51041666666</v>
+        <v>46253.51041666666</v>
       </c>
       <c r="B51">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46251.52083333334</v>
+        <v>46253.52083333334</v>
       </c>
       <c r="B52">
-        <v>373</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46251.53125</v>
+        <v>46253.53125</v>
       </c>
       <c r="B53">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46251.54166666666</v>
+        <v>46253.54166666666</v>
       </c>
       <c r="B54">
-        <v>515</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46251.55208333334</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="B55">
-        <v>523</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46251.5625</v>
+        <v>46253.5625</v>
       </c>
       <c r="B56">
-        <v>527</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46251.57291666666</v>
+        <v>46253.57291666666</v>
       </c>
       <c r="B57">
-        <v>527</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46251.58333333334</v>
+        <v>46253.58333333334</v>
       </c>
       <c r="B58">
-        <v>494</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46251.59375</v>
+        <v>46253.59375</v>
       </c>
       <c r="B59">
-        <v>497</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46251.60416666666</v>
+        <v>46253.60416666666</v>
       </c>
       <c r="B60">
-        <v>491</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46251.61458333334</v>
+        <v>46253.61458333334</v>
       </c>
       <c r="B61">
-        <v>502</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46251.625</v>
+        <v>46253.625</v>
       </c>
       <c r="B62">
-        <v>627</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46251.63541666666</v>
+        <v>46253.63541666666</v>
       </c>
       <c r="B63">
-        <v>442</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46251.64583333334</v>
+        <v>46253.64583333334</v>
       </c>
       <c r="B64">
-        <v>421</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46251.65625</v>
+        <v>46253.65625</v>
       </c>
       <c r="B65">
-        <v>518</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46251.66666666666</v>
+        <v>46253.66666666666</v>
       </c>
       <c r="B66">
-        <v>599</v>
+        <v>680</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46251.67708333334</v>
+        <v>46253.67708333334</v>
       </c>
       <c r="B67">
-        <v>601</v>
+        <v>708</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46251.6875</v>
+        <v>46253.6875</v>
       </c>
       <c r="B68">
-        <v>713</v>
+        <v>698</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46251.69791666666</v>
+        <v>46253.69791666666</v>
       </c>
       <c r="B69">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46251.70833333334</v>
+        <v>46253.70833333334</v>
       </c>
       <c r="B70">
-        <v>755</v>
+        <v>769</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46251.71875</v>
+        <v>46253.71875</v>
       </c>
       <c r="B71">
-        <v>762</v>
+        <v>773</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46251.72916666666</v>
+        <v>46253.72916666666</v>
       </c>
       <c r="B72">
-        <v>850</v>
+        <v>772</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46251.73958333334</v>
+        <v>46253.73958333334</v>
       </c>
       <c r="B73">
-        <v>877</v>
+        <v>783</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46251.75</v>
+        <v>46253.75</v>
       </c>
       <c r="B74">
-        <v>923</v>
+        <v>783</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46251.76041666666</v>
+        <v>46253.76041666666</v>
       </c>
       <c r="B75">
-        <v>921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46251.77083333334</v>
+        <v>46253.77083333334</v>
       </c>
       <c r="B76">
-        <v>912</v>
+        <v>839</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46251.78125</v>
+        <v>46253.78125</v>
       </c>
       <c r="B77">
-        <v>925</v>
+        <v>829</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46251.79166666666</v>
+        <v>46253.79166666666</v>
       </c>
       <c r="B78">
-        <v>890</v>
+        <v>879</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46251.80208333334</v>
+        <v>46253.80208333334</v>
       </c>
       <c r="B79">
-        <v>837</v>
+        <v>875</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46251.8125</v>
+        <v>46253.8125</v>
       </c>
       <c r="B80">
-        <v>829</v>
+        <v>881</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46251.82291666666</v>
+        <v>46253.82291666666</v>
       </c>
       <c r="B81">
-        <v>835</v>
+        <v>950</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46251.83333333334</v>
+        <v>46253.83333333334</v>
       </c>
       <c r="B82">
-        <v>835</v>
+        <v>978</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46251.84375</v>
+        <v>46253.84375</v>
       </c>
       <c r="B83">
-        <v>832</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46251.85416666666</v>
+        <v>46253.85416666666</v>
       </c>
       <c r="B84">
-        <v>830</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46251.86458333334</v>
+        <v>46253.86458333334</v>
       </c>
       <c r="B85">
-        <v>829</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46251.875</v>
+        <v>46253.875</v>
       </c>
       <c r="B86">
-        <v>769</v>
+        <v>904</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46251.88541666666</v>
+        <v>46253.88541666666</v>
       </c>
       <c r="B87">
-        <v>764</v>
+        <v>901</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46251.89583333334</v>
+        <v>46253.89583333334</v>
       </c>
       <c r="B88">
-        <v>767</v>
+        <v>826</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46251.90625</v>
+        <v>46253.90625</v>
       </c>
       <c r="B89">
-        <v>750</v>
+        <v>811</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46251.91666666666</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="B90">
-        <v>625</v>
+        <v>730</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46251.92708333334</v>
+        <v>46253.92708333334</v>
       </c>
       <c r="B91">
-        <v>622</v>
+        <v>721</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46251.9375</v>
+        <v>46253.9375</v>
       </c>
       <c r="B92">
-        <v>622</v>
+        <v>714</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46251.94791666666</v>
+        <v>46253.94791666666</v>
       </c>
       <c r="B93">
-        <v>620</v>
+        <v>718</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46251.95833333334</v>
+        <v>46253.95833333334</v>
       </c>
       <c r="B94">
-        <v>619</v>
+        <v>642</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46251.96875</v>
+        <v>46253.96875</v>
       </c>
       <c r="B95">
-        <v>617</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46251.97916666666</v>
+        <v>46253.97916666666</v>
       </c>
       <c r="B96">
-        <v>615</v>
+        <v>639</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46251.98958333334</v>
+        <v>46253.98958333334</v>
       </c>
       <c r="B97">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B98">
-        <v>730</v>
+        <v>698</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46252.01041666666</v>
+        <v>46254.01041666666</v>
       </c>
       <c r="B99">
-        <v>727</v>
+        <v>695</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46252.02083333334</v>
+        <v>46254.02083333334</v>
       </c>
       <c r="B100">
-        <v>726</v>
+        <v>696</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46252.03125</v>
+        <v>46254.03125</v>
       </c>
       <c r="B101">
-        <v>724</v>
+        <v>694</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46252.04166666666</v>
+        <v>46254.04166666666</v>
       </c>
       <c r="B102">
-        <v>751</v>
+        <v>672</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46252.05208333334</v>
+        <v>46254.05208333334</v>
       </c>
       <c r="B103">
-        <v>751</v>
+        <v>670</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46252.0625</v>
+        <v>46254.0625</v>
       </c>
       <c r="B104">
-        <v>750</v>
+        <v>671</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46252.07291666666</v>
+        <v>46254.07291666666</v>
       </c>
       <c r="B105">
-        <v>750</v>
+        <v>670</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46252.08333333334</v>
+        <v>46254.08333333334</v>
       </c>
       <c r="B106">
-        <v>739</v>
+        <v>661</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46252.09375</v>
+        <v>46254.09375</v>
       </c>
       <c r="B107">
-        <v>738</v>
+        <v>660</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46252.10416666666</v>
+        <v>46254.10416666666</v>
       </c>
       <c r="B108">
-        <v>739</v>
+        <v>664</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46252.11458333334</v>
+        <v>46254.11458333334</v>
       </c>
       <c r="B109">
-        <v>736</v>
+        <v>669</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46252.125</v>
+        <v>46254.125</v>
       </c>
       <c r="B110">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46252.13541666666</v>
+        <v>46254.13541666666</v>
       </c>
       <c r="B111">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46252.14583333334</v>
+        <v>46254.14583333334</v>
       </c>
       <c r="B112">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46252.15625</v>
+        <v>46254.15625</v>
       </c>
       <c r="B113">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46252.16666666666</v>
+        <v>46254.16666666666</v>
       </c>
       <c r="B114">
-        <v>726</v>
+        <v>682</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46252.17708333334</v>
+        <v>46254.17708333334</v>
       </c>
       <c r="B115">
-        <v>726</v>
+        <v>676</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46252.1875</v>
+        <v>46254.1875</v>
       </c>
       <c r="B116">
-        <v>726</v>
+        <v>677</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46252.19791666666</v>
+        <v>46254.19791666666</v>
       </c>
       <c r="B117">
-        <v>729</v>
+        <v>679</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46252.20833333334</v>
+        <v>46254.20833333334</v>
       </c>
       <c r="B118">
         <v>714</v>
@@ -1330,114 +1330,106 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46252.21875</v>
+        <v>46254.21875</v>
       </c>
       <c r="B119">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46252.22916666666</v>
+        <v>46254.22916666666</v>
       </c>
       <c r="B120">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46252.23958333334</v>
+        <v>46254.23958333334</v>
       </c>
       <c r="B121">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46252.25</v>
+        <v>46254.25</v>
       </c>
       <c r="B122">
-        <v>771</v>
+        <v>837</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46252.26041666666</v>
+        <v>46254.26041666666</v>
       </c>
       <c r="B123">
-        <v>768</v>
+        <v>838</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46252.27083333334</v>
+        <v>46254.27083333334</v>
       </c>
       <c r="B124">
-        <v>771</v>
+        <v>845</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46252.28125</v>
+        <v>46254.28125</v>
       </c>
       <c r="B125">
-        <v>771</v>
+        <v>840</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46252.29166666666</v>
+        <v>46254.29166666666</v>
       </c>
       <c r="B126">
-        <v>774</v>
+        <v>830</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46252.30208333334</v>
+        <v>46254.30208333334</v>
       </c>
       <c r="B127">
-        <v>762</v>
+        <v>829</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46252.3125</v>
+        <v>46254.3125</v>
       </c>
       <c r="B128">
-        <v>817</v>
+        <v>825</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46252.32291666666</v>
+        <v>46254.32291666666</v>
       </c>
       <c r="B129">
-        <v>865</v>
+        <v>824</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46252.33333333334</v>
+        <v>46254.33333333334</v>
       </c>
       <c r="B130">
-        <v>745</v>
+        <v>679</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46252.34375</v>
+        <v>46254.34375</v>
       </c>
       <c r="B131">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46252.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1042 +394,1010 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B2">
-        <v>653</v>
+        <v>793</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46253.01041666666</v>
+        <v>46258.01041666666</v>
       </c>
       <c r="B3">
-        <v>653</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46253.02083333334</v>
+        <v>46258.02083333334</v>
       </c>
       <c r="B4">
-        <v>652</v>
+        <v>789</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46253.03125</v>
+        <v>46258.03125</v>
       </c>
       <c r="B5">
-        <v>655</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46253.04166666666</v>
+        <v>46258.04166666666</v>
       </c>
       <c r="B6">
-        <v>717</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46253.05208333334</v>
+        <v>46258.05208333334</v>
       </c>
       <c r="B7">
-        <v>715</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46253.0625</v>
+        <v>46258.0625</v>
       </c>
       <c r="B8">
-        <v>716</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46253.07291666666</v>
+        <v>46258.07291666666</v>
       </c>
       <c r="B9">
-        <v>720</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46253.08333333334</v>
+        <v>46258.08333333334</v>
       </c>
       <c r="B10">
-        <v>766</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46253.09375</v>
+        <v>46258.09375</v>
       </c>
       <c r="B11">
-        <v>766</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46253.10416666666</v>
+        <v>46258.10416666666</v>
       </c>
       <c r="B12">
-        <v>767</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46253.11458333334</v>
+        <v>46258.11458333334</v>
       </c>
       <c r="B13">
-        <v>766</v>
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46253.125</v>
+        <v>46258.125</v>
       </c>
       <c r="B14">
-        <v>789</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46253.13541666666</v>
+        <v>46258.13541666666</v>
       </c>
       <c r="B15">
-        <v>789</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46253.14583333334</v>
+        <v>46258.14583333334</v>
       </c>
       <c r="B16">
-        <v>789</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46253.15625</v>
+        <v>46258.15625</v>
       </c>
       <c r="B17">
-        <v>790</v>
+        <v>745</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46253.16666666666</v>
+        <v>46258.16666666666</v>
       </c>
       <c r="B18">
-        <v>734</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46253.17708333334</v>
+        <v>46258.17708333334</v>
       </c>
       <c r="B19">
-        <v>730</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46253.1875</v>
+        <v>46258.1875</v>
       </c>
       <c r="B20">
-        <v>728</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46253.19791666666</v>
+        <v>46258.19791666666</v>
       </c>
       <c r="B21">
-        <v>730</v>
+        <v>748</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46253.20833333334</v>
+        <v>46258.20833333334</v>
       </c>
       <c r="B22">
-        <v>701</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46253.21875</v>
+        <v>46258.21875</v>
       </c>
       <c r="B23">
-        <v>702</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46253.22916666666</v>
+        <v>46258.22916666666</v>
       </c>
       <c r="B24">
-        <v>719</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46253.23958333334</v>
+        <v>46258.23958333334</v>
       </c>
       <c r="B25">
-        <v>729</v>
+        <v>648</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46253.25</v>
+        <v>46258.25</v>
       </c>
       <c r="B26">
-        <v>755</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46253.26041666666</v>
+        <v>46258.26041666666</v>
       </c>
       <c r="B27">
-        <v>751</v>
+        <v>774</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46253.27083333334</v>
+        <v>46258.27083333334</v>
       </c>
       <c r="B28">
-        <v>744</v>
+        <v>770</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46253.28125</v>
+        <v>46258.28125</v>
       </c>
       <c r="B29">
-        <v>729</v>
+        <v>769</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46253.29166666666</v>
+        <v>46258.29166666666</v>
       </c>
       <c r="B30">
-        <v>741</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46253.30208333334</v>
+        <v>46258.30208333334</v>
       </c>
       <c r="B31">
-        <v>737</v>
+        <v>804</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46253.3125</v>
+        <v>46258.3125</v>
       </c>
       <c r="B32">
-        <v>723</v>
+        <v>802</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46253.32291666666</v>
+        <v>46258.32291666666</v>
       </c>
       <c r="B33">
-        <v>725</v>
+        <v>797</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46253.33333333334</v>
+        <v>46258.33333333334</v>
       </c>
       <c r="B34">
-        <v>652</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46253.34375</v>
+        <v>46258.34375</v>
       </c>
       <c r="B35">
-        <v>648</v>
+        <v>597</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46253.35416666666</v>
+        <v>46258.35416666666</v>
       </c>
       <c r="B36">
-        <v>651</v>
+        <v>582</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46253.36458333334</v>
+        <v>46258.36458333334</v>
       </c>
       <c r="B37">
-        <v>635</v>
+        <v>565</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46253.375</v>
+        <v>46258.375</v>
       </c>
       <c r="B38">
-        <v>574</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46253.38541666666</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="B39">
-        <v>570</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46253.39583333334</v>
+        <v>46258.39583333334</v>
       </c>
       <c r="B40">
-        <v>573</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46253.40625</v>
+        <v>46258.40625</v>
       </c>
       <c r="B41">
-        <v>570</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46253.41666666666</v>
+        <v>46258.41666666666</v>
       </c>
       <c r="B42">
-        <v>629</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46253.42708333334</v>
+        <v>46258.42708333334</v>
       </c>
       <c r="B43">
-        <v>825</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46253.4375</v>
+        <v>46258.4375</v>
       </c>
       <c r="B44">
-        <v>918</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46253.44791666666</v>
+        <v>46258.44791666666</v>
       </c>
       <c r="B45">
-        <v>921</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46253.45833333334</v>
+        <v>46258.45833333334</v>
       </c>
       <c r="B46">
-        <v>859</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46253.46875</v>
+        <v>46258.46875</v>
       </c>
       <c r="B47">
-        <v>831</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46253.47916666666</v>
+        <v>46258.47916666666</v>
       </c>
       <c r="B48">
-        <v>610</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46253.48958333334</v>
+        <v>46258.48958333334</v>
       </c>
       <c r="B49">
-        <v>551</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46253.5</v>
+        <v>46258.5</v>
       </c>
       <c r="B50">
-        <v>384</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46253.51041666666</v>
+        <v>46258.51041666666</v>
       </c>
       <c r="B51">
-        <v>372</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46253.52083333334</v>
+        <v>46258.52083333334</v>
       </c>
       <c r="B52">
-        <v>348</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46253.53125</v>
+        <v>46258.53125</v>
       </c>
       <c r="B53">
-        <v>380</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46253.54166666666</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="B54">
-        <v>171</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46253.55208333334</v>
+        <v>46258.55208333334</v>
       </c>
       <c r="B55">
-        <v>170</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46253.5625</v>
+        <v>46258.5625</v>
       </c>
       <c r="B56">
-        <v>171</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46253.57291666666</v>
+        <v>46258.57291666666</v>
       </c>
       <c r="B57">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46253.58333333334</v>
+        <v>46258.58333333334</v>
       </c>
       <c r="B58">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46253.59375</v>
+        <v>46258.59375</v>
       </c>
       <c r="B59">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46253.60416666666</v>
+        <v>46258.60416666666</v>
       </c>
       <c r="B60">
-        <v>120</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46253.61458333334</v>
+        <v>46258.61458333334</v>
       </c>
       <c r="B61">
-        <v>104</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46253.625</v>
+        <v>46258.625</v>
       </c>
       <c r="B62">
-        <v>98</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46253.63541666666</v>
+        <v>46258.63541666666</v>
       </c>
       <c r="B63">
-        <v>99</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46253.64583333334</v>
+        <v>46258.64583333334</v>
       </c>
       <c r="B64">
-        <v>92</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46253.65625</v>
+        <v>46258.65625</v>
       </c>
       <c r="B65">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46253.66666666666</v>
+        <v>46258.66666666666</v>
       </c>
       <c r="B66">
-        <v>680</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46253.67708333334</v>
+        <v>46258.67708333334</v>
       </c>
       <c r="B67">
-        <v>708</v>
+        <v>434</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46253.6875</v>
+        <v>46258.6875</v>
       </c>
       <c r="B68">
-        <v>698</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46253.69791666666</v>
+        <v>46258.69791666666</v>
       </c>
       <c r="B69">
-        <v>724</v>
+        <v>377</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46253.70833333334</v>
+        <v>46258.70833333334</v>
       </c>
       <c r="B70">
-        <v>769</v>
+        <v>457</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46253.71875</v>
+        <v>46258.71875</v>
       </c>
       <c r="B71">
-        <v>773</v>
+        <v>516</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46253.72916666666</v>
+        <v>46258.72916666666</v>
       </c>
       <c r="B72">
-        <v>772</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46253.73958333334</v>
+        <v>46258.73958333334</v>
       </c>
       <c r="B73">
-        <v>783</v>
+        <v>543</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46253.75</v>
+        <v>46258.75</v>
       </c>
       <c r="B74">
-        <v>783</v>
+        <v>562</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46253.76041666666</v>
+        <v>46258.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46253.77083333334</v>
+        <v>46258.77083333334</v>
       </c>
       <c r="B76">
-        <v>839</v>
+        <v>815</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46253.78125</v>
+        <v>46258.78125</v>
       </c>
       <c r="B77">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46253.79166666666</v>
+        <v>46258.79166666666</v>
       </c>
       <c r="B78">
-        <v>879</v>
+        <v>850</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46253.80208333334</v>
+        <v>46258.80208333334</v>
       </c>
       <c r="B79">
-        <v>875</v>
+        <v>860</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46253.8125</v>
+        <v>46258.8125</v>
       </c>
       <c r="B80">
-        <v>881</v>
+        <v>863</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46253.82291666666</v>
+        <v>46258.82291666666</v>
       </c>
       <c r="B81">
-        <v>950</v>
+        <v>858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46253.83333333334</v>
+        <v>46258.83333333334</v>
       </c>
       <c r="B82">
-        <v>978</v>
+        <v>874</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46253.84375</v>
+        <v>46258.84375</v>
       </c>
       <c r="B83">
-        <v>1063</v>
+        <v>873</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46253.85416666666</v>
+        <v>46258.85416666666</v>
       </c>
       <c r="B84">
-        <v>1067</v>
+        <v>876</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46253.86458333334</v>
+        <v>46258.86458333334</v>
       </c>
       <c r="B85">
-        <v>1065</v>
+        <v>874</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46253.875</v>
+        <v>46258.875</v>
       </c>
       <c r="B86">
-        <v>904</v>
+        <v>831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46253.88541666666</v>
+        <v>46258.88541666666</v>
       </c>
       <c r="B87">
-        <v>901</v>
+        <v>833</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46253.89583333334</v>
+        <v>46258.89583333334</v>
       </c>
       <c r="B88">
-        <v>826</v>
+        <v>841</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46253.90625</v>
+        <v>46258.90625</v>
       </c>
       <c r="B89">
-        <v>811</v>
+        <v>827</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46253.91666666666</v>
+        <v>46258.91666666666</v>
       </c>
       <c r="B90">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46253.92708333334</v>
+        <v>46258.92708333334</v>
       </c>
       <c r="B91">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46253.9375</v>
+        <v>46258.9375</v>
       </c>
       <c r="B92">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46253.94791666666</v>
+        <v>46258.94791666666</v>
       </c>
       <c r="B93">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46253.95833333334</v>
+        <v>46258.95833333334</v>
       </c>
       <c r="B94">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46253.96875</v>
+        <v>46258.96875</v>
       </c>
       <c r="B95">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46253.97916666666</v>
+        <v>46258.97916666666</v>
       </c>
       <c r="B96">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46253.98958333334</v>
+        <v>46258.98958333334</v>
       </c>
       <c r="B97">
-        <v>637</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="B98">
-        <v>698</v>
+        <v>842</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46254.01041666666</v>
+        <v>46259.01041666666</v>
       </c>
       <c r="B99">
-        <v>695</v>
+        <v>919</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46254.02083333334</v>
+        <v>46259.02083333334</v>
       </c>
       <c r="B100">
-        <v>696</v>
+        <v>870</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46254.03125</v>
+        <v>46259.03125</v>
       </c>
       <c r="B101">
-        <v>694</v>
+        <v>735</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46254.04166666666</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="B102">
-        <v>672</v>
+        <v>732</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46254.05208333334</v>
+        <v>46259.05208333334</v>
       </c>
       <c r="B103">
-        <v>670</v>
+        <v>731</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46254.0625</v>
+        <v>46259.0625</v>
       </c>
       <c r="B104">
-        <v>671</v>
+        <v>730</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46254.07291666666</v>
+        <v>46259.07291666666</v>
       </c>
       <c r="B105">
-        <v>670</v>
+        <v>730</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46254.08333333334</v>
+        <v>46259.08333333334</v>
       </c>
       <c r="B106">
-        <v>661</v>
+        <v>716</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46254.09375</v>
+        <v>46259.09375</v>
       </c>
       <c r="B107">
-        <v>660</v>
+        <v>714</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46254.10416666666</v>
+        <v>46259.10416666666</v>
       </c>
       <c r="B108">
-        <v>664</v>
+        <v>712</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46254.11458333334</v>
+        <v>46259.11458333334</v>
       </c>
       <c r="B109">
-        <v>669</v>
+        <v>717</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46254.125</v>
+        <v>46259.125</v>
       </c>
       <c r="B110">
-        <v>747</v>
+        <v>794</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46254.13541666666</v>
+        <v>46259.13541666666</v>
       </c>
       <c r="B111">
-        <v>742</v>
+        <v>794</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46254.14583333334</v>
+        <v>46259.14583333334</v>
       </c>
       <c r="B112">
-        <v>741</v>
+        <v>792</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46254.15625</v>
+        <v>46259.15625</v>
       </c>
       <c r="B113">
-        <v>740</v>
+        <v>792</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46254.16666666666</v>
+        <v>46259.16666666666</v>
       </c>
       <c r="B114">
-        <v>682</v>
+        <v>791</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46254.17708333334</v>
+        <v>46259.17708333334</v>
       </c>
       <c r="B115">
-        <v>676</v>
+        <v>790</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46254.1875</v>
+        <v>46259.1875</v>
       </c>
       <c r="B116">
-        <v>677</v>
+        <v>791</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46254.19791666666</v>
+        <v>46259.19791666666</v>
       </c>
       <c r="B117">
-        <v>679</v>
+        <v>791</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46254.20833333334</v>
+        <v>46259.20833333334</v>
       </c>
       <c r="B118">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46254.21875</v>
+        <v>46259.21875</v>
       </c>
       <c r="B119">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46254.22916666666</v>
+        <v>46259.22916666666</v>
       </c>
       <c r="B120">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46254.23958333334</v>
+        <v>46259.23958333334</v>
       </c>
       <c r="B121">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46254.25</v>
+        <v>46259.25</v>
       </c>
       <c r="B122">
-        <v>837</v>
+        <v>866</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46254.26041666666</v>
+        <v>46259.26041666666</v>
       </c>
       <c r="B123">
-        <v>838</v>
+        <v>862</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46254.27083333334</v>
+        <v>46259.27083333334</v>
       </c>
       <c r="B124">
-        <v>845</v>
+        <v>869</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46254.28125</v>
+        <v>46259.28125</v>
       </c>
       <c r="B125">
-        <v>840</v>
+        <v>829</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46254.29166666666</v>
+        <v>46259.29166666666</v>
       </c>
       <c r="B126">
-        <v>830</v>
+        <v>701</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46254.30208333334</v>
+        <v>46259.30208333334</v>
       </c>
       <c r="B127">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46254.3125</v>
-      </c>
-      <c r="B128">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46254.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46254.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46254.34375</v>
-      </c>
-      <c r="B131">
-        <v>673</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1010 +394,1922 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B2">
-        <v>793</v>
+        <v>824</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46258.01041666666</v>
+        <v>46260.01041666666</v>
       </c>
       <c r="B3">
-        <v>790</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46258.02083333334</v>
+        <v>46260.02083333334</v>
       </c>
       <c r="B4">
-        <v>789</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46258.03125</v>
+        <v>46260.03125</v>
       </c>
       <c r="B5">
-        <v>789</v>
+        <v>828</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46258.04166666666</v>
+        <v>46260.04166666666</v>
       </c>
       <c r="B6">
-        <v>767</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46258.05208333334</v>
+        <v>46260.05208333334</v>
       </c>
       <c r="B7">
-        <v>765</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46258.0625</v>
+        <v>46260.0625</v>
       </c>
       <c r="B8">
-        <v>765</v>
+        <v>834</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46258.07291666666</v>
+        <v>46260.07291666666</v>
       </c>
       <c r="B9">
-        <v>764</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46258.08333333334</v>
+        <v>46260.08333333334</v>
       </c>
       <c r="B10">
-        <v>753</v>
+        <v>813</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46258.09375</v>
+        <v>46260.09375</v>
       </c>
       <c r="B11">
-        <v>743</v>
+        <v>811</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46258.10416666666</v>
+        <v>46260.10416666666</v>
       </c>
       <c r="B12">
-        <v>742</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46258.11458333334</v>
+        <v>46260.11458333334</v>
       </c>
       <c r="B13">
-        <v>742</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46258.125</v>
+        <v>46260.125</v>
       </c>
       <c r="B14">
-        <v>746</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46258.13541666666</v>
+        <v>46260.13541666666</v>
       </c>
       <c r="B15">
-        <v>744</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46258.14583333334</v>
+        <v>46260.14583333334</v>
       </c>
       <c r="B16">
-        <v>745</v>
+        <v>798</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46258.15625</v>
+        <v>46260.15625</v>
       </c>
       <c r="B17">
-        <v>745</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46258.16666666666</v>
+        <v>46260.16666666666</v>
       </c>
       <c r="B18">
-        <v>747</v>
+        <v>802</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46258.17708333334</v>
+        <v>46260.17708333334</v>
       </c>
       <c r="B19">
-        <v>743</v>
+        <v>870</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46258.1875</v>
+        <v>46260.1875</v>
       </c>
       <c r="B20">
-        <v>741</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46258.19791666666</v>
+        <v>46260.19791666666</v>
       </c>
       <c r="B21">
-        <v>748</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46258.20833333334</v>
+        <v>46260.20833333334</v>
       </c>
       <c r="B22">
-        <v>641</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46258.21875</v>
+        <v>46260.21875</v>
       </c>
       <c r="B23">
-        <v>639</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46258.22916666666</v>
+        <v>46260.22916666666</v>
       </c>
       <c r="B24">
-        <v>641</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46258.23958333334</v>
+        <v>46260.23958333334</v>
       </c>
       <c r="B25">
-        <v>648</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46258.25</v>
+        <v>46260.25</v>
       </c>
       <c r="B26">
-        <v>773</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46258.26041666666</v>
+        <v>46260.26041666666</v>
       </c>
       <c r="B27">
-        <v>774</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46258.27083333334</v>
+        <v>46260.27083333334</v>
       </c>
       <c r="B28">
-        <v>770</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46258.28125</v>
+        <v>46260.28125</v>
       </c>
       <c r="B29">
-        <v>769</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46258.29166666666</v>
+        <v>46260.29166666666</v>
       </c>
       <c r="B30">
-        <v>800</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46258.30208333334</v>
+        <v>46260.30208333334</v>
       </c>
       <c r="B31">
-        <v>804</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46258.3125</v>
+        <v>46260.3125</v>
       </c>
       <c r="B32">
-        <v>802</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46258.32291666666</v>
+        <v>46260.32291666666</v>
       </c>
       <c r="B33">
-        <v>797</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46258.33333333334</v>
+        <v>46260.33333333334</v>
       </c>
       <c r="B34">
-        <v>611</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46258.34375</v>
+        <v>46260.34375</v>
       </c>
       <c r="B35">
-        <v>597</v>
+        <v>991</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46258.35416666666</v>
+        <v>46260.35416666666</v>
       </c>
       <c r="B36">
-        <v>582</v>
+        <v>991</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46258.36458333334</v>
+        <v>46260.36458333334</v>
       </c>
       <c r="B37">
-        <v>565</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46258.375</v>
+        <v>46260.375</v>
       </c>
       <c r="B38">
-        <v>441</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46258.38541666666</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="B39">
-        <v>436</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46258.39583333334</v>
+        <v>46260.39583333334</v>
       </c>
       <c r="B40">
-        <v>445</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46258.40625</v>
+        <v>46260.40625</v>
       </c>
       <c r="B41">
-        <v>443</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46258.41666666666</v>
+        <v>46260.41666666666</v>
       </c>
       <c r="B42">
-        <v>135</v>
+        <v>892</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46258.42708333334</v>
+        <v>46260.42708333334</v>
       </c>
       <c r="B43">
-        <v>127</v>
+        <v>824</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46258.4375</v>
+        <v>46260.4375</v>
       </c>
       <c r="B44">
-        <v>123</v>
+        <v>781</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46258.44791666666</v>
+        <v>46260.44791666666</v>
       </c>
       <c r="B45">
-        <v>124</v>
+        <v>790</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46258.45833333334</v>
+        <v>46260.45833333334</v>
       </c>
       <c r="B46">
-        <v>97</v>
+        <v>720</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46258.46875</v>
+        <v>46260.46875</v>
       </c>
       <c r="B47">
-        <v>96</v>
+        <v>748</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46258.47916666666</v>
+        <v>46260.47916666666</v>
       </c>
       <c r="B48">
-        <v>95</v>
+        <v>708</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46258.48958333334</v>
+        <v>46260.48958333334</v>
       </c>
       <c r="B49">
-        <v>93</v>
+        <v>708</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46258.5</v>
+        <v>46260.5</v>
       </c>
       <c r="B50">
-        <v>88</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46258.51041666666</v>
+        <v>46260.51041666666</v>
       </c>
       <c r="B51">
-        <v>87</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46258.52083333334</v>
+        <v>46260.52083333334</v>
       </c>
       <c r="B52">
-        <v>119</v>
+        <v>393</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46258.53125</v>
+        <v>46260.53125</v>
       </c>
       <c r="B53">
-        <v>92</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46258.54166666666</v>
+        <v>46260.54166666666</v>
       </c>
       <c r="B54">
-        <v>93</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46258.55208333334</v>
+        <v>46260.55208333334</v>
       </c>
       <c r="B55">
-        <v>95</v>
+        <v>438</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46258.5625</v>
+        <v>46260.5625</v>
       </c>
       <c r="B56">
-        <v>101</v>
+        <v>506</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46258.57291666666</v>
+        <v>46260.57291666666</v>
       </c>
       <c r="B57">
-        <v>98</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46258.58333333334</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="B58">
-        <v>124</v>
+        <v>703</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46258.59375</v>
+        <v>46260.59375</v>
       </c>
       <c r="B59">
-        <v>133</v>
+        <v>729</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46258.60416666666</v>
+        <v>46260.60416666666</v>
       </c>
       <c r="B60">
-        <v>149</v>
+        <v>787</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46258.61458333334</v>
+        <v>46260.61458333334</v>
       </c>
       <c r="B61">
-        <v>144</v>
+        <v>784</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46258.625</v>
+        <v>46260.625</v>
       </c>
       <c r="B62">
-        <v>230</v>
+        <v>776</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46258.63541666666</v>
+        <v>46260.63541666666</v>
       </c>
       <c r="B63">
-        <v>239</v>
+        <v>777</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46258.64583333334</v>
+        <v>46260.64583333334</v>
       </c>
       <c r="B64">
-        <v>239</v>
+        <v>771</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46258.65625</v>
+        <v>46260.65625</v>
       </c>
       <c r="B65">
-        <v>167</v>
+        <v>777</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46258.66666666666</v>
+        <v>46260.66666666666</v>
       </c>
       <c r="B66">
-        <v>550</v>
+        <v>768</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46258.67708333334</v>
+        <v>46260.67708333334</v>
       </c>
       <c r="B67">
-        <v>434</v>
+        <v>769</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46258.6875</v>
+        <v>46260.6875</v>
       </c>
       <c r="B68">
-        <v>366</v>
+        <v>767</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46258.69791666666</v>
+        <v>46260.69791666666</v>
       </c>
       <c r="B69">
-        <v>377</v>
+        <v>776</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46258.70833333334</v>
+        <v>46260.70833333334</v>
       </c>
       <c r="B70">
-        <v>457</v>
+        <v>834</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46258.71875</v>
+        <v>46260.71875</v>
       </c>
       <c r="B71">
-        <v>516</v>
+        <v>799</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46258.72916666666</v>
+        <v>46260.72916666666</v>
       </c>
       <c r="B72">
-        <v>526</v>
+        <v>819</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46258.73958333334</v>
+        <v>46260.73958333334</v>
       </c>
       <c r="B73">
-        <v>543</v>
+        <v>830</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46258.75</v>
+        <v>46260.75</v>
       </c>
       <c r="B74">
-        <v>562</v>
+        <v>853</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46258.76041666666</v>
+        <v>46260.76041666666</v>
       </c>
       <c r="B75">
-        <v>796</v>
+        <v>850</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46258.77083333334</v>
+        <v>46260.77083333334</v>
       </c>
       <c r="B76">
-        <v>815</v>
+        <v>840</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46258.78125</v>
+        <v>46260.78125</v>
       </c>
       <c r="B77">
-        <v>836</v>
+        <v>849</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46258.79166666666</v>
+        <v>46260.79166666666</v>
       </c>
       <c r="B78">
-        <v>850</v>
+        <v>917</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46258.80208333334</v>
+        <v>46260.80208333334</v>
       </c>
       <c r="B79">
-        <v>860</v>
+        <v>921</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46258.8125</v>
+        <v>46260.8125</v>
       </c>
       <c r="B80">
-        <v>863</v>
+        <v>914</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46258.82291666666</v>
+        <v>46260.82291666666</v>
       </c>
       <c r="B81">
-        <v>858</v>
+        <v>908</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46258.83333333334</v>
+        <v>46260.83333333334</v>
       </c>
       <c r="B82">
-        <v>874</v>
+        <v>888</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46258.84375</v>
+        <v>46260.84375</v>
       </c>
       <c r="B83">
-        <v>873</v>
+        <v>905</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46258.85416666666</v>
+        <v>46260.85416666666</v>
       </c>
       <c r="B84">
-        <v>876</v>
+        <v>901</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46258.86458333334</v>
+        <v>46260.86458333334</v>
       </c>
       <c r="B85">
-        <v>874</v>
+        <v>892</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46258.875</v>
+        <v>46260.875</v>
       </c>
       <c r="B86">
-        <v>831</v>
+        <v>844</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46258.88541666666</v>
+        <v>46260.88541666666</v>
       </c>
       <c r="B87">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46258.89583333334</v>
+        <v>46260.89583333334</v>
       </c>
       <c r="B88">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46258.90625</v>
+        <v>46260.90625</v>
       </c>
       <c r="B89">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46258.91666666666</v>
+        <v>46260.91666666666</v>
       </c>
       <c r="B90">
-        <v>734</v>
+        <v>743</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46258.92708333334</v>
+        <v>46260.92708333334</v>
       </c>
       <c r="B91">
-        <v>722</v>
+        <v>744</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46258.9375</v>
+        <v>46260.9375</v>
       </c>
       <c r="B92">
-        <v>721</v>
+        <v>749</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46258.94791666666</v>
+        <v>46260.94791666666</v>
       </c>
       <c r="B93">
-        <v>713</v>
+        <v>741</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46258.95833333334</v>
+        <v>46260.95833333334</v>
       </c>
       <c r="B94">
-        <v>646</v>
+        <v>731</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46258.96875</v>
+        <v>46260.96875</v>
       </c>
       <c r="B95">
-        <v>645</v>
+        <v>733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46258.97916666666</v>
+        <v>46260.97916666666</v>
       </c>
       <c r="B96">
-        <v>646</v>
+        <v>731</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46258.98958333334</v>
+        <v>46260.98958333334</v>
       </c>
       <c r="B97">
-        <v>653</v>
+        <v>739</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B98">
-        <v>842</v>
+        <v>888</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46259.01041666666</v>
+        <v>46261.01041666666</v>
       </c>
       <c r="B99">
-        <v>919</v>
+        <v>885</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46259.02083333334</v>
+        <v>46261.02083333334</v>
       </c>
       <c r="B100">
-        <v>870</v>
+        <v>885</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46259.03125</v>
+        <v>46261.03125</v>
       </c>
       <c r="B101">
-        <v>735</v>
+        <v>884</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46259.04166666666</v>
+        <v>46261.04166666666</v>
       </c>
       <c r="B102">
-        <v>732</v>
+        <v>887</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46259.05208333334</v>
+        <v>46261.05208333334</v>
       </c>
       <c r="B103">
-        <v>731</v>
+        <v>885</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46259.0625</v>
+        <v>46261.0625</v>
       </c>
       <c r="B104">
-        <v>730</v>
+        <v>884</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46259.07291666666</v>
+        <v>46261.07291666666</v>
       </c>
       <c r="B105">
-        <v>730</v>
+        <v>879</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46259.08333333334</v>
+        <v>46261.08333333334</v>
       </c>
       <c r="B106">
-        <v>716</v>
+        <v>854</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46259.09375</v>
+        <v>46261.09375</v>
       </c>
       <c r="B107">
-        <v>714</v>
+        <v>852</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46259.10416666666</v>
+        <v>46261.10416666666</v>
       </c>
       <c r="B108">
-        <v>712</v>
+        <v>854</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46259.11458333334</v>
+        <v>46261.11458333334</v>
       </c>
       <c r="B109">
-        <v>717</v>
+        <v>851</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46259.125</v>
+        <v>46261.125</v>
       </c>
       <c r="B110">
-        <v>794</v>
+        <v>839</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46259.13541666666</v>
+        <v>46261.13541666666</v>
       </c>
       <c r="B111">
-        <v>794</v>
+        <v>837</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46259.14583333334</v>
+        <v>46261.14583333334</v>
       </c>
       <c r="B112">
-        <v>792</v>
+        <v>837</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46259.15625</v>
+        <v>46261.15625</v>
       </c>
       <c r="B113">
-        <v>792</v>
+        <v>835</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46259.16666666666</v>
+        <v>46261.16666666666</v>
       </c>
       <c r="B114">
-        <v>791</v>
+        <v>835</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46259.17708333334</v>
+        <v>46261.17708333334</v>
       </c>
       <c r="B115">
-        <v>790</v>
+        <v>835</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46259.1875</v>
+        <v>46261.1875</v>
       </c>
       <c r="B116">
-        <v>791</v>
+        <v>835</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46259.19791666666</v>
+        <v>46261.19791666666</v>
       </c>
       <c r="B117">
-        <v>791</v>
+        <v>838</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46259.20833333334</v>
+        <v>46261.20833333334</v>
       </c>
       <c r="B118">
-        <v>718</v>
+        <v>867</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46259.21875</v>
+        <v>46261.21875</v>
       </c>
       <c r="B119">
-        <v>719</v>
+        <v>873</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46259.22916666666</v>
+        <v>46261.22916666666</v>
       </c>
       <c r="B120">
-        <v>722</v>
+        <v>871</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46259.23958333334</v>
+        <v>46261.23958333334</v>
       </c>
       <c r="B121">
-        <v>735</v>
+        <v>873</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46259.25</v>
+        <v>46261.25</v>
       </c>
       <c r="B122">
-        <v>866</v>
+        <v>898</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46259.26041666666</v>
+        <v>46261.26041666666</v>
       </c>
       <c r="B123">
-        <v>862</v>
+        <v>904</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46259.27083333334</v>
+        <v>46261.27083333334</v>
       </c>
       <c r="B124">
-        <v>869</v>
+        <v>901</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46259.28125</v>
+        <v>46261.28125</v>
       </c>
       <c r="B125">
-        <v>829</v>
+        <v>910</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46259.29166666666</v>
+        <v>46261.29166666666</v>
       </c>
       <c r="B126">
-        <v>701</v>
+        <v>949</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46259.30208333334</v>
+        <v>46261.30208333334</v>
       </c>
       <c r="B127">
-        <v>687</v>
+        <v>946</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46261.3125</v>
+      </c>
+      <c r="B128">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46261.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46261.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46261.34375</v>
+      </c>
+      <c r="B131">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46261.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46261.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46261.375</v>
+      </c>
+      <c r="B134">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46261.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46261.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46261.40625</v>
+      </c>
+      <c r="B137">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46261.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46261.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46261.4375</v>
+      </c>
+      <c r="B140">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46261.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46261.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46261.46875</v>
+      </c>
+      <c r="B143">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46261.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46261.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46261.5</v>
+      </c>
+      <c r="B146">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46261.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46261.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46261.53125</v>
+      </c>
+      <c r="B149">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46261.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46261.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46261.5625</v>
+      </c>
+      <c r="B152">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46261.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46261.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46261.59375</v>
+      </c>
+      <c r="B155">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46261.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46261.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46261.625</v>
+      </c>
+      <c r="B158">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46261.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46261.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46261.65625</v>
+      </c>
+      <c r="B161">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46261.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46261.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46261.6875</v>
+      </c>
+      <c r="B164">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46261.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46261.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46261.71875</v>
+      </c>
+      <c r="B167">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46261.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46261.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46261.75</v>
+      </c>
+      <c r="B170">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46261.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46261.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46261.78125</v>
+      </c>
+      <c r="B173">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46261.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46261.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46261.8125</v>
+      </c>
+      <c r="B176">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46261.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46261.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46261.84375</v>
+      </c>
+      <c r="B179">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46261.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46261.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46261.875</v>
+      </c>
+      <c r="B182">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46261.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46261.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46261.90625</v>
+      </c>
+      <c r="B185">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46261.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46261.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46261.9375</v>
+      </c>
+      <c r="B188">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46261.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46261.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46261.96875</v>
+      </c>
+      <c r="B191">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46261.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46261.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B194">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46262.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46262.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46262.03125</v>
+      </c>
+      <c r="B197">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46262.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46262.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46262.0625</v>
+      </c>
+      <c r="B200">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46262.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46262.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46262.09375</v>
+      </c>
+      <c r="B203">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46262.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46262.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46262.125</v>
+      </c>
+      <c r="B206">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46262.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46262.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46262.15625</v>
+      </c>
+      <c r="B209">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46262.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46262.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46262.1875</v>
+      </c>
+      <c r="B212">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46262.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46262.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46262.21875</v>
+      </c>
+      <c r="B215">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46262.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46262.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46262.25</v>
+      </c>
+      <c r="B218">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46262.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46262.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46262.28125</v>
+      </c>
+      <c r="B221">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46262.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46262.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46262.3125</v>
+      </c>
+      <c r="B224">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46262.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46262.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46262.34375</v>
+      </c>
+      <c r="B227">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46262.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46262.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46262.375</v>
+      </c>
+      <c r="B230">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46262.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46262.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46262.40625</v>
+      </c>
+      <c r="B233">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46262.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46262.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46262.4375</v>
+      </c>
+      <c r="B236">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46262.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46262.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46262.46875</v>
+      </c>
+      <c r="B239">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46262.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46262.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Hydro_Water_Reservoir.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,855 +394,855 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="B2">
-        <v>824</v>
+        <v>803</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46260.01041666666</v>
+        <v>46268.01041666666</v>
       </c>
       <c r="B3">
-        <v>831</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46260.02083333334</v>
+        <v>46268.02083333334</v>
       </c>
       <c r="B4">
-        <v>829</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46260.03125</v>
+        <v>46268.03125</v>
       </c>
       <c r="B5">
-        <v>828</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46260.04166666666</v>
+        <v>46268.04166666666</v>
       </c>
       <c r="B6">
-        <v>834</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46260.05208333334</v>
+        <v>46268.05208333334</v>
       </c>
       <c r="B7">
-        <v>831</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46260.0625</v>
+        <v>46268.0625</v>
       </c>
       <c r="B8">
-        <v>834</v>
+        <v>802</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46260.07291666666</v>
+        <v>46268.07291666666</v>
       </c>
       <c r="B9">
-        <v>831</v>
+        <v>804</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46260.08333333334</v>
+        <v>46268.08333333334</v>
       </c>
       <c r="B10">
-        <v>813</v>
+        <v>795</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46260.09375</v>
+        <v>46268.09375</v>
       </c>
       <c r="B11">
-        <v>811</v>
+        <v>795</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46260.10416666666</v>
+        <v>46268.10416666666</v>
       </c>
       <c r="B12">
-        <v>811</v>
+        <v>794</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46260.11458333334</v>
+        <v>46268.11458333334</v>
       </c>
       <c r="B13">
-        <v>813</v>
+        <v>794</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46260.125</v>
+        <v>46268.125</v>
       </c>
       <c r="B14">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46260.13541666666</v>
+        <v>46268.13541666666</v>
       </c>
       <c r="B15">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46260.14583333334</v>
+        <v>46268.14583333334</v>
       </c>
       <c r="B16">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46260.15625</v>
+        <v>46268.15625</v>
       </c>
       <c r="B17">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46260.16666666666</v>
+        <v>46268.16666666666</v>
       </c>
       <c r="B18">
-        <v>802</v>
+        <v>821</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46260.17708333334</v>
+        <v>46268.17708333334</v>
       </c>
       <c r="B19">
-        <v>870</v>
+        <v>819</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46260.1875</v>
+        <v>46268.1875</v>
       </c>
       <c r="B20">
-        <v>1024</v>
+        <v>821</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46260.19791666666</v>
+        <v>46268.19791666666</v>
       </c>
       <c r="B21">
-        <v>1031</v>
+        <v>824</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46260.20833333334</v>
+        <v>46268.20833333334</v>
       </c>
       <c r="B22">
-        <v>1001</v>
+        <v>849</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46260.21875</v>
+        <v>46268.21875</v>
       </c>
       <c r="B23">
-        <v>1006</v>
+        <v>853</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46260.22916666666</v>
+        <v>46268.22916666666</v>
       </c>
       <c r="B24">
-        <v>1008</v>
+        <v>853</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46260.23958333334</v>
+        <v>46268.23958333334</v>
       </c>
       <c r="B25">
-        <v>1015</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46260.25</v>
+        <v>46268.25</v>
       </c>
       <c r="B26">
-        <v>1107</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46260.26041666666</v>
+        <v>46268.26041666666</v>
       </c>
       <c r="B27">
-        <v>1110</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46260.27083333334</v>
+        <v>46268.27083333334</v>
       </c>
       <c r="B28">
-        <v>1159</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46260.28125</v>
+        <v>46268.28125</v>
       </c>
       <c r="B29">
-        <v>1027</v>
+        <v>996</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46260.29166666666</v>
+        <v>46268.29166666666</v>
       </c>
       <c r="B30">
-        <v>1255</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46260.30208333334</v>
+        <v>46268.30208333334</v>
       </c>
       <c r="B31">
-        <v>1259</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46260.3125</v>
+        <v>46268.3125</v>
       </c>
       <c r="B32">
-        <v>1236</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46260.32291666666</v>
+        <v>46268.32291666666</v>
       </c>
       <c r="B33">
-        <v>1235</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46260.33333333334</v>
+        <v>46268.33333333334</v>
       </c>
       <c r="B34">
-        <v>1045</v>
+        <v>846</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46260.34375</v>
+        <v>46268.34375</v>
       </c>
       <c r="B35">
-        <v>991</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46260.35416666666</v>
+        <v>46268.35416666666</v>
       </c>
       <c r="B36">
-        <v>991</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46260.36458333334</v>
+        <v>46268.36458333334</v>
       </c>
       <c r="B37">
-        <v>1044</v>
+        <v>615</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46260.375</v>
+        <v>46268.375</v>
       </c>
       <c r="B38">
-        <v>1055</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46260.38541666666</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="B39">
-        <v>1040</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46260.39583333334</v>
+        <v>46268.39583333334</v>
       </c>
       <c r="B40">
-        <v>1003</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46260.40625</v>
+        <v>46268.40625</v>
       </c>
       <c r="B41">
-        <v>1003</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46260.41666666666</v>
+        <v>46268.41666666666</v>
       </c>
       <c r="B42">
-        <v>892</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46260.42708333334</v>
+        <v>46268.42708333334</v>
       </c>
       <c r="B43">
-        <v>824</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46260.4375</v>
+        <v>46268.4375</v>
       </c>
       <c r="B44">
-        <v>781</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46260.44791666666</v>
+        <v>46268.44791666666</v>
       </c>
       <c r="B45">
-        <v>790</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46260.45833333334</v>
+        <v>46268.45833333334</v>
       </c>
       <c r="B46">
-        <v>720</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46260.46875</v>
+        <v>46268.46875</v>
       </c>
       <c r="B47">
-        <v>748</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46260.47916666666</v>
+        <v>46268.47916666666</v>
       </c>
       <c r="B48">
-        <v>708</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46260.48958333334</v>
+        <v>46268.48958333334</v>
       </c>
       <c r="B49">
-        <v>708</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46260.5</v>
+        <v>46268.5</v>
       </c>
       <c r="B50">
-        <v>454</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46260.51041666666</v>
+        <v>46268.51041666666</v>
       </c>
       <c r="B51">
-        <v>447</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46260.52083333334</v>
+        <v>46268.52083333334</v>
       </c>
       <c r="B52">
-        <v>393</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46260.53125</v>
+        <v>46268.53125</v>
       </c>
       <c r="B53">
-        <v>390</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46260.54166666666</v>
+        <v>46268.54166666666</v>
       </c>
       <c r="B54">
-        <v>420</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46260.55208333334</v>
+        <v>46268.55208333334</v>
       </c>
       <c r="B55">
-        <v>438</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46260.5625</v>
+        <v>46268.5625</v>
       </c>
       <c r="B56">
-        <v>506</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46260.57291666666</v>
+        <v>46268.57291666666</v>
       </c>
       <c r="B57">
-        <v>524</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46260.58333333334</v>
+        <v>46268.58333333334</v>
       </c>
       <c r="B58">
-        <v>703</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46260.59375</v>
+        <v>46268.59375</v>
       </c>
       <c r="B59">
-        <v>729</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46260.60416666666</v>
+        <v>46268.60416666666</v>
       </c>
       <c r="B60">
-        <v>787</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46260.61458333334</v>
+        <v>46268.61458333334</v>
       </c>
       <c r="B61">
-        <v>784</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46260.625</v>
+        <v>46268.625</v>
       </c>
       <c r="B62">
-        <v>776</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46260.63541666666</v>
+        <v>46268.63541666666</v>
       </c>
       <c r="B63">
-        <v>777</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46260.64583333334</v>
+        <v>46268.64583333334</v>
       </c>
       <c r="B64">
-        <v>771</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46260.65625</v>
+        <v>46268.65625</v>
       </c>
       <c r="B65">
-        <v>777</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46260.66666666666</v>
+        <v>46268.66666666666</v>
       </c>
       <c r="B66">
-        <v>768</v>
+        <v>797</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46260.67708333334</v>
+        <v>46268.67708333334</v>
       </c>
       <c r="B67">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46260.6875</v>
+        <v>46268.6875</v>
       </c>
       <c r="B68">
-        <v>767</v>
+        <v>833</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46260.69791666666</v>
+        <v>46268.69791666666</v>
       </c>
       <c r="B69">
-        <v>776</v>
+        <v>922</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46260.70833333334</v>
+        <v>46268.70833333334</v>
       </c>
       <c r="B70">
-        <v>834</v>
+        <v>965</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46260.71875</v>
+        <v>46268.71875</v>
       </c>
       <c r="B71">
-        <v>799</v>
+        <v>979</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46260.72916666666</v>
+        <v>46268.72916666666</v>
       </c>
       <c r="B72">
-        <v>819</v>
+        <v>979</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46260.73958333334</v>
+        <v>46268.73958333334</v>
       </c>
       <c r="B73">
-        <v>830</v>
+        <v>916</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46260.75</v>
+        <v>46268.75</v>
       </c>
       <c r="B74">
-        <v>853</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46260.76041666666</v>
+        <v>46268.76041666666</v>
       </c>
       <c r="B75">
-        <v>850</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46260.77083333334</v>
+        <v>46268.77083333334</v>
       </c>
       <c r="B76">
-        <v>840</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46260.78125</v>
+        <v>46268.78125</v>
       </c>
       <c r="B77">
-        <v>849</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46260.79166666666</v>
+        <v>46268.79166666666</v>
       </c>
       <c r="B78">
-        <v>917</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46260.80208333334</v>
+        <v>46268.80208333334</v>
       </c>
       <c r="B79">
-        <v>921</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46260.8125</v>
+        <v>46268.8125</v>
       </c>
       <c r="B80">
-        <v>914</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46260.82291666666</v>
+        <v>46268.82291666666</v>
       </c>
       <c r="B81">
-        <v>908</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46260.83333333334</v>
+        <v>46268.83333333334</v>
       </c>
       <c r="B82">
-        <v>888</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46260.84375</v>
+        <v>46268.84375</v>
       </c>
       <c r="B83">
-        <v>905</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46260.85416666666</v>
+        <v>46268.85416666666</v>
       </c>
       <c r="B84">
-        <v>901</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46260.86458333334</v>
+        <v>46268.86458333334</v>
       </c>
       <c r="B85">
-        <v>892</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46260.875</v>
+        <v>46268.875</v>
       </c>
       <c r="B86">
-        <v>844</v>
+        <v>947</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46260.88541666666</v>
+        <v>46268.88541666666</v>
       </c>
       <c r="B87">
-        <v>836</v>
+        <v>948</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46260.89583333334</v>
+        <v>46268.89583333334</v>
       </c>
       <c r="B88">
-        <v>834</v>
+        <v>952</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46260.90625</v>
+        <v>46268.90625</v>
       </c>
       <c r="B89">
-        <v>822</v>
+        <v>932</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46260.91666666666</v>
+        <v>46268.91666666666</v>
       </c>
       <c r="B90">
-        <v>743</v>
+        <v>855</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46260.92708333334</v>
+        <v>46268.92708333334</v>
       </c>
       <c r="B91">
-        <v>744</v>
+        <v>850</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46260.9375</v>
+        <v>46268.9375</v>
       </c>
       <c r="B92">
-        <v>749</v>
+        <v>843</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46260.94791666666</v>
+        <v>46268.94791666666</v>
       </c>
       <c r="B93">
-        <v>741</v>
+        <v>843</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46260.95833333334</v>
+        <v>46268.95833333334</v>
       </c>
       <c r="B94">
-        <v>731</v>
+        <v>813</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46260.96875</v>
+        <v>46268.96875</v>
       </c>
       <c r="B95">
-        <v>733</v>
+        <v>810</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46260.97916666666</v>
+        <v>46268.97916666666</v>
       </c>
       <c r="B96">
-        <v>731</v>
+        <v>806</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46260.98958333334</v>
+        <v>46268.98958333334</v>
       </c>
       <c r="B97">
-        <v>739</v>
+        <v>810</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="B98">
-        <v>888</v>
+        <v>867</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46261.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B99">
-        <v>885</v>
+        <v>867</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46261.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B100">
-        <v>885</v>
+        <v>866</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46261.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B101">
-        <v>884</v>
+        <v>863</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46261.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B102">
-        <v>887</v>
+        <v>867</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46261.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B103">
-        <v>885</v>
+        <v>864</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46261.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B104">
-        <v>884</v>
+        <v>864</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46261.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B105">
-        <v>879</v>
+        <v>866</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46261.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B106">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46261.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B107">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46261.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B108">
         <v>854</v>
@@ -1250,1066 +1250,274 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46261.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B109">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46261.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B110">
-        <v>839</v>
+        <v>855</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46261.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B111">
-        <v>837</v>
+        <v>855</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46261.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B112">
-        <v>837</v>
+        <v>854</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46261.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B113">
-        <v>835</v>
+        <v>861</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46261.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B114">
-        <v>835</v>
+        <v>884</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46261.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B115">
-        <v>835</v>
+        <v>884</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46261.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B116">
-        <v>835</v>
+        <v>885</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46261.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B117">
-        <v>838</v>
+        <v>884</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46261.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B118">
-        <v>867</v>
+        <v>924</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46261.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B119">
-        <v>873</v>
+        <v>931</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46261.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B120">
-        <v>871</v>
+        <v>958</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46261.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B121">
-        <v>873</v>
+        <v>960</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46261.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B122">
-        <v>898</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46261.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B123">
-        <v>904</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46261.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B124">
-        <v>901</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46261.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B125">
-        <v>910</v>
+        <v>991</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46261.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B126">
-        <v>949</v>
+        <v>964</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46261.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B127">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46261.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B128">
-        <v>897</v>
+        <v>932</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46261.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B129">
-        <v>898</v>
+        <v>931</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46261.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B130">
-        <v>785</v>
+        <v>899</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46261.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B131">
-        <v>813</v>
+        <v>936</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46261.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B132">
-        <v>812</v>
+        <v>787</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46261.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B133">
-        <v>818</v>
+        <v>766</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46261.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B134">
-        <v>853</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46261.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B135">
-        <v>836</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46261.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B136">
-        <v>800</v>
+        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46261.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B137">
-        <v>799</v>
+        <v>221</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46261.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B138">
-        <v>799</v>
+        <v>173</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46261.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B139">
-        <v>652</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46261.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B140">
-        <v>660</v>
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46261.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B141">
-        <v>665</v>
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46261.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B142">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46261.46875</v>
-      </c>
-      <c r="B143">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46261.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46261.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46261.5</v>
-      </c>
-      <c r="B146">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46261.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46261.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46261.53125</v>
-      </c>
-      <c r="B149">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46261.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46261.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46261.5625</v>
-      </c>
-      <c r="B152">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46261.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46261.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46261.59375</v>
-      </c>
-      <c r="B155">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46261.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46261.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46261.625</v>
-      </c>
-      <c r="B158">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46261.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46261.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46261.65625</v>
-      </c>
-      <c r="B161">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46261.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46261.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46261.6875</v>
-      </c>
-      <c r="B164">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46261.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46261.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46261.71875</v>
-      </c>
-      <c r="B167">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46261.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46261.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46261.75</v>
-      </c>
-      <c r="B170">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46261.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46261.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46261.78125</v>
-      </c>
-      <c r="B173">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46261.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46261.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46261.8125</v>
-      </c>
-      <c r="B176">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46261.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46261.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46261.84375</v>
-      </c>
-      <c r="B179">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46261.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46261.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46261.875</v>
-      </c>
-      <c r="B182">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46261.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46261.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46261.90625</v>
-      </c>
-      <c r="B185">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46261.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46261.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46261.9375</v>
-      </c>
-      <c r="B188">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46261.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46261.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46261.96875</v>
-      </c>
-      <c r="B191">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46261.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46261.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B194">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="2">
-        <v>46262.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="2">
-        <v>46262.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="2">
-        <v>46262.03125</v>
-      </c>
-      <c r="B197">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="2">
-        <v>46262.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="2">
-        <v>46262.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="2">
-        <v>46262.0625</v>
-      </c>
-      <c r="B200">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="2">
-        <v>46262.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="2">
-        <v>46262.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="2">
-        <v>46262.09375</v>
-      </c>
-      <c r="B203">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="2">
-        <v>46262.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="2">
-        <v>46262.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="2">
-        <v>46262.125</v>
-      </c>
-      <c r="B206">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="2">
-        <v>46262.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="2">
-        <v>46262.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="2">
-        <v>46262.15625</v>
-      </c>
-      <c r="B209">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="2">
-        <v>46262.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="2">
-        <v>46262.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="2">
-        <v>46262.1875</v>
-      </c>
-      <c r="B212">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="2">
-        <v>46262.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="2">
-        <v>46262.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="2">
-        <v>46262.21875</v>
-      </c>
-      <c r="B215">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="2">
-        <v>46262.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="2">
-        <v>46262.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="2">
-        <v>46262.25</v>
-      </c>
-      <c r="B218">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="2">
-        <v>46262.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="2">
-        <v>46262.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="2">
-        <v>46262.28125</v>
-      </c>
-      <c r="B221">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="2">
-        <v>46262.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="2">
-        <v>46262.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="2">
-        <v>46262.3125</v>
-      </c>
-      <c r="B224">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="2">
-        <v>46262.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="2">
-        <v>46262.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
-      <c r="A227" s="2">
-        <v>46262.34375</v>
-      </c>
-      <c r="B227">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
-      <c r="A228" s="2">
-        <v>46262.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
-      <c r="A229" s="2">
-        <v>46262.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
-      <c r="A230" s="2">
-        <v>46262.375</v>
-      </c>
-      <c r="B230">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="2">
-        <v>46262.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="A232" s="2">
-        <v>46262.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="A233" s="2">
-        <v>46262.40625</v>
-      </c>
-      <c r="B233">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" s="2">
-        <v>46262.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="A235" s="2">
-        <v>46262.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="A236" s="2">
-        <v>46262.4375</v>
-      </c>
-      <c r="B236">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" s="2">
-        <v>46262.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="A238" s="2">
-        <v>46262.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" s="2">
-        <v>46262.46875</v>
-      </c>
-      <c r="B239">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" s="2">
-        <v>46262.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="A241" s="2">
-        <v>46262.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
